--- a/rcads/data/xls/23_InstrumentItemMap.xlsx
+++ b/rcads/data/xls/23_InstrumentItemMap.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_23_InstrumentItemMap"/>
   </sheets>
   <definedNames>
-    <definedName name="_23_InstrumentItemMap">'_23_InstrumentItemMap'!$A$1:$E$4719</definedName>
+    <definedName name="_23_InstrumentItemMap">'_23_InstrumentItemMap'!$A$1:$E$5007</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4719"/>
+  <dimension ref="A1:E5007"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -26882,7 +26882,7 @@
         <v>1</v>
       </c>
       <c r="C1863" s="0">
-        <v>1972</v>
+        <v>15</v>
       </c>
       <c r="D1863" s="0">
         <v>29</v>
@@ -65138,2157 +65138,6189 @@
     </row>
     <row outlineLevel="0" r="4566">
       <c r="A4566" s="0">
-        <v>5578</v>
+        <v>5747</v>
       </c>
       <c r="B4566" s="0">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="C4566" s="0">
-        <v>3248</v>
+        <v>3348</v>
       </c>
       <c r="D4566" s="0">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="4567">
       <c r="A4567" s="0">
-        <v>5579</v>
+        <v>5748</v>
       </c>
       <c r="B4567" s="0">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C4567" s="0">
-        <v>3248</v>
+        <v>3349</v>
       </c>
       <c r="D4567" s="0">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row outlineLevel="0" r="4568">
       <c r="A4568" s="0">
-        <v>5580</v>
+        <v>5749</v>
       </c>
       <c r="B4568" s="0">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="C4568" s="0">
-        <v>3249</v>
+        <v>3350</v>
       </c>
       <c r="D4568" s="0">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row outlineLevel="0" r="4569">
       <c r="A4569" s="0">
-        <v>5581</v>
+        <v>5750</v>
       </c>
       <c r="B4569" s="0">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C4569" s="0">
-        <v>3249</v>
+        <v>3351</v>
       </c>
       <c r="D4569" s="0">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row outlineLevel="0" r="4570">
       <c r="A4570" s="0">
-        <v>5582</v>
+        <v>5751</v>
       </c>
       <c r="B4570" s="0">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="C4570" s="0">
-        <v>3250</v>
+        <v>3352</v>
       </c>
       <c r="D4570" s="0">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="4571">
       <c r="A4571" s="0">
-        <v>5583</v>
+        <v>5752</v>
       </c>
       <c r="B4571" s="0">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C4571" s="0">
-        <v>3250</v>
+        <v>3353</v>
       </c>
       <c r="D4571" s="0">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row outlineLevel="0" r="4572">
       <c r="A4572" s="0">
-        <v>5584</v>
+        <v>5753</v>
       </c>
       <c r="B4572" s="0">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="C4572" s="0">
-        <v>3251</v>
+        <v>3354</v>
       </c>
       <c r="D4572" s="0">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="4573">
       <c r="A4573" s="0">
-        <v>5585</v>
+        <v>5754</v>
       </c>
       <c r="B4573" s="0">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="C4573" s="0">
-        <v>3252</v>
+        <v>3355</v>
       </c>
       <c r="D4573" s="0">
-        <v>46</v>
+        <v>8</v>
       </c>
     </row>
     <row outlineLevel="0" r="4574">
       <c r="A4574" s="0">
-        <v>5586</v>
+        <v>5755</v>
       </c>
       <c r="B4574" s="0">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="C4574" s="0">
-        <v>3253</v>
+        <v>3356</v>
       </c>
       <c r="D4574" s="0">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row outlineLevel="0" r="4575">
       <c r="A4575" s="0">
-        <v>5587</v>
+        <v>5756</v>
       </c>
       <c r="B4575" s="0">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C4575" s="0">
-        <v>3253</v>
+        <v>3357</v>
       </c>
       <c r="D4575" s="0">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row outlineLevel="0" r="4576">
       <c r="A4576" s="0">
-        <v>5588</v>
+        <v>5757</v>
       </c>
       <c r="B4576" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4576" s="0">
-        <v>3254</v>
+        <v>3358</v>
       </c>
       <c r="D4576" s="0">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row outlineLevel="0" r="4577">
       <c r="A4577" s="0">
-        <v>5589</v>
+        <v>5758</v>
       </c>
       <c r="B4577" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4577" s="0">
-        <v>3255</v>
+        <v>3359</v>
       </c>
       <c r="D4577" s="0">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row outlineLevel="0" r="4578">
       <c r="A4578" s="0">
-        <v>5590</v>
+        <v>5759</v>
       </c>
       <c r="B4578" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4578" s="0">
-        <v>3256</v>
+        <v>3360</v>
       </c>
       <c r="D4578" s="0">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row outlineLevel="0" r="4579">
       <c r="A4579" s="0">
-        <v>5591</v>
+        <v>5760</v>
       </c>
       <c r="B4579" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4579" s="0">
-        <v>3257</v>
+        <v>3361</v>
       </c>
       <c r="D4579" s="0">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row outlineLevel="0" r="4580">
       <c r="A4580" s="0">
-        <v>5592</v>
+        <v>5761</v>
       </c>
       <c r="B4580" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4580" s="0">
-        <v>3258</v>
+        <v>3362</v>
       </c>
       <c r="D4580" s="0">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row outlineLevel="0" r="4581">
       <c r="A4581" s="0">
-        <v>5593</v>
+        <v>5762</v>
       </c>
       <c r="B4581" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4581" s="0">
-        <v>3259</v>
+        <v>3363</v>
       </c>
       <c r="D4581" s="0">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row outlineLevel="0" r="4582">
       <c r="A4582" s="0">
-        <v>5594</v>
+        <v>5763</v>
       </c>
       <c r="B4582" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4582" s="0">
-        <v>3260</v>
+        <v>3364</v>
       </c>
       <c r="D4582" s="0">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row outlineLevel="0" r="4583">
       <c r="A4583" s="0">
-        <v>5595</v>
+        <v>5764</v>
       </c>
       <c r="B4583" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4583" s="0">
-        <v>3261</v>
+        <v>3365</v>
       </c>
       <c r="D4583" s="0">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row outlineLevel="0" r="4584">
       <c r="A4584" s="0">
-        <v>5596</v>
+        <v>5765</v>
       </c>
       <c r="B4584" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4584" s="0">
-        <v>3262</v>
+        <v>3366</v>
       </c>
       <c r="D4584" s="0">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row outlineLevel="0" r="4585">
       <c r="A4585" s="0">
-        <v>5597</v>
+        <v>5766</v>
       </c>
       <c r="B4585" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4585" s="0">
-        <v>3263</v>
+        <v>3367</v>
       </c>
       <c r="D4585" s="0">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row outlineLevel="0" r="4586">
       <c r="A4586" s="0">
-        <v>5598</v>
+        <v>5767</v>
       </c>
       <c r="B4586" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4586" s="0">
-        <v>3264</v>
+        <v>3368</v>
       </c>
       <c r="D4586" s="0">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row outlineLevel="0" r="4587">
       <c r="A4587" s="0">
-        <v>5599</v>
+        <v>5768</v>
       </c>
       <c r="B4587" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4587" s="0">
-        <v>3265</v>
+        <v>3369</v>
       </c>
       <c r="D4587" s="0">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="4588">
       <c r="A4588" s="0">
-        <v>5600</v>
+        <v>5769</v>
       </c>
       <c r="B4588" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4588" s="0">
-        <v>3266</v>
+        <v>3370</v>
       </c>
       <c r="D4588" s="0">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row outlineLevel="0" r="4589">
       <c r="A4589" s="0">
-        <v>5601</v>
+        <v>5770</v>
       </c>
       <c r="B4589" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4589" s="0">
-        <v>3267</v>
+        <v>3371</v>
       </c>
       <c r="D4589" s="0">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row outlineLevel="0" r="4590">
       <c r="A4590" s="0">
-        <v>5602</v>
+        <v>5771</v>
       </c>
       <c r="B4590" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4590" s="0">
-        <v>3268</v>
+        <v>3372</v>
       </c>
       <c r="D4590" s="0">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row outlineLevel="0" r="4591">
       <c r="A4591" s="0">
-        <v>5603</v>
+        <v>5772</v>
       </c>
       <c r="B4591" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4591" s="0">
-        <v>3269</v>
+        <v>3373</v>
       </c>
       <c r="D4591" s="0">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row outlineLevel="0" r="4592">
       <c r="A4592" s="0">
-        <v>5604</v>
+        <v>5773</v>
       </c>
       <c r="B4592" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4592" s="0">
-        <v>3270</v>
+        <v>3374</v>
       </c>
       <c r="D4592" s="0">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row outlineLevel="0" r="4593">
       <c r="A4593" s="0">
-        <v>5605</v>
+        <v>5774</v>
       </c>
       <c r="B4593" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4593" s="0">
-        <v>3271</v>
+        <v>3375</v>
       </c>
       <c r="D4593" s="0">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row outlineLevel="0" r="4594">
       <c r="A4594" s="0">
-        <v>5606</v>
+        <v>5775</v>
       </c>
       <c r="B4594" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4594" s="0">
-        <v>3272</v>
+        <v>3376</v>
       </c>
       <c r="D4594" s="0">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row outlineLevel="0" r="4595">
       <c r="A4595" s="0">
-        <v>5607</v>
+        <v>5776</v>
       </c>
       <c r="B4595" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4595" s="0">
-        <v>3273</v>
+        <v>3377</v>
       </c>
       <c r="D4595" s="0">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row outlineLevel="0" r="4596">
       <c r="A4596" s="0">
-        <v>5608</v>
+        <v>5777</v>
       </c>
       <c r="B4596" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4596" s="0">
-        <v>3274</v>
+        <v>3378</v>
       </c>
       <c r="D4596" s="0">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row outlineLevel="0" r="4597">
       <c r="A4597" s="0">
-        <v>5609</v>
+        <v>5778</v>
       </c>
       <c r="B4597" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4597" s="0">
-        <v>3275</v>
+        <v>3379</v>
       </c>
       <c r="D4597" s="0">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row outlineLevel="0" r="4598">
       <c r="A4598" s="0">
-        <v>5610</v>
+        <v>5779</v>
       </c>
       <c r="B4598" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4598" s="0">
-        <v>3276</v>
+        <v>3380</v>
       </c>
       <c r="D4598" s="0">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row outlineLevel="0" r="4599">
       <c r="A4599" s="0">
-        <v>5611</v>
+        <v>5780</v>
       </c>
       <c r="B4599" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4599" s="0">
-        <v>3277</v>
+        <v>3381</v>
       </c>
       <c r="D4599" s="0">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row outlineLevel="0" r="4600">
       <c r="A4600" s="0">
-        <v>5612</v>
+        <v>5781</v>
       </c>
       <c r="B4600" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4600" s="0">
-        <v>3278</v>
+        <v>3382</v>
       </c>
       <c r="D4600" s="0">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row outlineLevel="0" r="4601">
       <c r="A4601" s="0">
-        <v>5613</v>
+        <v>5782</v>
       </c>
       <c r="B4601" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4601" s="0">
-        <v>3279</v>
+        <v>3383</v>
       </c>
       <c r="D4601" s="0">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row outlineLevel="0" r="4602">
       <c r="A4602" s="0">
-        <v>5614</v>
+        <v>5783</v>
       </c>
       <c r="B4602" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4602" s="0">
-        <v>3280</v>
+        <v>3384</v>
       </c>
       <c r="D4602" s="0">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row outlineLevel="0" r="4603">
       <c r="A4603" s="0">
-        <v>5615</v>
+        <v>5784</v>
       </c>
       <c r="B4603" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4603" s="0">
-        <v>3281</v>
+        <v>3385</v>
       </c>
       <c r="D4603" s="0">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row outlineLevel="0" r="4604">
       <c r="A4604" s="0">
-        <v>5616</v>
+        <v>5785</v>
       </c>
       <c r="B4604" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4604" s="0">
-        <v>3282</v>
+        <v>3386</v>
       </c>
       <c r="D4604" s="0">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row outlineLevel="0" r="4605">
       <c r="A4605" s="0">
-        <v>5617</v>
+        <v>5786</v>
       </c>
       <c r="B4605" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4605" s="0">
-        <v>3283</v>
+        <v>3387</v>
       </c>
       <c r="D4605" s="0">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row outlineLevel="0" r="4606">
       <c r="A4606" s="0">
-        <v>5618</v>
+        <v>5787</v>
       </c>
       <c r="B4606" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4606" s="0">
-        <v>3284</v>
+        <v>3388</v>
       </c>
       <c r="D4606" s="0">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row outlineLevel="0" r="4607">
       <c r="A4607" s="0">
-        <v>5619</v>
+        <v>5788</v>
       </c>
       <c r="B4607" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4607" s="0">
-        <v>3285</v>
+        <v>3389</v>
       </c>
       <c r="D4607" s="0">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row outlineLevel="0" r="4608">
       <c r="A4608" s="0">
-        <v>5620</v>
+        <v>5789</v>
       </c>
       <c r="B4608" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4608" s="0">
-        <v>3286</v>
+        <v>3390</v>
       </c>
       <c r="D4608" s="0">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row outlineLevel="0" r="4609">
       <c r="A4609" s="0">
-        <v>5621</v>
+        <v>5790</v>
       </c>
       <c r="B4609" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4609" s="0">
-        <v>3287</v>
+        <v>3391</v>
       </c>
       <c r="D4609" s="0">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row outlineLevel="0" r="4610">
       <c r="A4610" s="0">
-        <v>5622</v>
+        <v>5791</v>
       </c>
       <c r="B4610" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4610" s="0">
-        <v>3288</v>
+        <v>3392</v>
       </c>
       <c r="D4610" s="0">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row outlineLevel="0" r="4611">
       <c r="A4611" s="0">
-        <v>5623</v>
+        <v>5792</v>
       </c>
       <c r="B4611" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4611" s="0">
-        <v>3289</v>
+        <v>3393</v>
       </c>
       <c r="D4611" s="0">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row outlineLevel="0" r="4612">
       <c r="A4612" s="0">
-        <v>5624</v>
+        <v>5793</v>
       </c>
       <c r="B4612" s="0">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C4612" s="0">
-        <v>3290</v>
+        <v>3394</v>
       </c>
       <c r="D4612" s="0">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row outlineLevel="0" r="4613">
       <c r="A4613" s="0">
-        <v>5625</v>
+        <v>5794</v>
       </c>
       <c r="B4613" s="0">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C4613" s="0">
-        <v>3291</v>
+        <v>3395</v>
       </c>
       <c r="D4613" s="0">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="4614">
       <c r="A4614" s="0">
-        <v>5626</v>
+        <v>5795</v>
       </c>
       <c r="B4614" s="0">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C4614" s="0">
-        <v>3292</v>
+        <v>3396</v>
       </c>
       <c r="D4614" s="0">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row outlineLevel="0" r="4615">
       <c r="A4615" s="0">
-        <v>5627</v>
+        <v>5796</v>
       </c>
       <c r="B4615" s="0">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C4615" s="0">
-        <v>3293</v>
+        <v>3397</v>
       </c>
       <c r="D4615" s="0">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row outlineLevel="0" r="4616">
       <c r="A4616" s="0">
-        <v>5628</v>
+        <v>5797</v>
       </c>
       <c r="B4616" s="0">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C4616" s="0">
-        <v>3294</v>
+        <v>3398</v>
       </c>
       <c r="D4616" s="0">
-        <v>41</v>
+        <v>4</v>
       </c>
     </row>
     <row outlineLevel="0" r="4617">
       <c r="A4617" s="0">
-        <v>5629</v>
+        <v>5798</v>
       </c>
       <c r="B4617" s="0">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C4617" s="0">
-        <v>3295</v>
+        <v>3399</v>
       </c>
       <c r="D4617" s="0">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="4618">
       <c r="A4618" s="0">
-        <v>5630</v>
+        <v>5799</v>
       </c>
       <c r="B4618" s="0">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C4618" s="0">
-        <v>3296</v>
+        <v>3400</v>
       </c>
       <c r="D4618" s="0">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row outlineLevel="0" r="4619">
       <c r="A4619" s="0">
-        <v>5631</v>
+        <v>5800</v>
       </c>
       <c r="B4619" s="0">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C4619" s="0">
-        <v>3297</v>
+        <v>3401</v>
       </c>
       <c r="D4619" s="0">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="4620">
       <c r="A4620" s="0">
-        <v>5632</v>
+        <v>5801</v>
       </c>
       <c r="B4620" s="0">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C4620" s="0">
-        <v>3298</v>
+        <v>3402</v>
       </c>
       <c r="D4620" s="0">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row outlineLevel="0" r="4621">
       <c r="A4621" s="0">
-        <v>5633</v>
+        <v>5802</v>
       </c>
       <c r="B4621" s="0">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C4621" s="0">
-        <v>3299</v>
+        <v>3403</v>
       </c>
       <c r="D4621" s="0">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row outlineLevel="0" r="4622">
       <c r="A4622" s="0">
-        <v>5634</v>
+        <v>5803</v>
       </c>
       <c r="B4622" s="0">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C4622" s="0">
-        <v>3300</v>
+        <v>3404</v>
       </c>
       <c r="D4622" s="0">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row outlineLevel="0" r="4623">
       <c r="A4623" s="0">
-        <v>5635</v>
+        <v>5804</v>
       </c>
       <c r="B4623" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4623" s="0">
-        <v>3255</v>
+        <v>3405</v>
       </c>
       <c r="D4623" s="0">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row outlineLevel="0" r="4624">
       <c r="A4624" s="0">
-        <v>5636</v>
+        <v>5805</v>
       </c>
       <c r="B4624" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4624" s="0">
-        <v>3257</v>
+        <v>3406</v>
       </c>
       <c r="D4624" s="0">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row outlineLevel="0" r="4625">
       <c r="A4625" s="0">
-        <v>5637</v>
+        <v>5806</v>
       </c>
       <c r="B4625" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4625" s="0">
-        <v>3258</v>
+        <v>3407</v>
       </c>
       <c r="D4625" s="0">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row outlineLevel="0" r="4626">
       <c r="A4626" s="0">
-        <v>5638</v>
+        <v>5807</v>
       </c>
       <c r="B4626" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4626" s="0">
-        <v>3259</v>
+        <v>3408</v>
       </c>
       <c r="D4626" s="0">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row outlineLevel="0" r="4627">
       <c r="A4627" s="0">
-        <v>5639</v>
+        <v>5808</v>
       </c>
       <c r="B4627" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4627" s="0">
-        <v>3266</v>
+        <v>3409</v>
       </c>
       <c r="D4627" s="0">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row outlineLevel="0" r="4628">
       <c r="A4628" s="0">
-        <v>5640</v>
+        <v>5809</v>
       </c>
       <c r="B4628" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4628" s="0">
-        <v>3286</v>
+        <v>3410</v>
       </c>
       <c r="D4628" s="0">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row outlineLevel="0" r="4629">
       <c r="A4629" s="0">
-        <v>5641</v>
+        <v>5810</v>
       </c>
       <c r="B4629" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4629" s="0">
-        <v>3285</v>
+        <v>3411</v>
       </c>
       <c r="D4629" s="0">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row outlineLevel="0" r="4630">
       <c r="A4630" s="0">
-        <v>5642</v>
+        <v>5811</v>
       </c>
       <c r="B4630" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4630" s="0">
-        <v>3264</v>
+        <v>3412</v>
       </c>
       <c r="D4630" s="0">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row outlineLevel="0" r="4631">
       <c r="A4631" s="0">
-        <v>5643</v>
+        <v>5812</v>
       </c>
       <c r="B4631" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4631" s="0">
-        <v>3270</v>
+        <v>3413</v>
       </c>
       <c r="D4631" s="0">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row outlineLevel="0" r="4632">
       <c r="A4632" s="0">
-        <v>5644</v>
+        <v>5813</v>
       </c>
       <c r="B4632" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4632" s="0">
-        <v>3268</v>
+        <v>3414</v>
       </c>
       <c r="D4632" s="0">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row outlineLevel="0" r="4633">
       <c r="A4633" s="0">
-        <v>5645</v>
+        <v>5814</v>
       </c>
       <c r="B4633" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4633" s="0">
-        <v>3289</v>
+        <v>3415</v>
       </c>
       <c r="D4633" s="0">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row outlineLevel="0" r="4634">
       <c r="A4634" s="0">
-        <v>5646</v>
+        <v>5815</v>
       </c>
       <c r="B4634" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4634" s="0">
-        <v>3295</v>
+        <v>3416</v>
       </c>
       <c r="D4634" s="0">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="4635">
       <c r="A4635" s="0">
-        <v>5647</v>
+        <v>5816</v>
       </c>
       <c r="B4635" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4635" s="0">
-        <v>3272</v>
+        <v>3417</v>
       </c>
       <c r="D4635" s="0">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row outlineLevel="0" r="4636">
       <c r="A4636" s="0">
-        <v>5648</v>
+        <v>5817</v>
       </c>
       <c r="B4636" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4636" s="0">
-        <v>3279</v>
+        <v>3418</v>
       </c>
       <c r="D4636" s="0">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row outlineLevel="0" r="4637">
       <c r="A4637" s="0">
-        <v>5649</v>
+        <v>5818</v>
       </c>
       <c r="B4637" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4637" s="0">
-        <v>3278</v>
+        <v>3419</v>
       </c>
       <c r="D4637" s="0">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row outlineLevel="0" r="4638">
       <c r="A4638" s="0">
-        <v>5650</v>
+        <v>5819</v>
       </c>
       <c r="B4638" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4638" s="0">
-        <v>3282</v>
+        <v>3420</v>
       </c>
       <c r="D4638" s="0">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row outlineLevel="0" r="4639">
       <c r="A4639" s="0">
-        <v>5651</v>
+        <v>5820</v>
       </c>
       <c r="B4639" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4639" s="0">
-        <v>3284</v>
+        <v>3421</v>
       </c>
       <c r="D4639" s="0">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row outlineLevel="0" r="4640">
       <c r="A4640" s="0">
-        <v>5652</v>
+        <v>5821</v>
       </c>
       <c r="B4640" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4640" s="0">
-        <v>3290</v>
+        <v>3422</v>
       </c>
       <c r="D4640" s="0">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row outlineLevel="0" r="4641">
       <c r="A4641" s="0">
-        <v>5653</v>
+        <v>5822</v>
       </c>
       <c r="B4641" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4641" s="0">
-        <v>3293</v>
+        <v>3423</v>
       </c>
       <c r="D4641" s="0">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row outlineLevel="0" r="4642">
       <c r="A4642" s="0">
-        <v>5654</v>
+        <v>5823</v>
       </c>
       <c r="B4642" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4642" s="0">
-        <v>3294</v>
+        <v>3424</v>
       </c>
       <c r="D4642" s="0">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row outlineLevel="0" r="4643">
       <c r="A4643" s="0">
-        <v>5655</v>
+        <v>5824</v>
       </c>
       <c r="B4643" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4643" s="0">
-        <v>3274</v>
+        <v>3425</v>
       </c>
       <c r="D4643" s="0">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row outlineLevel="0" r="4644">
       <c r="A4644" s="0">
-        <v>5656</v>
+        <v>5825</v>
       </c>
       <c r="B4644" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4644" s="0">
-        <v>3296</v>
+        <v>3426</v>
       </c>
       <c r="D4644" s="0">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row outlineLevel="0" r="4645">
       <c r="A4645" s="0">
-        <v>5657</v>
+        <v>5826</v>
       </c>
       <c r="B4645" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4645" s="0">
-        <v>3297</v>
+        <v>3427</v>
       </c>
       <c r="D4645" s="0">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row outlineLevel="0" r="4646">
       <c r="A4646" s="0">
-        <v>5658</v>
+        <v>5827</v>
       </c>
       <c r="B4646" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4646" s="0">
-        <v>3300</v>
+        <v>3428</v>
       </c>
       <c r="D4646" s="0">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row outlineLevel="0" r="4647">
       <c r="A4647" s="0">
-        <v>5659</v>
+        <v>5828</v>
       </c>
       <c r="B4647" s="0">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4647" s="0">
-        <v>3280</v>
+        <v>3429</v>
       </c>
       <c r="D4647" s="0">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row outlineLevel="0" r="4648">
       <c r="A4648" s="0">
-        <v>5660</v>
+        <v>5829</v>
       </c>
       <c r="B4648" s="0">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C4648" s="0">
-        <v>3301</v>
+        <v>3430</v>
       </c>
       <c r="D4648" s="0">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row outlineLevel="0" r="4649">
       <c r="A4649" s="0">
-        <v>5661</v>
+        <v>5830</v>
       </c>
       <c r="B4649" s="0">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C4649" s="0">
-        <v>3302</v>
+        <v>3431</v>
       </c>
       <c r="D4649" s="0">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row outlineLevel="0" r="4650">
       <c r="A4650" s="0">
-        <v>5662</v>
+        <v>5831</v>
       </c>
       <c r="B4650" s="0">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C4650" s="0">
-        <v>3303</v>
+        <v>3432</v>
       </c>
       <c r="D4650" s="0">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row outlineLevel="0" r="4651">
       <c r="A4651" s="0">
-        <v>5663</v>
+        <v>5832</v>
       </c>
       <c r="B4651" s="0">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C4651" s="0">
-        <v>3304</v>
+        <v>3433</v>
       </c>
       <c r="D4651" s="0">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row outlineLevel="0" r="4652">
       <c r="A4652" s="0">
-        <v>5664</v>
+        <v>5833</v>
       </c>
       <c r="B4652" s="0">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C4652" s="0">
-        <v>3305</v>
+        <v>3434</v>
       </c>
       <c r="D4652" s="0">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row outlineLevel="0" r="4653">
       <c r="A4653" s="0">
-        <v>5665</v>
+        <v>5834</v>
       </c>
       <c r="B4653" s="0">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C4653" s="0">
-        <v>3306</v>
+        <v>3435</v>
       </c>
       <c r="D4653" s="0">
-        <v>6</v>
+        <v>41</v>
       </c>
     </row>
     <row outlineLevel="0" r="4654">
       <c r="A4654" s="0">
-        <v>5666</v>
+        <v>5835</v>
       </c>
       <c r="B4654" s="0">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C4654" s="0">
-        <v>3307</v>
+        <v>3436</v>
       </c>
       <c r="D4654" s="0">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row outlineLevel="0" r="4655">
       <c r="A4655" s="0">
-        <v>5667</v>
+        <v>5836</v>
       </c>
       <c r="B4655" s="0">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C4655" s="0">
-        <v>3308</v>
+        <v>3437</v>
       </c>
       <c r="D4655" s="0">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row outlineLevel="0" r="4656">
       <c r="A4656" s="0">
-        <v>5668</v>
+        <v>5837</v>
       </c>
       <c r="B4656" s="0">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C4656" s="0">
-        <v>3309</v>
+        <v>3438</v>
       </c>
       <c r="D4656" s="0">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row outlineLevel="0" r="4657">
       <c r="A4657" s="0">
-        <v>5669</v>
+        <v>5838</v>
       </c>
       <c r="B4657" s="0">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C4657" s="0">
-        <v>3310</v>
+        <v>3439</v>
       </c>
       <c r="D4657" s="0">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row outlineLevel="0" r="4658">
       <c r="A4658" s="0">
-        <v>5670</v>
+        <v>5839</v>
       </c>
       <c r="B4658" s="0">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C4658" s="0">
-        <v>3311</v>
+        <v>3440</v>
       </c>
       <c r="D4658" s="0">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row outlineLevel="0" r="4659">
       <c r="A4659" s="0">
-        <v>5671</v>
+        <v>5840</v>
       </c>
       <c r="B4659" s="0">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C4659" s="0">
-        <v>3312</v>
+        <v>3441</v>
       </c>
       <c r="D4659" s="0">
-        <v>12</v>
+        <v>47</v>
       </c>
     </row>
     <row outlineLevel="0" r="4660">
       <c r="A4660" s="0">
-        <v>5672</v>
+        <v>5841</v>
       </c>
       <c r="B4660" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4660" s="0">
-        <v>3313</v>
+        <v>3349</v>
       </c>
       <c r="D4660" s="0">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="4661">
       <c r="A4661" s="0">
-        <v>5673</v>
+        <v>5842</v>
       </c>
       <c r="B4661" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4661" s="0">
-        <v>3314</v>
+        <v>3351</v>
       </c>
       <c r="D4661" s="0">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row outlineLevel="0" r="4662">
       <c r="A4662" s="0">
-        <v>5674</v>
+        <v>5843</v>
       </c>
       <c r="B4662" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4662" s="0">
-        <v>3315</v>
+        <v>3352</v>
       </c>
       <c r="D4662" s="0">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row outlineLevel="0" r="4663">
       <c r="A4663" s="0">
-        <v>5675</v>
+        <v>5844</v>
       </c>
       <c r="B4663" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4663" s="0">
-        <v>3316</v>
+        <v>3353</v>
       </c>
       <c r="D4663" s="0">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row outlineLevel="0" r="4664">
       <c r="A4664" s="0">
-        <v>5676</v>
+        <v>5845</v>
       </c>
       <c r="B4664" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4664" s="0">
-        <v>3317</v>
+        <v>3360</v>
       </c>
       <c r="D4664" s="0">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="4665">
       <c r="A4665" s="0">
-        <v>5677</v>
+        <v>5846</v>
       </c>
       <c r="B4665" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4665" s="0">
-        <v>3318</v>
+        <v>3380</v>
       </c>
       <c r="D4665" s="0">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row outlineLevel="0" r="4666">
       <c r="A4666" s="0">
-        <v>5678</v>
+        <v>5847</v>
       </c>
       <c r="B4666" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4666" s="0">
-        <v>3319</v>
+        <v>3379</v>
       </c>
       <c r="D4666" s="0">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="4667">
       <c r="A4667" s="0">
-        <v>5679</v>
+        <v>5848</v>
       </c>
       <c r="B4667" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4667" s="0">
-        <v>3320</v>
+        <v>3358</v>
       </c>
       <c r="D4667" s="0">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row outlineLevel="0" r="4668">
       <c r="A4668" s="0">
-        <v>5680</v>
+        <v>5849</v>
       </c>
       <c r="B4668" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4668" s="0">
-        <v>3321</v>
+        <v>3364</v>
       </c>
       <c r="D4668" s="0">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row outlineLevel="0" r="4669">
       <c r="A4669" s="0">
-        <v>5681</v>
+        <v>5850</v>
       </c>
       <c r="B4669" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4669" s="0">
-        <v>3322</v>
+        <v>3362</v>
       </c>
       <c r="D4669" s="0">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row outlineLevel="0" r="4670">
       <c r="A4670" s="0">
-        <v>5682</v>
+        <v>5851</v>
       </c>
       <c r="B4670" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4670" s="0">
-        <v>3323</v>
+        <v>3383</v>
       </c>
       <c r="D4670" s="0">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row outlineLevel="0" r="4671">
       <c r="A4671" s="0">
-        <v>5683</v>
+        <v>5852</v>
       </c>
       <c r="B4671" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4671" s="0">
-        <v>3324</v>
+        <v>3389</v>
       </c>
       <c r="D4671" s="0">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row outlineLevel="0" r="4672">
       <c r="A4672" s="0">
-        <v>5684</v>
+        <v>5853</v>
       </c>
       <c r="B4672" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4672" s="0">
-        <v>3325</v>
+        <v>3366</v>
       </c>
       <c r="D4672" s="0">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row outlineLevel="0" r="4673">
       <c r="A4673" s="0">
-        <v>5685</v>
+        <v>5854</v>
       </c>
       <c r="B4673" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4673" s="0">
-        <v>3326</v>
+        <v>3373</v>
       </c>
       <c r="D4673" s="0">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row outlineLevel="0" r="4674">
       <c r="A4674" s="0">
-        <v>5686</v>
+        <v>5855</v>
       </c>
       <c r="B4674" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4674" s="0">
-        <v>3327</v>
+        <v>3372</v>
       </c>
       <c r="D4674" s="0">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row outlineLevel="0" r="4675">
       <c r="A4675" s="0">
-        <v>5687</v>
+        <v>5856</v>
       </c>
       <c r="B4675" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4675" s="0">
-        <v>3328</v>
+        <v>3376</v>
       </c>
       <c r="D4675" s="0">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row outlineLevel="0" r="4676">
       <c r="A4676" s="0">
-        <v>5688</v>
+        <v>5857</v>
       </c>
       <c r="B4676" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4676" s="0">
-        <v>3329</v>
+        <v>3378</v>
       </c>
       <c r="D4676" s="0">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row outlineLevel="0" r="4677">
       <c r="A4677" s="0">
-        <v>5689</v>
+        <v>5858</v>
       </c>
       <c r="B4677" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4677" s="0">
-        <v>3330</v>
+        <v>3384</v>
       </c>
       <c r="D4677" s="0">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row outlineLevel="0" r="4678">
       <c r="A4678" s="0">
-        <v>5690</v>
+        <v>5859</v>
       </c>
       <c r="B4678" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4678" s="0">
-        <v>3331</v>
+        <v>3387</v>
       </c>
       <c r="D4678" s="0">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row outlineLevel="0" r="4679">
       <c r="A4679" s="0">
-        <v>5691</v>
+        <v>5860</v>
       </c>
       <c r="B4679" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4679" s="0">
-        <v>3332</v>
+        <v>3388</v>
       </c>
       <c r="D4679" s="0">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row outlineLevel="0" r="4680">
       <c r="A4680" s="0">
-        <v>5692</v>
+        <v>5861</v>
       </c>
       <c r="B4680" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4680" s="0">
-        <v>3333</v>
+        <v>3368</v>
       </c>
       <c r="D4680" s="0">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row outlineLevel="0" r="4681">
       <c r="A4681" s="0">
-        <v>5693</v>
+        <v>5862</v>
       </c>
       <c r="B4681" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4681" s="0">
-        <v>3334</v>
+        <v>3390</v>
       </c>
       <c r="D4681" s="0">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="4682">
       <c r="A4682" s="0">
-        <v>5694</v>
+        <v>5863</v>
       </c>
       <c r="B4682" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4682" s="0">
-        <v>3335</v>
+        <v>3391</v>
       </c>
       <c r="D4682" s="0">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row outlineLevel="0" r="4683">
       <c r="A4683" s="0">
-        <v>5695</v>
+        <v>5864</v>
       </c>
       <c r="B4683" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4683" s="0">
-        <v>3336</v>
+        <v>3394</v>
       </c>
       <c r="D4683" s="0">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row outlineLevel="0" r="4684">
       <c r="A4684" s="0">
-        <v>5696</v>
+        <v>5865</v>
       </c>
       <c r="B4684" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4684" s="0">
-        <v>3337</v>
+        <v>3374</v>
       </c>
       <c r="D4684" s="0">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row outlineLevel="0" r="4685">
       <c r="A4685" s="0">
-        <v>5697</v>
+        <v>5866</v>
       </c>
       <c r="B4685" s="0">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C4685" s="0">
-        <v>3338</v>
+        <v>3396</v>
       </c>
       <c r="D4685" s="0">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="4686">
       <c r="A4686" s="0">
-        <v>5698</v>
+        <v>5867</v>
       </c>
       <c r="B4686" s="0">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C4686" s="0">
-        <v>3339</v>
+        <v>3398</v>
       </c>
       <c r="D4686" s="0">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row outlineLevel="0" r="4687">
       <c r="A4687" s="0">
-        <v>5699</v>
+        <v>5868</v>
       </c>
       <c r="B4687" s="0">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C4687" s="0">
-        <v>3340</v>
+        <v>3399</v>
       </c>
       <c r="D4687" s="0">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row outlineLevel="0" r="4688">
       <c r="A4688" s="0">
-        <v>5700</v>
+        <v>5869</v>
       </c>
       <c r="B4688" s="0">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C4688" s="0">
-        <v>3341</v>
+        <v>3400</v>
       </c>
       <c r="D4688" s="0">
-        <v>41</v>
+        <v>4</v>
       </c>
     </row>
     <row outlineLevel="0" r="4689">
       <c r="A4689" s="0">
-        <v>5701</v>
+        <v>5870</v>
       </c>
       <c r="B4689" s="0">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C4689" s="0">
-        <v>3342</v>
+        <v>3407</v>
       </c>
       <c r="D4689" s="0">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="4690">
       <c r="A4690" s="0">
-        <v>5702</v>
+        <v>5871</v>
       </c>
       <c r="B4690" s="0">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C4690" s="0">
-        <v>3343</v>
+        <v>3427</v>
       </c>
       <c r="D4690" s="0">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row outlineLevel="0" r="4691">
       <c r="A4691" s="0">
-        <v>5703</v>
+        <v>5872</v>
       </c>
       <c r="B4691" s="0">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C4691" s="0">
-        <v>3344</v>
+        <v>3426</v>
       </c>
       <c r="D4691" s="0">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="4692">
       <c r="A4692" s="0">
-        <v>5704</v>
+        <v>5873</v>
       </c>
       <c r="B4692" s="0">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C4692" s="0">
-        <v>3345</v>
+        <v>3405</v>
       </c>
       <c r="D4692" s="0">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row outlineLevel="0" r="4693">
       <c r="A4693" s="0">
-        <v>5705</v>
+        <v>5874</v>
       </c>
       <c r="B4693" s="0">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C4693" s="0">
-        <v>3346</v>
+        <v>3411</v>
       </c>
       <c r="D4693" s="0">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row outlineLevel="0" r="4694">
       <c r="A4694" s="0">
-        <v>5706</v>
+        <v>5875</v>
       </c>
       <c r="B4694" s="0">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C4694" s="0">
-        <v>3347</v>
+        <v>3409</v>
       </c>
       <c r="D4694" s="0">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row outlineLevel="0" r="4695">
       <c r="A4695" s="0">
-        <v>5707</v>
+        <v>5876</v>
       </c>
       <c r="B4695" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4695" s="0">
-        <v>3302</v>
+        <v>3430</v>
       </c>
       <c r="D4695" s="0">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row outlineLevel="0" r="4696">
       <c r="A4696" s="0">
-        <v>5708</v>
+        <v>5877</v>
       </c>
       <c r="B4696" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4696" s="0">
-        <v>3304</v>
+        <v>3436</v>
       </c>
       <c r="D4696" s="0">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row outlineLevel="0" r="4697">
       <c r="A4697" s="0">
-        <v>5709</v>
+        <v>5878</v>
       </c>
       <c r="B4697" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4697" s="0">
-        <v>3305</v>
+        <v>3413</v>
       </c>
       <c r="D4697" s="0">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row outlineLevel="0" r="4698">
       <c r="A4698" s="0">
-        <v>5710</v>
+        <v>5879</v>
       </c>
       <c r="B4698" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4698" s="0">
-        <v>3306</v>
+        <v>3420</v>
       </c>
       <c r="D4698" s="0">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row outlineLevel="0" r="4699">
       <c r="A4699" s="0">
-        <v>5711</v>
+        <v>5880</v>
       </c>
       <c r="B4699" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4699" s="0">
-        <v>3313</v>
+        <v>3419</v>
       </c>
       <c r="D4699" s="0">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row outlineLevel="0" r="4700">
       <c r="A4700" s="0">
-        <v>5712</v>
+        <v>5881</v>
       </c>
       <c r="B4700" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4700" s="0">
-        <v>3333</v>
+        <v>3423</v>
       </c>
       <c r="D4700" s="0">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row outlineLevel="0" r="4701">
       <c r="A4701" s="0">
-        <v>5713</v>
+        <v>5882</v>
       </c>
       <c r="B4701" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4701" s="0">
-        <v>3332</v>
+        <v>3425</v>
       </c>
       <c r="D4701" s="0">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row outlineLevel="0" r="4702">
       <c r="A4702" s="0">
-        <v>5714</v>
+        <v>5883</v>
       </c>
       <c r="B4702" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4702" s="0">
-        <v>3311</v>
+        <v>3431</v>
       </c>
       <c r="D4702" s="0">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row outlineLevel="0" r="4703">
       <c r="A4703" s="0">
-        <v>5715</v>
+        <v>5884</v>
       </c>
       <c r="B4703" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4703" s="0">
-        <v>3317</v>
+        <v>3434</v>
       </c>
       <c r="D4703" s="0">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row outlineLevel="0" r="4704">
       <c r="A4704" s="0">
-        <v>5716</v>
+        <v>5885</v>
       </c>
       <c r="B4704" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4704" s="0">
-        <v>3315</v>
+        <v>3435</v>
       </c>
       <c r="D4704" s="0">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row outlineLevel="0" r="4705">
       <c r="A4705" s="0">
-        <v>5717</v>
+        <v>5886</v>
       </c>
       <c r="B4705" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4705" s="0">
-        <v>3336</v>
+        <v>3415</v>
       </c>
       <c r="D4705" s="0">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row outlineLevel="0" r="4706">
       <c r="A4706" s="0">
-        <v>5718</v>
+        <v>5887</v>
       </c>
       <c r="B4706" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4706" s="0">
-        <v>3342</v>
+        <v>3437</v>
       </c>
       <c r="D4706" s="0">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="4707">
       <c r="A4707" s="0">
-        <v>5719</v>
+        <v>5888</v>
       </c>
       <c r="B4707" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4707" s="0">
-        <v>3319</v>
+        <v>3438</v>
       </c>
       <c r="D4707" s="0">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row outlineLevel="0" r="4708">
       <c r="A4708" s="0">
-        <v>5720</v>
+        <v>5889</v>
       </c>
       <c r="B4708" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4708" s="0">
-        <v>3326</v>
+        <v>3441</v>
       </c>
       <c r="D4708" s="0">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row outlineLevel="0" r="4709">
       <c r="A4709" s="0">
-        <v>5721</v>
+        <v>5890</v>
       </c>
       <c r="B4709" s="0">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C4709" s="0">
-        <v>3325</v>
+        <v>3421</v>
       </c>
       <c r="D4709" s="0">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row outlineLevel="0" r="4710">
       <c r="A4710" s="0">
-        <v>5722</v>
+        <v>5891</v>
       </c>
       <c r="B4710" s="0">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C4710" s="0">
-        <v>3329</v>
+        <v>3442</v>
       </c>
       <c r="D4710" s="0">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="4711">
       <c r="A4711" s="0">
-        <v>5723</v>
+        <v>5892</v>
       </c>
       <c r="B4711" s="0">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C4711" s="0">
-        <v>3331</v>
+        <v>3443</v>
       </c>
       <c r="D4711" s="0">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row outlineLevel="0" r="4712">
       <c r="A4712" s="0">
-        <v>5724</v>
+        <v>5893</v>
       </c>
       <c r="B4712" s="0">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C4712" s="0">
-        <v>3337</v>
+        <v>3444</v>
       </c>
       <c r="D4712" s="0">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row outlineLevel="0" r="4713">
       <c r="A4713" s="0">
-        <v>5725</v>
+        <v>5894</v>
       </c>
       <c r="B4713" s="0">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C4713" s="0">
-        <v>3340</v>
+        <v>3445</v>
       </c>
       <c r="D4713" s="0">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row outlineLevel="0" r="4714">
       <c r="A4714" s="0">
-        <v>5726</v>
+        <v>5895</v>
       </c>
       <c r="B4714" s="0">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C4714" s="0">
-        <v>3341</v>
+        <v>3446</v>
       </c>
       <c r="D4714" s="0">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="4715">
       <c r="A4715" s="0">
-        <v>5727</v>
+        <v>5896</v>
       </c>
       <c r="B4715" s="0">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C4715" s="0">
-        <v>3321</v>
+        <v>3447</v>
       </c>
       <c r="D4715" s="0">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row outlineLevel="0" r="4716">
       <c r="A4716" s="0">
-        <v>5728</v>
+        <v>5897</v>
       </c>
       <c r="B4716" s="0">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C4716" s="0">
-        <v>3343</v>
+        <v>3448</v>
       </c>
       <c r="D4716" s="0">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="4717">
       <c r="A4717" s="0">
-        <v>5729</v>
+        <v>5898</v>
       </c>
       <c r="B4717" s="0">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C4717" s="0">
-        <v>3344</v>
+        <v>3449</v>
       </c>
       <c r="D4717" s="0">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row outlineLevel="0" r="4718">
       <c r="A4718" s="0">
-        <v>5730</v>
+        <v>5899</v>
       </c>
       <c r="B4718" s="0">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C4718" s="0">
-        <v>3347</v>
+        <v>3450</v>
       </c>
       <c r="D4718" s="0">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row outlineLevel="0" r="4719">
       <c r="A4719" s="0">
+        <v>5900</v>
+      </c>
+      <c r="B4719" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4719" s="0">
+        <v>3451</v>
+      </c>
+      <c r="D4719" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4720">
+      <c r="A4720" s="0">
+        <v>5901</v>
+      </c>
+      <c r="B4720" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4720" s="0">
+        <v>3452</v>
+      </c>
+      <c r="D4720" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4721">
+      <c r="A4721" s="0">
+        <v>5902</v>
+      </c>
+      <c r="B4721" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4721" s="0">
+        <v>3453</v>
+      </c>
+      <c r="D4721" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4722">
+      <c r="A4722" s="0">
+        <v>5903</v>
+      </c>
+      <c r="B4722" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4722" s="0">
+        <v>3454</v>
+      </c>
+      <c r="D4722" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4723">
+      <c r="A4723" s="0">
+        <v>5578</v>
+      </c>
+      <c r="B4723" s="0">
+        <v>110</v>
+      </c>
+      <c r="C4723" s="0">
+        <v>3248</v>
+      </c>
+      <c r="D4723" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4724">
+      <c r="A4724" s="0">
+        <v>5579</v>
+      </c>
+      <c r="B4724" s="0">
+        <v>142</v>
+      </c>
+      <c r="C4724" s="0">
+        <v>3248</v>
+      </c>
+      <c r="D4724" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4725">
+      <c r="A4725" s="0">
+        <v>5580</v>
+      </c>
+      <c r="B4725" s="0">
+        <v>110</v>
+      </c>
+      <c r="C4725" s="0">
+        <v>3249</v>
+      </c>
+      <c r="D4725" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4726">
+      <c r="A4726" s="0">
+        <v>5581</v>
+      </c>
+      <c r="B4726" s="0">
+        <v>142</v>
+      </c>
+      <c r="C4726" s="0">
+        <v>3249</v>
+      </c>
+      <c r="D4726" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4727">
+      <c r="A4727" s="0">
+        <v>5582</v>
+      </c>
+      <c r="B4727" s="0">
+        <v>110</v>
+      </c>
+      <c r="C4727" s="0">
+        <v>3250</v>
+      </c>
+      <c r="D4727" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4728">
+      <c r="A4728" s="0">
+        <v>5583</v>
+      </c>
+      <c r="B4728" s="0">
+        <v>142</v>
+      </c>
+      <c r="C4728" s="0">
+        <v>3250</v>
+      </c>
+      <c r="D4728" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4729">
+      <c r="A4729" s="0">
+        <v>5584</v>
+      </c>
+      <c r="B4729" s="0">
+        <v>110</v>
+      </c>
+      <c r="C4729" s="0">
+        <v>3251</v>
+      </c>
+      <c r="D4729" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4730">
+      <c r="A4730" s="0">
+        <v>5585</v>
+      </c>
+      <c r="B4730" s="0">
+        <v>110</v>
+      </c>
+      <c r="C4730" s="0">
+        <v>3252</v>
+      </c>
+      <c r="D4730" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4731">
+      <c r="A4731" s="0">
+        <v>5586</v>
+      </c>
+      <c r="B4731" s="0">
+        <v>110</v>
+      </c>
+      <c r="C4731" s="0">
+        <v>3253</v>
+      </c>
+      <c r="D4731" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4732">
+      <c r="A4732" s="0">
+        <v>5587</v>
+      </c>
+      <c r="B4732" s="0">
+        <v>142</v>
+      </c>
+      <c r="C4732" s="0">
+        <v>3253</v>
+      </c>
+      <c r="D4732" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4733">
+      <c r="A4733" s="0">
+        <v>5588</v>
+      </c>
+      <c r="B4733" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4733" s="0">
+        <v>3254</v>
+      </c>
+      <c r="D4733" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4734">
+      <c r="A4734" s="0">
+        <v>5589</v>
+      </c>
+      <c r="B4734" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4734" s="0">
+        <v>3255</v>
+      </c>
+      <c r="D4734" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4735">
+      <c r="A4735" s="0">
+        <v>5590</v>
+      </c>
+      <c r="B4735" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4735" s="0">
+        <v>3256</v>
+      </c>
+      <c r="D4735" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4736">
+      <c r="A4736" s="0">
+        <v>5591</v>
+      </c>
+      <c r="B4736" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4736" s="0">
+        <v>3257</v>
+      </c>
+      <c r="D4736" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4737">
+      <c r="A4737" s="0">
+        <v>5592</v>
+      </c>
+      <c r="B4737" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4737" s="0">
+        <v>3258</v>
+      </c>
+      <c r="D4737" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4738">
+      <c r="A4738" s="0">
+        <v>5593</v>
+      </c>
+      <c r="B4738" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4738" s="0">
+        <v>3259</v>
+      </c>
+      <c r="D4738" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4739">
+      <c r="A4739" s="0">
+        <v>5594</v>
+      </c>
+      <c r="B4739" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4739" s="0">
+        <v>3260</v>
+      </c>
+      <c r="D4739" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4740">
+      <c r="A4740" s="0">
+        <v>5595</v>
+      </c>
+      <c r="B4740" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4740" s="0">
+        <v>3261</v>
+      </c>
+      <c r="D4740" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4741">
+      <c r="A4741" s="0">
+        <v>5596</v>
+      </c>
+      <c r="B4741" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4741" s="0">
+        <v>3262</v>
+      </c>
+      <c r="D4741" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4742">
+      <c r="A4742" s="0">
+        <v>5597</v>
+      </c>
+      <c r="B4742" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4742" s="0">
+        <v>3263</v>
+      </c>
+      <c r="D4742" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4743">
+      <c r="A4743" s="0">
+        <v>5598</v>
+      </c>
+      <c r="B4743" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4743" s="0">
+        <v>3264</v>
+      </c>
+      <c r="D4743" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4744">
+      <c r="A4744" s="0">
+        <v>5599</v>
+      </c>
+      <c r="B4744" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4744" s="0">
+        <v>3265</v>
+      </c>
+      <c r="D4744" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4745">
+      <c r="A4745" s="0">
+        <v>5600</v>
+      </c>
+      <c r="B4745" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4745" s="0">
+        <v>3266</v>
+      </c>
+      <c r="D4745" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4746">
+      <c r="A4746" s="0">
+        <v>5601</v>
+      </c>
+      <c r="B4746" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4746" s="0">
+        <v>3267</v>
+      </c>
+      <c r="D4746" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4747">
+      <c r="A4747" s="0">
+        <v>5602</v>
+      </c>
+      <c r="B4747" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4747" s="0">
+        <v>3268</v>
+      </c>
+      <c r="D4747" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4748">
+      <c r="A4748" s="0">
+        <v>5603</v>
+      </c>
+      <c r="B4748" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4748" s="0">
+        <v>3269</v>
+      </c>
+      <c r="D4748" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4749">
+      <c r="A4749" s="0">
+        <v>5604</v>
+      </c>
+      <c r="B4749" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4749" s="0">
+        <v>3270</v>
+      </c>
+      <c r="D4749" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4750">
+      <c r="A4750" s="0">
+        <v>5605</v>
+      </c>
+      <c r="B4750" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4750" s="0">
+        <v>3271</v>
+      </c>
+      <c r="D4750" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4751">
+      <c r="A4751" s="0">
+        <v>5606</v>
+      </c>
+      <c r="B4751" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4751" s="0">
+        <v>3272</v>
+      </c>
+      <c r="D4751" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4752">
+      <c r="A4752" s="0">
+        <v>5607</v>
+      </c>
+      <c r="B4752" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4752" s="0">
+        <v>3273</v>
+      </c>
+      <c r="D4752" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4753">
+      <c r="A4753" s="0">
+        <v>5608</v>
+      </c>
+      <c r="B4753" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4753" s="0">
+        <v>3274</v>
+      </c>
+      <c r="D4753" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4754">
+      <c r="A4754" s="0">
+        <v>5609</v>
+      </c>
+      <c r="B4754" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4754" s="0">
+        <v>3275</v>
+      </c>
+      <c r="D4754" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4755">
+      <c r="A4755" s="0">
+        <v>5610</v>
+      </c>
+      <c r="B4755" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4755" s="0">
+        <v>3276</v>
+      </c>
+      <c r="D4755" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4756">
+      <c r="A4756" s="0">
+        <v>5611</v>
+      </c>
+      <c r="B4756" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4756" s="0">
+        <v>3277</v>
+      </c>
+      <c r="D4756" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4757">
+      <c r="A4757" s="0">
+        <v>5612</v>
+      </c>
+      <c r="B4757" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4757" s="0">
+        <v>3278</v>
+      </c>
+      <c r="D4757" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4758">
+      <c r="A4758" s="0">
+        <v>5613</v>
+      </c>
+      <c r="B4758" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4758" s="0">
+        <v>3279</v>
+      </c>
+      <c r="D4758" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4759">
+      <c r="A4759" s="0">
+        <v>5614</v>
+      </c>
+      <c r="B4759" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4759" s="0">
+        <v>3280</v>
+      </c>
+      <c r="D4759" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4760">
+      <c r="A4760" s="0">
+        <v>5615</v>
+      </c>
+      <c r="B4760" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4760" s="0">
+        <v>3281</v>
+      </c>
+      <c r="D4760" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4761">
+      <c r="A4761" s="0">
+        <v>5616</v>
+      </c>
+      <c r="B4761" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4761" s="0">
+        <v>3282</v>
+      </c>
+      <c r="D4761" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4762">
+      <c r="A4762" s="0">
+        <v>5617</v>
+      </c>
+      <c r="B4762" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4762" s="0">
+        <v>3283</v>
+      </c>
+      <c r="D4762" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4763">
+      <c r="A4763" s="0">
+        <v>5618</v>
+      </c>
+      <c r="B4763" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4763" s="0">
+        <v>3284</v>
+      </c>
+      <c r="D4763" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4764">
+      <c r="A4764" s="0">
+        <v>5619</v>
+      </c>
+      <c r="B4764" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4764" s="0">
+        <v>3285</v>
+      </c>
+      <c r="D4764" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4765">
+      <c r="A4765" s="0">
+        <v>5620</v>
+      </c>
+      <c r="B4765" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4765" s="0">
+        <v>3286</v>
+      </c>
+      <c r="D4765" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4766">
+      <c r="A4766" s="0">
+        <v>5621</v>
+      </c>
+      <c r="B4766" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4766" s="0">
+        <v>3287</v>
+      </c>
+      <c r="D4766" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4767">
+      <c r="A4767" s="0">
+        <v>5622</v>
+      </c>
+      <c r="B4767" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4767" s="0">
+        <v>3288</v>
+      </c>
+      <c r="D4767" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4768">
+      <c r="A4768" s="0">
+        <v>5623</v>
+      </c>
+      <c r="B4768" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4768" s="0">
+        <v>3289</v>
+      </c>
+      <c r="D4768" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4769">
+      <c r="A4769" s="0">
+        <v>5624</v>
+      </c>
+      <c r="B4769" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4769" s="0">
+        <v>3290</v>
+      </c>
+      <c r="D4769" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4770">
+      <c r="A4770" s="0">
+        <v>5625</v>
+      </c>
+      <c r="B4770" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4770" s="0">
+        <v>3291</v>
+      </c>
+      <c r="D4770" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4771">
+      <c r="A4771" s="0">
+        <v>5626</v>
+      </c>
+      <c r="B4771" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4771" s="0">
+        <v>3292</v>
+      </c>
+      <c r="D4771" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4772">
+      <c r="A4772" s="0">
+        <v>5627</v>
+      </c>
+      <c r="B4772" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4772" s="0">
+        <v>3293</v>
+      </c>
+      <c r="D4772" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4773">
+      <c r="A4773" s="0">
+        <v>5628</v>
+      </c>
+      <c r="B4773" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4773" s="0">
+        <v>3294</v>
+      </c>
+      <c r="D4773" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4774">
+      <c r="A4774" s="0">
+        <v>5629</v>
+      </c>
+      <c r="B4774" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4774" s="0">
+        <v>3295</v>
+      </c>
+      <c r="D4774" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4775">
+      <c r="A4775" s="0">
+        <v>5630</v>
+      </c>
+      <c r="B4775" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4775" s="0">
+        <v>3296</v>
+      </c>
+      <c r="D4775" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4776">
+      <c r="A4776" s="0">
+        <v>5631</v>
+      </c>
+      <c r="B4776" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4776" s="0">
+        <v>3297</v>
+      </c>
+      <c r="D4776" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4777">
+      <c r="A4777" s="0">
+        <v>5632</v>
+      </c>
+      <c r="B4777" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4777" s="0">
+        <v>3298</v>
+      </c>
+      <c r="D4777" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4778">
+      <c r="A4778" s="0">
+        <v>5633</v>
+      </c>
+      <c r="B4778" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4778" s="0">
+        <v>3299</v>
+      </c>
+      <c r="D4778" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4779">
+      <c r="A4779" s="0">
+        <v>5634</v>
+      </c>
+      <c r="B4779" s="0">
+        <v>162</v>
+      </c>
+      <c r="C4779" s="0">
+        <v>3300</v>
+      </c>
+      <c r="D4779" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4780">
+      <c r="A4780" s="0">
+        <v>5635</v>
+      </c>
+      <c r="B4780" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4780" s="0">
+        <v>3255</v>
+      </c>
+      <c r="D4780" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4781">
+      <c r="A4781" s="0">
+        <v>5636</v>
+      </c>
+      <c r="B4781" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4781" s="0">
+        <v>3257</v>
+      </c>
+      <c r="D4781" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4782">
+      <c r="A4782" s="0">
+        <v>5637</v>
+      </c>
+      <c r="B4782" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4782" s="0">
+        <v>3258</v>
+      </c>
+      <c r="D4782" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4783">
+      <c r="A4783" s="0">
+        <v>5638</v>
+      </c>
+      <c r="B4783" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4783" s="0">
+        <v>3259</v>
+      </c>
+      <c r="D4783" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4784">
+      <c r="A4784" s="0">
+        <v>5639</v>
+      </c>
+      <c r="B4784" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4784" s="0">
+        <v>3266</v>
+      </c>
+      <c r="D4784" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4785">
+      <c r="A4785" s="0">
+        <v>5640</v>
+      </c>
+      <c r="B4785" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4785" s="0">
+        <v>3286</v>
+      </c>
+      <c r="D4785" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4786">
+      <c r="A4786" s="0">
+        <v>5641</v>
+      </c>
+      <c r="B4786" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4786" s="0">
+        <v>3285</v>
+      </c>
+      <c r="D4786" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4787">
+      <c r="A4787" s="0">
+        <v>5642</v>
+      </c>
+      <c r="B4787" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4787" s="0">
+        <v>3264</v>
+      </c>
+      <c r="D4787" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4788">
+      <c r="A4788" s="0">
+        <v>5643</v>
+      </c>
+      <c r="B4788" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4788" s="0">
+        <v>3270</v>
+      </c>
+      <c r="D4788" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4789">
+      <c r="A4789" s="0">
+        <v>5644</v>
+      </c>
+      <c r="B4789" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4789" s="0">
+        <v>3268</v>
+      </c>
+      <c r="D4789" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4790">
+      <c r="A4790" s="0">
+        <v>5645</v>
+      </c>
+      <c r="B4790" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4790" s="0">
+        <v>3289</v>
+      </c>
+      <c r="D4790" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4791">
+      <c r="A4791" s="0">
+        <v>5646</v>
+      </c>
+      <c r="B4791" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4791" s="0">
+        <v>3295</v>
+      </c>
+      <c r="D4791" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4792">
+      <c r="A4792" s="0">
+        <v>5647</v>
+      </c>
+      <c r="B4792" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4792" s="0">
+        <v>3272</v>
+      </c>
+      <c r="D4792" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4793">
+      <c r="A4793" s="0">
+        <v>5648</v>
+      </c>
+      <c r="B4793" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4793" s="0">
+        <v>3279</v>
+      </c>
+      <c r="D4793" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4794">
+      <c r="A4794" s="0">
+        <v>5649</v>
+      </c>
+      <c r="B4794" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4794" s="0">
+        <v>3278</v>
+      </c>
+      <c r="D4794" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4795">
+      <c r="A4795" s="0">
+        <v>5650</v>
+      </c>
+      <c r="B4795" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4795" s="0">
+        <v>3282</v>
+      </c>
+      <c r="D4795" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4796">
+      <c r="A4796" s="0">
+        <v>5651</v>
+      </c>
+      <c r="B4796" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4796" s="0">
+        <v>3284</v>
+      </c>
+      <c r="D4796" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4797">
+      <c r="A4797" s="0">
+        <v>5652</v>
+      </c>
+      <c r="B4797" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4797" s="0">
+        <v>3290</v>
+      </c>
+      <c r="D4797" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4798">
+      <c r="A4798" s="0">
+        <v>5653</v>
+      </c>
+      <c r="B4798" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4798" s="0">
+        <v>3293</v>
+      </c>
+      <c r="D4798" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4799">
+      <c r="A4799" s="0">
+        <v>5654</v>
+      </c>
+      <c r="B4799" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4799" s="0">
+        <v>3294</v>
+      </c>
+      <c r="D4799" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4800">
+      <c r="A4800" s="0">
+        <v>5655</v>
+      </c>
+      <c r="B4800" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4800" s="0">
+        <v>3274</v>
+      </c>
+      <c r="D4800" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4801">
+      <c r="A4801" s="0">
+        <v>5656</v>
+      </c>
+      <c r="B4801" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4801" s="0">
+        <v>3296</v>
+      </c>
+      <c r="D4801" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4802">
+      <c r="A4802" s="0">
+        <v>5657</v>
+      </c>
+      <c r="B4802" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4802" s="0">
+        <v>3297</v>
+      </c>
+      <c r="D4802" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4803">
+      <c r="A4803" s="0">
+        <v>5658</v>
+      </c>
+      <c r="B4803" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4803" s="0">
+        <v>3300</v>
+      </c>
+      <c r="D4803" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4804">
+      <c r="A4804" s="0">
+        <v>5659</v>
+      </c>
+      <c r="B4804" s="0">
+        <v>164</v>
+      </c>
+      <c r="C4804" s="0">
+        <v>3280</v>
+      </c>
+      <c r="D4804" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4805">
+      <c r="A4805" s="0">
+        <v>5660</v>
+      </c>
+      <c r="B4805" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4805" s="0">
+        <v>3301</v>
+      </c>
+      <c r="D4805" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4806">
+      <c r="A4806" s="0">
+        <v>5661</v>
+      </c>
+      <c r="B4806" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4806" s="0">
+        <v>3302</v>
+      </c>
+      <c r="D4806" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4807">
+      <c r="A4807" s="0">
+        <v>5662</v>
+      </c>
+      <c r="B4807" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4807" s="0">
+        <v>3303</v>
+      </c>
+      <c r="D4807" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4808">
+      <c r="A4808" s="0">
+        <v>5663</v>
+      </c>
+      <c r="B4808" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4808" s="0">
+        <v>3304</v>
+      </c>
+      <c r="D4808" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4809">
+      <c r="A4809" s="0">
+        <v>5664</v>
+      </c>
+      <c r="B4809" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4809" s="0">
+        <v>3305</v>
+      </c>
+      <c r="D4809" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4810">
+      <c r="A4810" s="0">
+        <v>5665</v>
+      </c>
+      <c r="B4810" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4810" s="0">
+        <v>3306</v>
+      </c>
+      <c r="D4810" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4811">
+      <c r="A4811" s="0">
+        <v>5666</v>
+      </c>
+      <c r="B4811" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4811" s="0">
+        <v>3307</v>
+      </c>
+      <c r="D4811" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4812">
+      <c r="A4812" s="0">
+        <v>5667</v>
+      </c>
+      <c r="B4812" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4812" s="0">
+        <v>3308</v>
+      </c>
+      <c r="D4812" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4813">
+      <c r="A4813" s="0">
+        <v>5668</v>
+      </c>
+      <c r="B4813" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4813" s="0">
+        <v>3309</v>
+      </c>
+      <c r="D4813" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4814">
+      <c r="A4814" s="0">
+        <v>5669</v>
+      </c>
+      <c r="B4814" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4814" s="0">
+        <v>3310</v>
+      </c>
+      <c r="D4814" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4815">
+      <c r="A4815" s="0">
+        <v>5670</v>
+      </c>
+      <c r="B4815" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4815" s="0">
+        <v>3311</v>
+      </c>
+      <c r="D4815" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4816">
+      <c r="A4816" s="0">
+        <v>5671</v>
+      </c>
+      <c r="B4816" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4816" s="0">
+        <v>3312</v>
+      </c>
+      <c r="D4816" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4817">
+      <c r="A4817" s="0">
+        <v>5672</v>
+      </c>
+      <c r="B4817" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4817" s="0">
+        <v>3313</v>
+      </c>
+      <c r="D4817" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4818">
+      <c r="A4818" s="0">
+        <v>5673</v>
+      </c>
+      <c r="B4818" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4818" s="0">
+        <v>3314</v>
+      </c>
+      <c r="D4818" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4819">
+      <c r="A4819" s="0">
+        <v>5674</v>
+      </c>
+      <c r="B4819" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4819" s="0">
+        <v>3315</v>
+      </c>
+      <c r="D4819" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4820">
+      <c r="A4820" s="0">
+        <v>5675</v>
+      </c>
+      <c r="B4820" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4820" s="0">
+        <v>3316</v>
+      </c>
+      <c r="D4820" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4821">
+      <c r="A4821" s="0">
+        <v>5676</v>
+      </c>
+      <c r="B4821" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4821" s="0">
+        <v>3317</v>
+      </c>
+      <c r="D4821" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4822">
+      <c r="A4822" s="0">
+        <v>5677</v>
+      </c>
+      <c r="B4822" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4822" s="0">
+        <v>3318</v>
+      </c>
+      <c r="D4822" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4823">
+      <c r="A4823" s="0">
+        <v>5678</v>
+      </c>
+      <c r="B4823" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4823" s="0">
+        <v>3319</v>
+      </c>
+      <c r="D4823" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4824">
+      <c r="A4824" s="0">
+        <v>5679</v>
+      </c>
+      <c r="B4824" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4824" s="0">
+        <v>3320</v>
+      </c>
+      <c r="D4824" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4825">
+      <c r="A4825" s="0">
+        <v>5680</v>
+      </c>
+      <c r="B4825" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4825" s="0">
+        <v>3321</v>
+      </c>
+      <c r="D4825" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4826">
+      <c r="A4826" s="0">
+        <v>5681</v>
+      </c>
+      <c r="B4826" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4826" s="0">
+        <v>3322</v>
+      </c>
+      <c r="D4826" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4827">
+      <c r="A4827" s="0">
+        <v>5682</v>
+      </c>
+      <c r="B4827" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4827" s="0">
+        <v>3323</v>
+      </c>
+      <c r="D4827" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4828">
+      <c r="A4828" s="0">
+        <v>5683</v>
+      </c>
+      <c r="B4828" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4828" s="0">
+        <v>3324</v>
+      </c>
+      <c r="D4828" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4829">
+      <c r="A4829" s="0">
+        <v>5684</v>
+      </c>
+      <c r="B4829" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4829" s="0">
+        <v>3325</v>
+      </c>
+      <c r="D4829" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4830">
+      <c r="A4830" s="0">
+        <v>5685</v>
+      </c>
+      <c r="B4830" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4830" s="0">
+        <v>3326</v>
+      </c>
+      <c r="D4830" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4831">
+      <c r="A4831" s="0">
+        <v>5686</v>
+      </c>
+      <c r="B4831" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4831" s="0">
+        <v>3327</v>
+      </c>
+      <c r="D4831" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4832">
+      <c r="A4832" s="0">
+        <v>5687</v>
+      </c>
+      <c r="B4832" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4832" s="0">
+        <v>3328</v>
+      </c>
+      <c r="D4832" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4833">
+      <c r="A4833" s="0">
+        <v>5688</v>
+      </c>
+      <c r="B4833" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4833" s="0">
+        <v>3329</v>
+      </c>
+      <c r="D4833" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4834">
+      <c r="A4834" s="0">
+        <v>5689</v>
+      </c>
+      <c r="B4834" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4834" s="0">
+        <v>3330</v>
+      </c>
+      <c r="D4834" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4835">
+      <c r="A4835" s="0">
+        <v>5690</v>
+      </c>
+      <c r="B4835" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4835" s="0">
+        <v>3331</v>
+      </c>
+      <c r="D4835" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4836">
+      <c r="A4836" s="0">
+        <v>5691</v>
+      </c>
+      <c r="B4836" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4836" s="0">
+        <v>3332</v>
+      </c>
+      <c r="D4836" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4837">
+      <c r="A4837" s="0">
+        <v>5692</v>
+      </c>
+      <c r="B4837" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4837" s="0">
+        <v>3333</v>
+      </c>
+      <c r="D4837" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4838">
+      <c r="A4838" s="0">
+        <v>5693</v>
+      </c>
+      <c r="B4838" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4838" s="0">
+        <v>3334</v>
+      </c>
+      <c r="D4838" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4839">
+      <c r="A4839" s="0">
+        <v>5694</v>
+      </c>
+      <c r="B4839" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4839" s="0">
+        <v>3335</v>
+      </c>
+      <c r="D4839" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4840">
+      <c r="A4840" s="0">
+        <v>5695</v>
+      </c>
+      <c r="B4840" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4840" s="0">
+        <v>3336</v>
+      </c>
+      <c r="D4840" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4841">
+      <c r="A4841" s="0">
+        <v>5696</v>
+      </c>
+      <c r="B4841" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4841" s="0">
+        <v>3337</v>
+      </c>
+      <c r="D4841" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4842">
+      <c r="A4842" s="0">
+        <v>5697</v>
+      </c>
+      <c r="B4842" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4842" s="0">
+        <v>3338</v>
+      </c>
+      <c r="D4842" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4843">
+      <c r="A4843" s="0">
+        <v>5698</v>
+      </c>
+      <c r="B4843" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4843" s="0">
+        <v>3339</v>
+      </c>
+      <c r="D4843" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4844">
+      <c r="A4844" s="0">
+        <v>5699</v>
+      </c>
+      <c r="B4844" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4844" s="0">
+        <v>3340</v>
+      </c>
+      <c r="D4844" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4845">
+      <c r="A4845" s="0">
+        <v>5700</v>
+      </c>
+      <c r="B4845" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4845" s="0">
+        <v>3341</v>
+      </c>
+      <c r="D4845" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4846">
+      <c r="A4846" s="0">
+        <v>5701</v>
+      </c>
+      <c r="B4846" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4846" s="0">
+        <v>3342</v>
+      </c>
+      <c r="D4846" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4847">
+      <c r="A4847" s="0">
+        <v>5702</v>
+      </c>
+      <c r="B4847" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4847" s="0">
+        <v>3343</v>
+      </c>
+      <c r="D4847" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4848">
+      <c r="A4848" s="0">
+        <v>5703</v>
+      </c>
+      <c r="B4848" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4848" s="0">
+        <v>3344</v>
+      </c>
+      <c r="D4848" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4849">
+      <c r="A4849" s="0">
+        <v>5704</v>
+      </c>
+      <c r="B4849" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4849" s="0">
+        <v>3345</v>
+      </c>
+      <c r="D4849" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4850">
+      <c r="A4850" s="0">
+        <v>5705</v>
+      </c>
+      <c r="B4850" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4850" s="0">
+        <v>3346</v>
+      </c>
+      <c r="D4850" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4851">
+      <c r="A4851" s="0">
+        <v>5706</v>
+      </c>
+      <c r="B4851" s="0">
+        <v>163</v>
+      </c>
+      <c r="C4851" s="0">
+        <v>3347</v>
+      </c>
+      <c r="D4851" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4852">
+      <c r="A4852" s="0">
+        <v>5707</v>
+      </c>
+      <c r="B4852" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4852" s="0">
+        <v>3302</v>
+      </c>
+      <c r="D4852" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4853">
+      <c r="A4853" s="0">
+        <v>5708</v>
+      </c>
+      <c r="B4853" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4853" s="0">
+        <v>3304</v>
+      </c>
+      <c r="D4853" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4854">
+      <c r="A4854" s="0">
+        <v>5709</v>
+      </c>
+      <c r="B4854" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4854" s="0">
+        <v>3305</v>
+      </c>
+      <c r="D4854" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4855">
+      <c r="A4855" s="0">
+        <v>5710</v>
+      </c>
+      <c r="B4855" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4855" s="0">
+        <v>3306</v>
+      </c>
+      <c r="D4855" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4856">
+      <c r="A4856" s="0">
+        <v>5711</v>
+      </c>
+      <c r="B4856" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4856" s="0">
+        <v>3313</v>
+      </c>
+      <c r="D4856" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4857">
+      <c r="A4857" s="0">
+        <v>5712</v>
+      </c>
+      <c r="B4857" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4857" s="0">
+        <v>3333</v>
+      </c>
+      <c r="D4857" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4858">
+      <c r="A4858" s="0">
+        <v>5713</v>
+      </c>
+      <c r="B4858" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4858" s="0">
+        <v>3332</v>
+      </c>
+      <c r="D4858" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4859">
+      <c r="A4859" s="0">
+        <v>5714</v>
+      </c>
+      <c r="B4859" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4859" s="0">
+        <v>3311</v>
+      </c>
+      <c r="D4859" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4860">
+      <c r="A4860" s="0">
+        <v>5715</v>
+      </c>
+      <c r="B4860" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4860" s="0">
+        <v>3317</v>
+      </c>
+      <c r="D4860" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4861">
+      <c r="A4861" s="0">
+        <v>5716</v>
+      </c>
+      <c r="B4861" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4861" s="0">
+        <v>3315</v>
+      </c>
+      <c r="D4861" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4862">
+      <c r="A4862" s="0">
+        <v>5717</v>
+      </c>
+      <c r="B4862" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4862" s="0">
+        <v>3336</v>
+      </c>
+      <c r="D4862" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4863">
+      <c r="A4863" s="0">
+        <v>5718</v>
+      </c>
+      <c r="B4863" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4863" s="0">
+        <v>3342</v>
+      </c>
+      <c r="D4863" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4864">
+      <c r="A4864" s="0">
+        <v>5719</v>
+      </c>
+      <c r="B4864" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4864" s="0">
+        <v>3319</v>
+      </c>
+      <c r="D4864" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4865">
+      <c r="A4865" s="0">
+        <v>5720</v>
+      </c>
+      <c r="B4865" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4865" s="0">
+        <v>3326</v>
+      </c>
+      <c r="D4865" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4866">
+      <c r="A4866" s="0">
+        <v>5721</v>
+      </c>
+      <c r="B4866" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4866" s="0">
+        <v>3325</v>
+      </c>
+      <c r="D4866" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4867">
+      <c r="A4867" s="0">
+        <v>5722</v>
+      </c>
+      <c r="B4867" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4867" s="0">
+        <v>3329</v>
+      </c>
+      <c r="D4867" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4868">
+      <c r="A4868" s="0">
+        <v>5723</v>
+      </c>
+      <c r="B4868" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4868" s="0">
+        <v>3331</v>
+      </c>
+      <c r="D4868" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4869">
+      <c r="A4869" s="0">
+        <v>5724</v>
+      </c>
+      <c r="B4869" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4869" s="0">
+        <v>3337</v>
+      </c>
+      <c r="D4869" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4870">
+      <c r="A4870" s="0">
+        <v>5725</v>
+      </c>
+      <c r="B4870" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4870" s="0">
+        <v>3340</v>
+      </c>
+      <c r="D4870" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4871">
+      <c r="A4871" s="0">
+        <v>5726</v>
+      </c>
+      <c r="B4871" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4871" s="0">
+        <v>3341</v>
+      </c>
+      <c r="D4871" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4872">
+      <c r="A4872" s="0">
+        <v>5727</v>
+      </c>
+      <c r="B4872" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4872" s="0">
+        <v>3321</v>
+      </c>
+      <c r="D4872" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4873">
+      <c r="A4873" s="0">
+        <v>5728</v>
+      </c>
+      <c r="B4873" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4873" s="0">
+        <v>3343</v>
+      </c>
+      <c r="D4873" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4874">
+      <c r="A4874" s="0">
+        <v>5729</v>
+      </c>
+      <c r="B4874" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4874" s="0">
+        <v>3344</v>
+      </c>
+      <c r="D4874" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4875">
+      <c r="A4875" s="0">
+        <v>5730</v>
+      </c>
+      <c r="B4875" s="0">
+        <v>165</v>
+      </c>
+      <c r="C4875" s="0">
+        <v>3347</v>
+      </c>
+      <c r="D4875" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4876">
+      <c r="A4876" s="0">
         <v>5731</v>
       </c>
-      <c r="B4719" s="0">
+      <c r="B4876" s="0">
         <v>165</v>
       </c>
-      <c r="C4719" s="0">
+      <c r="C4876" s="0">
         <v>3327</v>
       </c>
-      <c r="D4719" s="0">
+      <c r="D4876" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4877">
+      <c r="A4877" s="0">
+        <v>5904</v>
+      </c>
+      <c r="B4877" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4877" s="0">
+        <v>3455</v>
+      </c>
+      <c r="D4877" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4878">
+      <c r="A4878" s="0">
+        <v>5905</v>
+      </c>
+      <c r="B4878" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4878" s="0">
+        <v>3456</v>
+      </c>
+      <c r="D4878" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4879">
+      <c r="A4879" s="0">
+        <v>5906</v>
+      </c>
+      <c r="B4879" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4879" s="0">
+        <v>3457</v>
+      </c>
+      <c r="D4879" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4880">
+      <c r="A4880" s="0">
+        <v>5907</v>
+      </c>
+      <c r="B4880" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4880" s="0">
+        <v>3458</v>
+      </c>
+      <c r="D4880" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4881">
+      <c r="A4881" s="0">
+        <v>5908</v>
+      </c>
+      <c r="B4881" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4881" s="0">
+        <v>3459</v>
+      </c>
+      <c r="D4881" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4882">
+      <c r="A4882" s="0">
+        <v>5909</v>
+      </c>
+      <c r="B4882" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4882" s="0">
+        <v>3460</v>
+      </c>
+      <c r="D4882" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4883">
+      <c r="A4883" s="0">
+        <v>5910</v>
+      </c>
+      <c r="B4883" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4883" s="0">
+        <v>3461</v>
+      </c>
+      <c r="D4883" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4884">
+      <c r="A4884" s="0">
+        <v>5911</v>
+      </c>
+      <c r="B4884" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4884" s="0">
+        <v>3462</v>
+      </c>
+      <c r="D4884" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4885">
+      <c r="A4885" s="0">
+        <v>5912</v>
+      </c>
+      <c r="B4885" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4885" s="0">
+        <v>3463</v>
+      </c>
+      <c r="D4885" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4886">
+      <c r="A4886" s="0">
+        <v>5913</v>
+      </c>
+      <c r="B4886" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4886" s="0">
+        <v>3464</v>
+      </c>
+      <c r="D4886" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4887">
+      <c r="A4887" s="0">
+        <v>5914</v>
+      </c>
+      <c r="B4887" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4887" s="0">
+        <v>3465</v>
+      </c>
+      <c r="D4887" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4888">
+      <c r="A4888" s="0">
+        <v>5915</v>
+      </c>
+      <c r="B4888" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4888" s="0">
+        <v>3466</v>
+      </c>
+      <c r="D4888" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4889">
+      <c r="A4889" s="0">
+        <v>5916</v>
+      </c>
+      <c r="B4889" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4889" s="0">
+        <v>3467</v>
+      </c>
+      <c r="D4889" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4890">
+      <c r="A4890" s="0">
+        <v>5917</v>
+      </c>
+      <c r="B4890" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4890" s="0">
+        <v>3468</v>
+      </c>
+      <c r="D4890" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4891">
+      <c r="A4891" s="0">
+        <v>5918</v>
+      </c>
+      <c r="B4891" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4891" s="0">
+        <v>3469</v>
+      </c>
+      <c r="D4891" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4892">
+      <c r="A4892" s="0">
+        <v>5919</v>
+      </c>
+      <c r="B4892" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4892" s="0">
+        <v>3470</v>
+      </c>
+      <c r="D4892" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4893">
+      <c r="A4893" s="0">
+        <v>5920</v>
+      </c>
+      <c r="B4893" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4893" s="0">
+        <v>3471</v>
+      </c>
+      <c r="D4893" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4894">
+      <c r="A4894" s="0">
+        <v>5921</v>
+      </c>
+      <c r="B4894" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4894" s="0">
+        <v>3472</v>
+      </c>
+      <c r="D4894" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4895">
+      <c r="A4895" s="0">
+        <v>5922</v>
+      </c>
+      <c r="B4895" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4895" s="0">
+        <v>3473</v>
+      </c>
+      <c r="D4895" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4896">
+      <c r="A4896" s="0">
+        <v>5923</v>
+      </c>
+      <c r="B4896" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4896" s="0">
+        <v>3474</v>
+      </c>
+      <c r="D4896" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4897">
+      <c r="A4897" s="0">
+        <v>5924</v>
+      </c>
+      <c r="B4897" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4897" s="0">
+        <v>3475</v>
+      </c>
+      <c r="D4897" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4898">
+      <c r="A4898" s="0">
+        <v>5925</v>
+      </c>
+      <c r="B4898" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4898" s="0">
+        <v>3476</v>
+      </c>
+      <c r="D4898" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4899">
+      <c r="A4899" s="0">
+        <v>5926</v>
+      </c>
+      <c r="B4899" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4899" s="0">
+        <v>3477</v>
+      </c>
+      <c r="D4899" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4900">
+      <c r="A4900" s="0">
+        <v>5927</v>
+      </c>
+      <c r="B4900" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4900" s="0">
+        <v>3478</v>
+      </c>
+      <c r="D4900" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4901">
+      <c r="A4901" s="0">
+        <v>5928</v>
+      </c>
+      <c r="B4901" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4901" s="0">
+        <v>3479</v>
+      </c>
+      <c r="D4901" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4902">
+      <c r="A4902" s="0">
+        <v>5929</v>
+      </c>
+      <c r="B4902" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4902" s="0">
+        <v>3480</v>
+      </c>
+      <c r="D4902" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4903">
+      <c r="A4903" s="0">
+        <v>5930</v>
+      </c>
+      <c r="B4903" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4903" s="0">
+        <v>3481</v>
+      </c>
+      <c r="D4903" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4904">
+      <c r="A4904" s="0">
+        <v>5931</v>
+      </c>
+      <c r="B4904" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4904" s="0">
+        <v>3482</v>
+      </c>
+      <c r="D4904" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4905">
+      <c r="A4905" s="0">
+        <v>5932</v>
+      </c>
+      <c r="B4905" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4905" s="0">
+        <v>3483</v>
+      </c>
+      <c r="D4905" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4906">
+      <c r="A4906" s="0">
+        <v>5933</v>
+      </c>
+      <c r="B4906" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4906" s="0">
+        <v>3484</v>
+      </c>
+      <c r="D4906" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4907">
+      <c r="A4907" s="0">
+        <v>5934</v>
+      </c>
+      <c r="B4907" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4907" s="0">
+        <v>3485</v>
+      </c>
+      <c r="D4907" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4908">
+      <c r="A4908" s="0">
+        <v>5935</v>
+      </c>
+      <c r="B4908" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4908" s="0">
+        <v>3486</v>
+      </c>
+      <c r="D4908" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4909">
+      <c r="A4909" s="0">
+        <v>5936</v>
+      </c>
+      <c r="B4909" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4909" s="0">
+        <v>3487</v>
+      </c>
+      <c r="D4909" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4910">
+      <c r="A4910" s="0">
+        <v>5937</v>
+      </c>
+      <c r="B4910" s="0">
+        <v>172</v>
+      </c>
+      <c r="C4910" s="0">
+        <v>3488</v>
+      </c>
+      <c r="D4910" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4911">
+      <c r="A4911" s="0">
+        <v>5938</v>
+      </c>
+      <c r="B4911" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4911" s="0">
+        <v>3443</v>
+      </c>
+      <c r="D4911" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4912">
+      <c r="A4912" s="0">
+        <v>5939</v>
+      </c>
+      <c r="B4912" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4912" s="0">
+        <v>3445</v>
+      </c>
+      <c r="D4912" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4913">
+      <c r="A4913" s="0">
+        <v>5940</v>
+      </c>
+      <c r="B4913" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4913" s="0">
+        <v>3446</v>
+      </c>
+      <c r="D4913" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4914">
+      <c r="A4914" s="0">
+        <v>5941</v>
+      </c>
+      <c r="B4914" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4914" s="0">
+        <v>3447</v>
+      </c>
+      <c r="D4914" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4915">
+      <c r="A4915" s="0">
+        <v>5942</v>
+      </c>
+      <c r="B4915" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4915" s="0">
+        <v>3454</v>
+      </c>
+      <c r="D4915" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4916">
+      <c r="A4916" s="0">
+        <v>5943</v>
+      </c>
+      <c r="B4916" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4916" s="0">
+        <v>3474</v>
+      </c>
+      <c r="D4916" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4917">
+      <c r="A4917" s="0">
+        <v>5944</v>
+      </c>
+      <c r="B4917" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4917" s="0">
+        <v>3473</v>
+      </c>
+      <c r="D4917" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4918">
+      <c r="A4918" s="0">
+        <v>5945</v>
+      </c>
+      <c r="B4918" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4918" s="0">
+        <v>3452</v>
+      </c>
+      <c r="D4918" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4919">
+      <c r="A4919" s="0">
+        <v>5946</v>
+      </c>
+      <c r="B4919" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4919" s="0">
+        <v>3458</v>
+      </c>
+      <c r="D4919" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4920">
+      <c r="A4920" s="0">
+        <v>5947</v>
+      </c>
+      <c r="B4920" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4920" s="0">
+        <v>3456</v>
+      </c>
+      <c r="D4920" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4921">
+      <c r="A4921" s="0">
+        <v>5948</v>
+      </c>
+      <c r="B4921" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4921" s="0">
+        <v>3477</v>
+      </c>
+      <c r="D4921" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4922">
+      <c r="A4922" s="0">
+        <v>5949</v>
+      </c>
+      <c r="B4922" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4922" s="0">
+        <v>3483</v>
+      </c>
+      <c r="D4922" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4923">
+      <c r="A4923" s="0">
+        <v>5950</v>
+      </c>
+      <c r="B4923" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4923" s="0">
+        <v>3460</v>
+      </c>
+      <c r="D4923" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4924">
+      <c r="A4924" s="0">
+        <v>5951</v>
+      </c>
+      <c r="B4924" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4924" s="0">
+        <v>3467</v>
+      </c>
+      <c r="D4924" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4925">
+      <c r="A4925" s="0">
+        <v>5952</v>
+      </c>
+      <c r="B4925" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4925" s="0">
+        <v>3466</v>
+      </c>
+      <c r="D4925" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4926">
+      <c r="A4926" s="0">
+        <v>5953</v>
+      </c>
+      <c r="B4926" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4926" s="0">
+        <v>3470</v>
+      </c>
+      <c r="D4926" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4927">
+      <c r="A4927" s="0">
+        <v>5954</v>
+      </c>
+      <c r="B4927" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4927" s="0">
+        <v>3472</v>
+      </c>
+      <c r="D4927" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4928">
+      <c r="A4928" s="0">
+        <v>5955</v>
+      </c>
+      <c r="B4928" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4928" s="0">
+        <v>3478</v>
+      </c>
+      <c r="D4928" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4929">
+      <c r="A4929" s="0">
+        <v>5956</v>
+      </c>
+      <c r="B4929" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4929" s="0">
+        <v>3481</v>
+      </c>
+      <c r="D4929" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4930">
+      <c r="A4930" s="0">
+        <v>5957</v>
+      </c>
+      <c r="B4930" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4930" s="0">
+        <v>3482</v>
+      </c>
+      <c r="D4930" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4931">
+      <c r="A4931" s="0">
+        <v>5958</v>
+      </c>
+      <c r="B4931" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4931" s="0">
+        <v>3462</v>
+      </c>
+      <c r="D4931" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4932">
+      <c r="A4932" s="0">
+        <v>5959</v>
+      </c>
+      <c r="B4932" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4932" s="0">
+        <v>3484</v>
+      </c>
+      <c r="D4932" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4933">
+      <c r="A4933" s="0">
+        <v>5960</v>
+      </c>
+      <c r="B4933" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4933" s="0">
+        <v>3485</v>
+      </c>
+      <c r="D4933" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4934">
+      <c r="A4934" s="0">
+        <v>5961</v>
+      </c>
+      <c r="B4934" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4934" s="0">
+        <v>3488</v>
+      </c>
+      <c r="D4934" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4935">
+      <c r="A4935" s="0">
+        <v>5962</v>
+      </c>
+      <c r="B4935" s="0">
+        <v>174</v>
+      </c>
+      <c r="C4935" s="0">
+        <v>3468</v>
+      </c>
+      <c r="D4935" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4936">
+      <c r="A4936" s="0">
+        <v>5963</v>
+      </c>
+      <c r="B4936" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4936" s="0">
+        <v>3489</v>
+      </c>
+      <c r="D4936" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4937">
+      <c r="A4937" s="0">
+        <v>5964</v>
+      </c>
+      <c r="B4937" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4937" s="0">
+        <v>3490</v>
+      </c>
+      <c r="D4937" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4938">
+      <c r="A4938" s="0">
+        <v>5965</v>
+      </c>
+      <c r="B4938" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4938" s="0">
+        <v>3491</v>
+      </c>
+      <c r="D4938" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4939">
+      <c r="A4939" s="0">
+        <v>5966</v>
+      </c>
+      <c r="B4939" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4939" s="0">
+        <v>3492</v>
+      </c>
+      <c r="D4939" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4940">
+      <c r="A4940" s="0">
+        <v>5967</v>
+      </c>
+      <c r="B4940" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4940" s="0">
+        <v>3493</v>
+      </c>
+      <c r="D4940" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4941">
+      <c r="A4941" s="0">
+        <v>5968</v>
+      </c>
+      <c r="B4941" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4941" s="0">
+        <v>3494</v>
+      </c>
+      <c r="D4941" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4942">
+      <c r="A4942" s="0">
+        <v>5969</v>
+      </c>
+      <c r="B4942" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4942" s="0">
+        <v>3495</v>
+      </c>
+      <c r="D4942" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4943">
+      <c r="A4943" s="0">
+        <v>5970</v>
+      </c>
+      <c r="B4943" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4943" s="0">
+        <v>3496</v>
+      </c>
+      <c r="D4943" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4944">
+      <c r="A4944" s="0">
+        <v>5971</v>
+      </c>
+      <c r="B4944" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4944" s="0">
+        <v>3497</v>
+      </c>
+      <c r="D4944" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4945">
+      <c r="A4945" s="0">
+        <v>5972</v>
+      </c>
+      <c r="B4945" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4945" s="0">
+        <v>3498</v>
+      </c>
+      <c r="D4945" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4946">
+      <c r="A4946" s="0">
+        <v>5973</v>
+      </c>
+      <c r="B4946" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4946" s="0">
+        <v>3499</v>
+      </c>
+      <c r="D4946" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4947">
+      <c r="A4947" s="0">
+        <v>5974</v>
+      </c>
+      <c r="B4947" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4947" s="0">
+        <v>3500</v>
+      </c>
+      <c r="D4947" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4948">
+      <c r="A4948" s="0">
+        <v>5975</v>
+      </c>
+      <c r="B4948" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4948" s="0">
+        <v>3501</v>
+      </c>
+      <c r="D4948" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4949">
+      <c r="A4949" s="0">
+        <v>5976</v>
+      </c>
+      <c r="B4949" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4949" s="0">
+        <v>3502</v>
+      </c>
+      <c r="D4949" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4950">
+      <c r="A4950" s="0">
+        <v>5977</v>
+      </c>
+      <c r="B4950" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4950" s="0">
+        <v>3503</v>
+      </c>
+      <c r="D4950" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4951">
+      <c r="A4951" s="0">
+        <v>5978</v>
+      </c>
+      <c r="B4951" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4951" s="0">
+        <v>3504</v>
+      </c>
+      <c r="D4951" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4952">
+      <c r="A4952" s="0">
+        <v>5979</v>
+      </c>
+      <c r="B4952" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4952" s="0">
+        <v>3505</v>
+      </c>
+      <c r="D4952" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4953">
+      <c r="A4953" s="0">
+        <v>5980</v>
+      </c>
+      <c r="B4953" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4953" s="0">
+        <v>3506</v>
+      </c>
+      <c r="D4953" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4954">
+      <c r="A4954" s="0">
+        <v>5981</v>
+      </c>
+      <c r="B4954" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4954" s="0">
+        <v>3507</v>
+      </c>
+      <c r="D4954" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4955">
+      <c r="A4955" s="0">
+        <v>5982</v>
+      </c>
+      <c r="B4955" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4955" s="0">
+        <v>3508</v>
+      </c>
+      <c r="D4955" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4956">
+      <c r="A4956" s="0">
+        <v>5983</v>
+      </c>
+      <c r="B4956" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4956" s="0">
+        <v>3509</v>
+      </c>
+      <c r="D4956" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4957">
+      <c r="A4957" s="0">
+        <v>5984</v>
+      </c>
+      <c r="B4957" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4957" s="0">
+        <v>3510</v>
+      </c>
+      <c r="D4957" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4958">
+      <c r="A4958" s="0">
+        <v>5985</v>
+      </c>
+      <c r="B4958" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4958" s="0">
+        <v>3511</v>
+      </c>
+      <c r="D4958" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4959">
+      <c r="A4959" s="0">
+        <v>5986</v>
+      </c>
+      <c r="B4959" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4959" s="0">
+        <v>3512</v>
+      </c>
+      <c r="D4959" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4960">
+      <c r="A4960" s="0">
+        <v>5987</v>
+      </c>
+      <c r="B4960" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4960" s="0">
+        <v>3513</v>
+      </c>
+      <c r="D4960" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4961">
+      <c r="A4961" s="0">
+        <v>5988</v>
+      </c>
+      <c r="B4961" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4961" s="0">
+        <v>3514</v>
+      </c>
+      <c r="D4961" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4962">
+      <c r="A4962" s="0">
+        <v>5989</v>
+      </c>
+      <c r="B4962" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4962" s="0">
+        <v>3515</v>
+      </c>
+      <c r="D4962" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4963">
+      <c r="A4963" s="0">
+        <v>5990</v>
+      </c>
+      <c r="B4963" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4963" s="0">
+        <v>3516</v>
+      </c>
+      <c r="D4963" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4964">
+      <c r="A4964" s="0">
+        <v>5991</v>
+      </c>
+      <c r="B4964" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4964" s="0">
+        <v>3517</v>
+      </c>
+      <c r="D4964" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4965">
+      <c r="A4965" s="0">
+        <v>5992</v>
+      </c>
+      <c r="B4965" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4965" s="0">
+        <v>3518</v>
+      </c>
+      <c r="D4965" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4966">
+      <c r="A4966" s="0">
+        <v>5993</v>
+      </c>
+      <c r="B4966" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4966" s="0">
+        <v>3519</v>
+      </c>
+      <c r="D4966" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4967">
+      <c r="A4967" s="0">
+        <v>5994</v>
+      </c>
+      <c r="B4967" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4967" s="0">
+        <v>3520</v>
+      </c>
+      <c r="D4967" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4968">
+      <c r="A4968" s="0">
+        <v>5995</v>
+      </c>
+      <c r="B4968" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4968" s="0">
+        <v>3521</v>
+      </c>
+      <c r="D4968" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4969">
+      <c r="A4969" s="0">
+        <v>5996</v>
+      </c>
+      <c r="B4969" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4969" s="0">
+        <v>3522</v>
+      </c>
+      <c r="D4969" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4970">
+      <c r="A4970" s="0">
+        <v>5997</v>
+      </c>
+      <c r="B4970" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4970" s="0">
+        <v>3523</v>
+      </c>
+      <c r="D4970" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4971">
+      <c r="A4971" s="0">
+        <v>5998</v>
+      </c>
+      <c r="B4971" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4971" s="0">
+        <v>3524</v>
+      </c>
+      <c r="D4971" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4972">
+      <c r="A4972" s="0">
+        <v>5999</v>
+      </c>
+      <c r="B4972" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4972" s="0">
+        <v>3525</v>
+      </c>
+      <c r="D4972" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4973">
+      <c r="A4973" s="0">
+        <v>6000</v>
+      </c>
+      <c r="B4973" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4973" s="0">
+        <v>3526</v>
+      </c>
+      <c r="D4973" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4974">
+      <c r="A4974" s="0">
+        <v>6001</v>
+      </c>
+      <c r="B4974" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4974" s="0">
+        <v>3527</v>
+      </c>
+      <c r="D4974" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4975">
+      <c r="A4975" s="0">
+        <v>6002</v>
+      </c>
+      <c r="B4975" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4975" s="0">
+        <v>3528</v>
+      </c>
+      <c r="D4975" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4976">
+      <c r="A4976" s="0">
+        <v>6003</v>
+      </c>
+      <c r="B4976" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4976" s="0">
+        <v>3529</v>
+      </c>
+      <c r="D4976" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4977">
+      <c r="A4977" s="0">
+        <v>6004</v>
+      </c>
+      <c r="B4977" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4977" s="0">
+        <v>3530</v>
+      </c>
+      <c r="D4977" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4978">
+      <c r="A4978" s="0">
+        <v>6005</v>
+      </c>
+      <c r="B4978" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4978" s="0">
+        <v>3531</v>
+      </c>
+      <c r="D4978" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4979">
+      <c r="A4979" s="0">
+        <v>6006</v>
+      </c>
+      <c r="B4979" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4979" s="0">
+        <v>3532</v>
+      </c>
+      <c r="D4979" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4980">
+      <c r="A4980" s="0">
+        <v>6007</v>
+      </c>
+      <c r="B4980" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4980" s="0">
+        <v>3533</v>
+      </c>
+      <c r="D4980" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4981">
+      <c r="A4981" s="0">
+        <v>6008</v>
+      </c>
+      <c r="B4981" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4981" s="0">
+        <v>3534</v>
+      </c>
+      <c r="D4981" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4982">
+      <c r="A4982" s="0">
+        <v>6009</v>
+      </c>
+      <c r="B4982" s="0">
+        <v>173</v>
+      </c>
+      <c r="C4982" s="0">
+        <v>3535</v>
+      </c>
+      <c r="D4982" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4983">
+      <c r="A4983" s="0">
+        <v>6010</v>
+      </c>
+      <c r="B4983" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4983" s="0">
+        <v>3490</v>
+      </c>
+      <c r="D4983" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4984">
+      <c r="A4984" s="0">
+        <v>6011</v>
+      </c>
+      <c r="B4984" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4984" s="0">
+        <v>3492</v>
+      </c>
+      <c r="D4984" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4985">
+      <c r="A4985" s="0">
+        <v>6012</v>
+      </c>
+      <c r="B4985" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4985" s="0">
+        <v>3493</v>
+      </c>
+      <c r="D4985" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4986">
+      <c r="A4986" s="0">
+        <v>6013</v>
+      </c>
+      <c r="B4986" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4986" s="0">
+        <v>3494</v>
+      </c>
+      <c r="D4986" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4987">
+      <c r="A4987" s="0">
+        <v>6014</v>
+      </c>
+      <c r="B4987" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4987" s="0">
+        <v>3501</v>
+      </c>
+      <c r="D4987" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4988">
+      <c r="A4988" s="0">
+        <v>6015</v>
+      </c>
+      <c r="B4988" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4988" s="0">
+        <v>3521</v>
+      </c>
+      <c r="D4988" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4989">
+      <c r="A4989" s="0">
+        <v>6016</v>
+      </c>
+      <c r="B4989" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4989" s="0">
+        <v>3520</v>
+      </c>
+      <c r="D4989" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4990">
+      <c r="A4990" s="0">
+        <v>6017</v>
+      </c>
+      <c r="B4990" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4990" s="0">
+        <v>3499</v>
+      </c>
+      <c r="D4990" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4991">
+      <c r="A4991" s="0">
+        <v>6018</v>
+      </c>
+      <c r="B4991" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4991" s="0">
+        <v>3505</v>
+      </c>
+      <c r="D4991" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4992">
+      <c r="A4992" s="0">
+        <v>6019</v>
+      </c>
+      <c r="B4992" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4992" s="0">
+        <v>3503</v>
+      </c>
+      <c r="D4992" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4993">
+      <c r="A4993" s="0">
+        <v>6020</v>
+      </c>
+      <c r="B4993" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4993" s="0">
+        <v>3524</v>
+      </c>
+      <c r="D4993" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4994">
+      <c r="A4994" s="0">
+        <v>6021</v>
+      </c>
+      <c r="B4994" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4994" s="0">
+        <v>3530</v>
+      </c>
+      <c r="D4994" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4995">
+      <c r="A4995" s="0">
+        <v>6022</v>
+      </c>
+      <c r="B4995" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4995" s="0">
+        <v>3507</v>
+      </c>
+      <c r="D4995" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4996">
+      <c r="A4996" s="0">
+        <v>6023</v>
+      </c>
+      <c r="B4996" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4996" s="0">
+        <v>3514</v>
+      </c>
+      <c r="D4996" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4997">
+      <c r="A4997" s="0">
+        <v>6024</v>
+      </c>
+      <c r="B4997" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4997" s="0">
+        <v>3513</v>
+      </c>
+      <c r="D4997" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4998">
+      <c r="A4998" s="0">
+        <v>6025</v>
+      </c>
+      <c r="B4998" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4998" s="0">
+        <v>3517</v>
+      </c>
+      <c r="D4998" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4999">
+      <c r="A4999" s="0">
+        <v>6026</v>
+      </c>
+      <c r="B4999" s="0">
+        <v>175</v>
+      </c>
+      <c r="C4999" s="0">
+        <v>3519</v>
+      </c>
+      <c r="D4999" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5000">
+      <c r="A5000" s="0">
+        <v>6027</v>
+      </c>
+      <c r="B5000" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5000" s="0">
+        <v>3525</v>
+      </c>
+      <c r="D5000" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5001">
+      <c r="A5001" s="0">
+        <v>6028</v>
+      </c>
+      <c r="B5001" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5001" s="0">
+        <v>3528</v>
+      </c>
+      <c r="D5001" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5002">
+      <c r="A5002" s="0">
+        <v>6029</v>
+      </c>
+      <c r="B5002" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5002" s="0">
+        <v>3529</v>
+      </c>
+      <c r="D5002" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5003">
+      <c r="A5003" s="0">
+        <v>6030</v>
+      </c>
+      <c r="B5003" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5003" s="0">
+        <v>3509</v>
+      </c>
+      <c r="D5003" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5004">
+      <c r="A5004" s="0">
+        <v>6031</v>
+      </c>
+      <c r="B5004" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5004" s="0">
+        <v>3531</v>
+      </c>
+      <c r="D5004" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5005">
+      <c r="A5005" s="0">
+        <v>6032</v>
+      </c>
+      <c r="B5005" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5005" s="0">
+        <v>3532</v>
+      </c>
+      <c r="D5005" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5006">
+      <c r="A5006" s="0">
+        <v>6033</v>
+      </c>
+      <c r="B5006" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5006" s="0">
+        <v>3535</v>
+      </c>
+      <c r="D5006" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5007">
+      <c r="A5007" s="0">
+        <v>6034</v>
+      </c>
+      <c r="B5007" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5007" s="0">
+        <v>3515</v>
+      </c>
+      <c r="D5007" s="0">
         <v>25</v>
       </c>
     </row>

--- a/rcads/data/xls/23_InstrumentItemMap.xlsx
+++ b/rcads/data/xls/23_InstrumentItemMap.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_23_InstrumentItemMap"/>
   </sheets>
   <definedNames>
-    <definedName name="_23_InstrumentItemMap">'_23_InstrumentItemMap'!$A$1:$E$5007</definedName>
+    <definedName name="_23_InstrumentItemMap">'_23_InstrumentItemMap'!$A$1:$E$5295</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5007"/>
+  <dimension ref="A1:E5295"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -67336,3992 +67336,8024 @@
     </row>
     <row outlineLevel="0" r="4723">
       <c r="A4723" s="0">
-        <v>5578</v>
+        <v>6067</v>
       </c>
       <c r="B4723" s="0">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="C4723" s="0">
-        <v>3248</v>
+        <v>3568</v>
       </c>
       <c r="D4723" s="0">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row outlineLevel="0" r="4724">
       <c r="A4724" s="0">
-        <v>5579</v>
+        <v>6068</v>
       </c>
       <c r="B4724" s="0">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="C4724" s="0">
-        <v>3248</v>
+        <v>3569</v>
       </c>
       <c r="D4724" s="0">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row outlineLevel="0" r="4725">
       <c r="A4725" s="0">
-        <v>5580</v>
+        <v>6069</v>
       </c>
       <c r="B4725" s="0">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="C4725" s="0">
-        <v>3249</v>
+        <v>3570</v>
       </c>
       <c r="D4725" s="0">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row outlineLevel="0" r="4726">
       <c r="A4726" s="0">
-        <v>5581</v>
+        <v>6070</v>
       </c>
       <c r="B4726" s="0">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="C4726" s="0">
-        <v>3249</v>
+        <v>3571</v>
       </c>
       <c r="D4726" s="0">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row outlineLevel="0" r="4727">
       <c r="A4727" s="0">
-        <v>5582</v>
+        <v>6071</v>
       </c>
       <c r="B4727" s="0">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="C4727" s="0">
-        <v>3250</v>
+        <v>3572</v>
       </c>
       <c r="D4727" s="0">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row outlineLevel="0" r="4728">
       <c r="A4728" s="0">
-        <v>5583</v>
+        <v>6072</v>
       </c>
       <c r="B4728" s="0">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="C4728" s="0">
-        <v>3250</v>
+        <v>3573</v>
       </c>
       <c r="D4728" s="0">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row outlineLevel="0" r="4729">
       <c r="A4729" s="0">
-        <v>5584</v>
+        <v>6073</v>
       </c>
       <c r="B4729" s="0">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="C4729" s="0">
-        <v>3251</v>
+        <v>3574</v>
       </c>
       <c r="D4729" s="0">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row outlineLevel="0" r="4730">
       <c r="A4730" s="0">
-        <v>5585</v>
+        <v>6074</v>
       </c>
       <c r="B4730" s="0">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="C4730" s="0">
-        <v>3252</v>
+        <v>3575</v>
       </c>
       <c r="D4730" s="0">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row outlineLevel="0" r="4731">
       <c r="A4731" s="0">
-        <v>5586</v>
+        <v>6075</v>
       </c>
       <c r="B4731" s="0">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="C4731" s="0">
-        <v>3253</v>
+        <v>3576</v>
       </c>
       <c r="D4731" s="0">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row outlineLevel="0" r="4732">
       <c r="A4732" s="0">
-        <v>5587</v>
+        <v>6076</v>
       </c>
       <c r="B4732" s="0">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="C4732" s="0">
-        <v>3253</v>
+        <v>3577</v>
       </c>
       <c r="D4732" s="0">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row outlineLevel="0" r="4733">
       <c r="A4733" s="0">
-        <v>5588</v>
+        <v>6077</v>
       </c>
       <c r="B4733" s="0">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C4733" s="0">
-        <v>3254</v>
+        <v>3578</v>
       </c>
       <c r="D4733" s="0">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row outlineLevel="0" r="4734">
       <c r="A4734" s="0">
-        <v>5589</v>
+        <v>6078</v>
       </c>
       <c r="B4734" s="0">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C4734" s="0">
-        <v>3255</v>
+        <v>3579</v>
       </c>
       <c r="D4734" s="0">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row outlineLevel="0" r="4735">
       <c r="A4735" s="0">
-        <v>5590</v>
+        <v>6079</v>
       </c>
       <c r="B4735" s="0">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C4735" s="0">
-        <v>3256</v>
+        <v>3580</v>
       </c>
       <c r="D4735" s="0">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row outlineLevel="0" r="4736">
       <c r="A4736" s="0">
-        <v>5591</v>
+        <v>6080</v>
       </c>
       <c r="B4736" s="0">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C4736" s="0">
-        <v>3257</v>
+        <v>3581</v>
       </c>
       <c r="D4736" s="0">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row outlineLevel="0" r="4737">
       <c r="A4737" s="0">
-        <v>5592</v>
+        <v>6081</v>
       </c>
       <c r="B4737" s="0">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C4737" s="0">
-        <v>3258</v>
+        <v>3582</v>
       </c>
       <c r="D4737" s="0">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row outlineLevel="0" r="4738">
       <c r="A4738" s="0">
-        <v>5593</v>
+        <v>6082</v>
       </c>
       <c r="B4738" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4738" s="0">
-        <v>3259</v>
+        <v>3537</v>
       </c>
       <c r="D4738" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="4739">
       <c r="A4739" s="0">
-        <v>5594</v>
+        <v>6083</v>
       </c>
       <c r="B4739" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4739" s="0">
-        <v>3260</v>
+        <v>3584</v>
       </c>
       <c r="D4739" s="0">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row outlineLevel="0" r="4740">
       <c r="A4740" s="0">
-        <v>5595</v>
+        <v>6084</v>
       </c>
       <c r="B4740" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4740" s="0">
-        <v>3261</v>
+        <v>3540</v>
       </c>
       <c r="D4740" s="0">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row outlineLevel="0" r="4741">
       <c r="A4741" s="0">
-        <v>5596</v>
+        <v>6085</v>
       </c>
       <c r="B4741" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4741" s="0">
-        <v>3262</v>
+        <v>3541</v>
       </c>
       <c r="D4741" s="0">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row outlineLevel="0" r="4742">
       <c r="A4742" s="0">
-        <v>5597</v>
+        <v>6086</v>
       </c>
       <c r="B4742" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4742" s="0">
-        <v>3263</v>
+        <v>3548</v>
       </c>
       <c r="D4742" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="4743">
       <c r="A4743" s="0">
-        <v>5598</v>
+        <v>6087</v>
       </c>
       <c r="B4743" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4743" s="0">
-        <v>3264</v>
+        <v>3568</v>
       </c>
       <c r="D4743" s="0">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row outlineLevel="0" r="4744">
       <c r="A4744" s="0">
-        <v>5599</v>
+        <v>6088</v>
       </c>
       <c r="B4744" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4744" s="0">
-        <v>3265</v>
+        <v>3589</v>
       </c>
       <c r="D4744" s="0">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="4745">
       <c r="A4745" s="0">
-        <v>5600</v>
+        <v>6089</v>
       </c>
       <c r="B4745" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4745" s="0">
-        <v>3266</v>
+        <v>3590</v>
       </c>
       <c r="D4745" s="0">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row outlineLevel="0" r="4746">
       <c r="A4746" s="0">
-        <v>5601</v>
+        <v>6090</v>
       </c>
       <c r="B4746" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4746" s="0">
-        <v>3267</v>
+        <v>3552</v>
       </c>
       <c r="D4746" s="0">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row outlineLevel="0" r="4747">
       <c r="A4747" s="0">
-        <v>5602</v>
+        <v>6091</v>
       </c>
       <c r="B4747" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4747" s="0">
-        <v>3268</v>
+        <v>3550</v>
       </c>
       <c r="D4747" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row outlineLevel="0" r="4748">
       <c r="A4748" s="0">
-        <v>5603</v>
+        <v>6092</v>
       </c>
       <c r="B4748" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4748" s="0">
-        <v>3269</v>
+        <v>3571</v>
       </c>
       <c r="D4748" s="0">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row outlineLevel="0" r="4749">
       <c r="A4749" s="0">
-        <v>5604</v>
+        <v>6093</v>
       </c>
       <c r="B4749" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4749" s="0">
-        <v>3270</v>
+        <v>3594</v>
       </c>
       <c r="D4749" s="0">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row outlineLevel="0" r="4750">
       <c r="A4750" s="0">
-        <v>5605</v>
+        <v>6094</v>
       </c>
       <c r="B4750" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4750" s="0">
-        <v>3271</v>
+        <v>3595</v>
       </c>
       <c r="D4750" s="0">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row outlineLevel="0" r="4751">
       <c r="A4751" s="0">
-        <v>5606</v>
+        <v>6095</v>
       </c>
       <c r="B4751" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4751" s="0">
-        <v>3272</v>
+        <v>3561</v>
       </c>
       <c r="D4751" s="0">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row outlineLevel="0" r="4752">
       <c r="A4752" s="0">
-        <v>5607</v>
+        <v>6096</v>
       </c>
       <c r="B4752" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4752" s="0">
-        <v>3273</v>
+        <v>3597</v>
       </c>
       <c r="D4752" s="0">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row outlineLevel="0" r="4753">
       <c r="A4753" s="0">
-        <v>5608</v>
+        <v>6097</v>
       </c>
       <c r="B4753" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4753" s="0">
-        <v>3274</v>
+        <v>3598</v>
       </c>
       <c r="D4753" s="0">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row outlineLevel="0" r="4754">
       <c r="A4754" s="0">
-        <v>5609</v>
+        <v>6098</v>
       </c>
       <c r="B4754" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4754" s="0">
-        <v>3275</v>
+        <v>3599</v>
       </c>
       <c r="D4754" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row outlineLevel="0" r="4755">
       <c r="A4755" s="0">
-        <v>5610</v>
+        <v>6099</v>
       </c>
       <c r="B4755" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4755" s="0">
-        <v>3276</v>
+        <v>3600</v>
       </c>
       <c r="D4755" s="0">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row outlineLevel="0" r="4756">
       <c r="A4756" s="0">
-        <v>5611</v>
+        <v>6100</v>
       </c>
       <c r="B4756" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4756" s="0">
-        <v>3277</v>
+        <v>3575</v>
       </c>
       <c r="D4756" s="0">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row outlineLevel="0" r="4757">
       <c r="A4757" s="0">
-        <v>5612</v>
+        <v>6101</v>
       </c>
       <c r="B4757" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4757" s="0">
-        <v>3278</v>
+        <v>3602</v>
       </c>
       <c r="D4757" s="0">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row outlineLevel="0" r="4758">
       <c r="A4758" s="0">
-        <v>5613</v>
+        <v>6102</v>
       </c>
       <c r="B4758" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4758" s="0">
-        <v>3279</v>
+        <v>3556</v>
       </c>
       <c r="D4758" s="0">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row outlineLevel="0" r="4759">
       <c r="A4759" s="0">
-        <v>5614</v>
+        <v>6103</v>
       </c>
       <c r="B4759" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4759" s="0">
-        <v>3280</v>
+        <v>3604</v>
       </c>
       <c r="D4759" s="0">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="4760">
       <c r="A4760" s="0">
-        <v>5615</v>
+        <v>6104</v>
       </c>
       <c r="B4760" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4760" s="0">
-        <v>3281</v>
+        <v>3605</v>
       </c>
       <c r="D4760" s="0">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row outlineLevel="0" r="4761">
       <c r="A4761" s="0">
-        <v>5616</v>
+        <v>6105</v>
       </c>
       <c r="B4761" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4761" s="0">
-        <v>3282</v>
+        <v>3582</v>
       </c>
       <c r="D4761" s="0">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row outlineLevel="0" r="4762">
       <c r="A4762" s="0">
-        <v>5617</v>
+        <v>6106</v>
       </c>
       <c r="B4762" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4762" s="0">
-        <v>3283</v>
+        <v>3607</v>
       </c>
       <c r="D4762" s="0">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row outlineLevel="0" r="4763">
       <c r="A4763" s="0">
-        <v>5618</v>
+        <v>6107</v>
       </c>
       <c r="B4763" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4763" s="0">
-        <v>3284</v>
+        <v>3608</v>
       </c>
       <c r="D4763" s="0">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="4764">
       <c r="A4764" s="0">
-        <v>5619</v>
+        <v>6108</v>
       </c>
       <c r="B4764" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4764" s="0">
-        <v>3285</v>
+        <v>3609</v>
       </c>
       <c r="D4764" s="0">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row outlineLevel="0" r="4765">
       <c r="A4765" s="0">
-        <v>5620</v>
+        <v>6109</v>
       </c>
       <c r="B4765" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4765" s="0">
-        <v>3286</v>
+        <v>3610</v>
       </c>
       <c r="D4765" s="0">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row outlineLevel="0" r="4766">
       <c r="A4766" s="0">
-        <v>5621</v>
+        <v>6110</v>
       </c>
       <c r="B4766" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4766" s="0">
-        <v>3287</v>
+        <v>3611</v>
       </c>
       <c r="D4766" s="0">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row outlineLevel="0" r="4767">
       <c r="A4767" s="0">
-        <v>5622</v>
+        <v>6111</v>
       </c>
       <c r="B4767" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4767" s="0">
-        <v>3288</v>
+        <v>3612</v>
       </c>
       <c r="D4767" s="0">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="4768">
       <c r="A4768" s="0">
-        <v>5623</v>
+        <v>6112</v>
       </c>
       <c r="B4768" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4768" s="0">
-        <v>3289</v>
+        <v>3613</v>
       </c>
       <c r="D4768" s="0">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row outlineLevel="0" r="4769">
       <c r="A4769" s="0">
-        <v>5624</v>
+        <v>6113</v>
       </c>
       <c r="B4769" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4769" s="0">
-        <v>3290</v>
+        <v>3614</v>
       </c>
       <c r="D4769" s="0">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="4770">
       <c r="A4770" s="0">
-        <v>5625</v>
+        <v>6114</v>
       </c>
       <c r="B4770" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4770" s="0">
-        <v>3291</v>
+        <v>3615</v>
       </c>
       <c r="D4770" s="0">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row outlineLevel="0" r="4771">
       <c r="A4771" s="0">
-        <v>5626</v>
+        <v>6115</v>
       </c>
       <c r="B4771" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4771" s="0">
-        <v>3292</v>
+        <v>3616</v>
       </c>
       <c r="D4771" s="0">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row outlineLevel="0" r="4772">
       <c r="A4772" s="0">
-        <v>5627</v>
+        <v>6116</v>
       </c>
       <c r="B4772" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4772" s="0">
-        <v>3293</v>
+        <v>3617</v>
       </c>
       <c r="D4772" s="0">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row outlineLevel="0" r="4773">
       <c r="A4773" s="0">
-        <v>5628</v>
+        <v>6117</v>
       </c>
       <c r="B4773" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4773" s="0">
-        <v>3294</v>
+        <v>3618</v>
       </c>
       <c r="D4773" s="0">
-        <v>41</v>
+        <v>11</v>
       </c>
     </row>
     <row outlineLevel="0" r="4774">
       <c r="A4774" s="0">
-        <v>5629</v>
+        <v>6118</v>
       </c>
       <c r="B4774" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4774" s="0">
-        <v>3295</v>
+        <v>3619</v>
       </c>
       <c r="D4774" s="0">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row outlineLevel="0" r="4775">
       <c r="A4775" s="0">
-        <v>5630</v>
+        <v>6119</v>
       </c>
       <c r="B4775" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4775" s="0">
-        <v>3296</v>
+        <v>3620</v>
       </c>
       <c r="D4775" s="0">
-        <v>43</v>
+        <v>13</v>
       </c>
     </row>
     <row outlineLevel="0" r="4776">
       <c r="A4776" s="0">
-        <v>5631</v>
+        <v>6120</v>
       </c>
       <c r="B4776" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4776" s="0">
-        <v>3297</v>
+        <v>3621</v>
       </c>
       <c r="D4776" s="0">
-        <v>44</v>
+        <v>14</v>
       </c>
     </row>
     <row outlineLevel="0" r="4777">
       <c r="A4777" s="0">
-        <v>5632</v>
+        <v>6121</v>
       </c>
       <c r="B4777" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4777" s="0">
-        <v>3298</v>
+        <v>3622</v>
       </c>
       <c r="D4777" s="0">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row outlineLevel="0" r="4778">
       <c r="A4778" s="0">
-        <v>5633</v>
+        <v>6122</v>
       </c>
       <c r="B4778" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4778" s="0">
-        <v>3299</v>
+        <v>3623</v>
       </c>
       <c r="D4778" s="0">
-        <v>46</v>
+        <v>16</v>
       </c>
     </row>
     <row outlineLevel="0" r="4779">
       <c r="A4779" s="0">
-        <v>5634</v>
+        <v>6123</v>
       </c>
       <c r="B4779" s="0">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C4779" s="0">
-        <v>3300</v>
+        <v>3624</v>
       </c>
       <c r="D4779" s="0">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
     <row outlineLevel="0" r="4780">
       <c r="A4780" s="0">
-        <v>5635</v>
+        <v>6124</v>
       </c>
       <c r="B4780" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4780" s="0">
-        <v>3255</v>
+        <v>3625</v>
       </c>
       <c r="D4780" s="0">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row outlineLevel="0" r="4781">
       <c r="A4781" s="0">
-        <v>5636</v>
+        <v>6125</v>
       </c>
       <c r="B4781" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4781" s="0">
-        <v>3257</v>
+        <v>3626</v>
       </c>
       <c r="D4781" s="0">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row outlineLevel="0" r="4782">
       <c r="A4782" s="0">
-        <v>5637</v>
+        <v>6126</v>
       </c>
       <c r="B4782" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4782" s="0">
-        <v>3258</v>
+        <v>3627</v>
       </c>
       <c r="D4782" s="0">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row outlineLevel="0" r="4783">
       <c r="A4783" s="0">
-        <v>5638</v>
+        <v>6127</v>
       </c>
       <c r="B4783" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4783" s="0">
-        <v>3259</v>
+        <v>3628</v>
       </c>
       <c r="D4783" s="0">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row outlineLevel="0" r="4784">
       <c r="A4784" s="0">
-        <v>5639</v>
+        <v>6128</v>
       </c>
       <c r="B4784" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4784" s="0">
-        <v>3266</v>
+        <v>3629</v>
       </c>
       <c r="D4784" s="0">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="4785">
       <c r="A4785" s="0">
-        <v>5640</v>
+        <v>6129</v>
       </c>
       <c r="B4785" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4785" s="0">
-        <v>3286</v>
+        <v>3630</v>
       </c>
       <c r="D4785" s="0">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row outlineLevel="0" r="4786">
       <c r="A4786" s="0">
-        <v>5641</v>
+        <v>6130</v>
       </c>
       <c r="B4786" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4786" s="0">
-        <v>3285</v>
+        <v>3631</v>
       </c>
       <c r="D4786" s="0">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row outlineLevel="0" r="4787">
       <c r="A4787" s="0">
-        <v>5642</v>
+        <v>6131</v>
       </c>
       <c r="B4787" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4787" s="0">
-        <v>3264</v>
+        <v>3632</v>
       </c>
       <c r="D4787" s="0">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row outlineLevel="0" r="4788">
       <c r="A4788" s="0">
-        <v>5643</v>
+        <v>6132</v>
       </c>
       <c r="B4788" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4788" s="0">
-        <v>3270</v>
+        <v>3633</v>
       </c>
       <c r="D4788" s="0">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row outlineLevel="0" r="4789">
       <c r="A4789" s="0">
-        <v>5644</v>
+        <v>6133</v>
       </c>
       <c r="B4789" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4789" s="0">
-        <v>3268</v>
+        <v>3634</v>
       </c>
       <c r="D4789" s="0">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row outlineLevel="0" r="4790">
       <c r="A4790" s="0">
-        <v>5645</v>
+        <v>6134</v>
       </c>
       <c r="B4790" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4790" s="0">
-        <v>3289</v>
+        <v>3635</v>
       </c>
       <c r="D4790" s="0">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row outlineLevel="0" r="4791">
       <c r="A4791" s="0">
-        <v>5646</v>
+        <v>6135</v>
       </c>
       <c r="B4791" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4791" s="0">
-        <v>3295</v>
+        <v>3636</v>
       </c>
       <c r="D4791" s="0">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row outlineLevel="0" r="4792">
       <c r="A4792" s="0">
-        <v>5647</v>
+        <v>6136</v>
       </c>
       <c r="B4792" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4792" s="0">
-        <v>3272</v>
+        <v>3637</v>
       </c>
       <c r="D4792" s="0">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row outlineLevel="0" r="4793">
       <c r="A4793" s="0">
-        <v>5648</v>
+        <v>6137</v>
       </c>
       <c r="B4793" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4793" s="0">
-        <v>3279</v>
+        <v>3638</v>
       </c>
       <c r="D4793" s="0">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row outlineLevel="0" r="4794">
       <c r="A4794" s="0">
-        <v>5649</v>
+        <v>6138</v>
       </c>
       <c r="B4794" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4794" s="0">
-        <v>3278</v>
+        <v>3639</v>
       </c>
       <c r="D4794" s="0">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row outlineLevel="0" r="4795">
       <c r="A4795" s="0">
-        <v>5650</v>
+        <v>6139</v>
       </c>
       <c r="B4795" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4795" s="0">
-        <v>3282</v>
+        <v>3640</v>
       </c>
       <c r="D4795" s="0">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row outlineLevel="0" r="4796">
       <c r="A4796" s="0">
-        <v>5651</v>
+        <v>6140</v>
       </c>
       <c r="B4796" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4796" s="0">
-        <v>3284</v>
+        <v>3641</v>
       </c>
       <c r="D4796" s="0">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row outlineLevel="0" r="4797">
       <c r="A4797" s="0">
-        <v>5652</v>
+        <v>6141</v>
       </c>
       <c r="B4797" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4797" s="0">
-        <v>3290</v>
+        <v>3642</v>
       </c>
       <c r="D4797" s="0">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row outlineLevel="0" r="4798">
       <c r="A4798" s="0">
-        <v>5653</v>
+        <v>6142</v>
       </c>
       <c r="B4798" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4798" s="0">
-        <v>3293</v>
+        <v>3643</v>
       </c>
       <c r="D4798" s="0">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row outlineLevel="0" r="4799">
       <c r="A4799" s="0">
-        <v>5654</v>
+        <v>6143</v>
       </c>
       <c r="B4799" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4799" s="0">
-        <v>3294</v>
+        <v>3644</v>
       </c>
       <c r="D4799" s="0">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row outlineLevel="0" r="4800">
       <c r="A4800" s="0">
-        <v>5655</v>
+        <v>6144</v>
       </c>
       <c r="B4800" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4800" s="0">
-        <v>3274</v>
+        <v>3645</v>
       </c>
       <c r="D4800" s="0">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row outlineLevel="0" r="4801">
       <c r="A4801" s="0">
-        <v>5656</v>
+        <v>6145</v>
       </c>
       <c r="B4801" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4801" s="0">
-        <v>3296</v>
+        <v>3646</v>
       </c>
       <c r="D4801" s="0">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row outlineLevel="0" r="4802">
       <c r="A4802" s="0">
-        <v>5657</v>
+        <v>6146</v>
       </c>
       <c r="B4802" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4802" s="0">
-        <v>3297</v>
+        <v>3647</v>
       </c>
       <c r="D4802" s="0">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row outlineLevel="0" r="4803">
       <c r="A4803" s="0">
-        <v>5658</v>
+        <v>6147</v>
       </c>
       <c r="B4803" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4803" s="0">
-        <v>3300</v>
+        <v>3648</v>
       </c>
       <c r="D4803" s="0">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row outlineLevel="0" r="4804">
       <c r="A4804" s="0">
-        <v>5659</v>
+        <v>6148</v>
       </c>
       <c r="B4804" s="0">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4804" s="0">
-        <v>3280</v>
+        <v>3649</v>
       </c>
       <c r="D4804" s="0">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row outlineLevel="0" r="4805">
       <c r="A4805" s="0">
-        <v>5660</v>
+        <v>6149</v>
       </c>
       <c r="B4805" s="0">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C4805" s="0">
-        <v>3301</v>
+        <v>3650</v>
       </c>
       <c r="D4805" s="0">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row outlineLevel="0" r="4806">
       <c r="A4806" s="0">
-        <v>5661</v>
+        <v>6150</v>
       </c>
       <c r="B4806" s="0">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C4806" s="0">
-        <v>3302</v>
+        <v>3651</v>
       </c>
       <c r="D4806" s="0">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row outlineLevel="0" r="4807">
       <c r="A4807" s="0">
-        <v>5662</v>
+        <v>6151</v>
       </c>
       <c r="B4807" s="0">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C4807" s="0">
-        <v>3303</v>
+        <v>3652</v>
       </c>
       <c r="D4807" s="0">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row outlineLevel="0" r="4808">
       <c r="A4808" s="0">
-        <v>5663</v>
+        <v>6152</v>
       </c>
       <c r="B4808" s="0">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C4808" s="0">
-        <v>3304</v>
+        <v>3653</v>
       </c>
       <c r="D4808" s="0">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row outlineLevel="0" r="4809">
       <c r="A4809" s="0">
-        <v>5664</v>
+        <v>6153</v>
       </c>
       <c r="B4809" s="0">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C4809" s="0">
-        <v>3305</v>
+        <v>3654</v>
       </c>
       <c r="D4809" s="0">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row outlineLevel="0" r="4810">
       <c r="A4810" s="0">
-        <v>5665</v>
+        <v>6154</v>
       </c>
       <c r="B4810" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4810" s="0">
-        <v>3306</v>
+        <v>3609</v>
       </c>
       <c r="D4810" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="4811">
       <c r="A4811" s="0">
-        <v>5666</v>
+        <v>6155</v>
       </c>
       <c r="B4811" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4811" s="0">
-        <v>3307</v>
+        <v>3611</v>
       </c>
       <c r="D4811" s="0">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row outlineLevel="0" r="4812">
       <c r="A4812" s="0">
-        <v>5667</v>
+        <v>6156</v>
       </c>
       <c r="B4812" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4812" s="0">
-        <v>3308</v>
+        <v>3612</v>
       </c>
       <c r="D4812" s="0">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row outlineLevel="0" r="4813">
       <c r="A4813" s="0">
-        <v>5668</v>
+        <v>6157</v>
       </c>
       <c r="B4813" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4813" s="0">
-        <v>3309</v>
+        <v>3613</v>
       </c>
       <c r="D4813" s="0">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row outlineLevel="0" r="4814">
       <c r="A4814" s="0">
-        <v>5669</v>
+        <v>6158</v>
       </c>
       <c r="B4814" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4814" s="0">
-        <v>3310</v>
+        <v>3620</v>
       </c>
       <c r="D4814" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="4815">
       <c r="A4815" s="0">
-        <v>5670</v>
+        <v>6159</v>
       </c>
       <c r="B4815" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4815" s="0">
-        <v>3311</v>
+        <v>3640</v>
       </c>
       <c r="D4815" s="0">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row outlineLevel="0" r="4816">
       <c r="A4816" s="0">
-        <v>5671</v>
+        <v>6160</v>
       </c>
       <c r="B4816" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4816" s="0">
-        <v>3312</v>
+        <v>3639</v>
       </c>
       <c r="D4816" s="0">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="4817">
       <c r="A4817" s="0">
-        <v>5672</v>
+        <v>6161</v>
       </c>
       <c r="B4817" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4817" s="0">
-        <v>3313</v>
+        <v>3618</v>
       </c>
       <c r="D4817" s="0">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row outlineLevel="0" r="4818">
       <c r="A4818" s="0">
-        <v>5673</v>
+        <v>6162</v>
       </c>
       <c r="B4818" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4818" s="0">
-        <v>3314</v>
+        <v>3624</v>
       </c>
       <c r="D4818" s="0">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row outlineLevel="0" r="4819">
       <c r="A4819" s="0">
-        <v>5674</v>
+        <v>6163</v>
       </c>
       <c r="B4819" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4819" s="0">
-        <v>3315</v>
+        <v>3622</v>
       </c>
       <c r="D4819" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row outlineLevel="0" r="4820">
       <c r="A4820" s="0">
-        <v>5675</v>
+        <v>6164</v>
       </c>
       <c r="B4820" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4820" s="0">
-        <v>3316</v>
+        <v>3643</v>
       </c>
       <c r="D4820" s="0">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row outlineLevel="0" r="4821">
       <c r="A4821" s="0">
-        <v>5676</v>
+        <v>6165</v>
       </c>
       <c r="B4821" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4821" s="0">
-        <v>3317</v>
+        <v>3649</v>
       </c>
       <c r="D4821" s="0">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row outlineLevel="0" r="4822">
       <c r="A4822" s="0">
-        <v>5677</v>
+        <v>6166</v>
       </c>
       <c r="B4822" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4822" s="0">
-        <v>3318</v>
+        <v>3626</v>
       </c>
       <c r="D4822" s="0">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row outlineLevel="0" r="4823">
       <c r="A4823" s="0">
-        <v>5678</v>
+        <v>6167</v>
       </c>
       <c r="B4823" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4823" s="0">
-        <v>3319</v>
+        <v>3633</v>
       </c>
       <c r="D4823" s="0">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row outlineLevel="0" r="4824">
       <c r="A4824" s="0">
-        <v>5679</v>
+        <v>6168</v>
       </c>
       <c r="B4824" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4824" s="0">
-        <v>3320</v>
+        <v>3632</v>
       </c>
       <c r="D4824" s="0">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row outlineLevel="0" r="4825">
       <c r="A4825" s="0">
-        <v>5680</v>
+        <v>6169</v>
       </c>
       <c r="B4825" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4825" s="0">
-        <v>3321</v>
+        <v>3636</v>
       </c>
       <c r="D4825" s="0">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row outlineLevel="0" r="4826">
       <c r="A4826" s="0">
-        <v>5681</v>
+        <v>6170</v>
       </c>
       <c r="B4826" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4826" s="0">
-        <v>3322</v>
+        <v>3638</v>
       </c>
       <c r="D4826" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row outlineLevel="0" r="4827">
       <c r="A4827" s="0">
-        <v>5682</v>
+        <v>6171</v>
       </c>
       <c r="B4827" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4827" s="0">
-        <v>3323</v>
+        <v>3644</v>
       </c>
       <c r="D4827" s="0">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row outlineLevel="0" r="4828">
       <c r="A4828" s="0">
-        <v>5683</v>
+        <v>6172</v>
       </c>
       <c r="B4828" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4828" s="0">
-        <v>3324</v>
+        <v>3647</v>
       </c>
       <c r="D4828" s="0">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row outlineLevel="0" r="4829">
       <c r="A4829" s="0">
-        <v>5684</v>
+        <v>6173</v>
       </c>
       <c r="B4829" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4829" s="0">
-        <v>3325</v>
+        <v>3648</v>
       </c>
       <c r="D4829" s="0">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row outlineLevel="0" r="4830">
       <c r="A4830" s="0">
-        <v>5685</v>
+        <v>6174</v>
       </c>
       <c r="B4830" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4830" s="0">
-        <v>3326</v>
+        <v>3628</v>
       </c>
       <c r="D4830" s="0">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row outlineLevel="0" r="4831">
       <c r="A4831" s="0">
-        <v>5686</v>
+        <v>6175</v>
       </c>
       <c r="B4831" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4831" s="0">
-        <v>3327</v>
+        <v>3650</v>
       </c>
       <c r="D4831" s="0">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="4832">
       <c r="A4832" s="0">
-        <v>5687</v>
+        <v>6176</v>
       </c>
       <c r="B4832" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4832" s="0">
-        <v>3328</v>
+        <v>3651</v>
       </c>
       <c r="D4832" s="0">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row outlineLevel="0" r="4833">
       <c r="A4833" s="0">
-        <v>5688</v>
+        <v>6177</v>
       </c>
       <c r="B4833" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4833" s="0">
-        <v>3329</v>
+        <v>3654</v>
       </c>
       <c r="D4833" s="0">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row outlineLevel="0" r="4834">
       <c r="A4834" s="0">
-        <v>5689</v>
+        <v>6178</v>
       </c>
       <c r="B4834" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4834" s="0">
-        <v>3330</v>
+        <v>3634</v>
       </c>
       <c r="D4834" s="0">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row outlineLevel="0" r="4835">
       <c r="A4835" s="0">
-        <v>5690</v>
+        <v>6179</v>
       </c>
       <c r="B4835" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4835" s="0">
-        <v>3331</v>
+        <v>3537</v>
       </c>
       <c r="D4835" s="0">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="4836">
       <c r="A4836" s="0">
-        <v>5691</v>
+        <v>6180</v>
       </c>
       <c r="B4836" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4836" s="0">
-        <v>3332</v>
+        <v>3584</v>
       </c>
       <c r="D4836" s="0">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row outlineLevel="0" r="4837">
       <c r="A4837" s="0">
-        <v>5692</v>
+        <v>6181</v>
       </c>
       <c r="B4837" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4837" s="0">
-        <v>3333</v>
+        <v>3540</v>
       </c>
       <c r="D4837" s="0">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row outlineLevel="0" r="4838">
       <c r="A4838" s="0">
-        <v>5693</v>
+        <v>6182</v>
       </c>
       <c r="B4838" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4838" s="0">
-        <v>3334</v>
+        <v>3541</v>
       </c>
       <c r="D4838" s="0">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row outlineLevel="0" r="4839">
       <c r="A4839" s="0">
-        <v>5694</v>
+        <v>6183</v>
       </c>
       <c r="B4839" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4839" s="0">
-        <v>3335</v>
+        <v>3548</v>
       </c>
       <c r="D4839" s="0">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="4840">
       <c r="A4840" s="0">
-        <v>5695</v>
+        <v>6184</v>
       </c>
       <c r="B4840" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4840" s="0">
-        <v>3336</v>
+        <v>3568</v>
       </c>
       <c r="D4840" s="0">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row outlineLevel="0" r="4841">
       <c r="A4841" s="0">
-        <v>5696</v>
+        <v>6185</v>
       </c>
       <c r="B4841" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4841" s="0">
-        <v>3337</v>
+        <v>3589</v>
       </c>
       <c r="D4841" s="0">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="4842">
       <c r="A4842" s="0">
-        <v>5697</v>
+        <v>6186</v>
       </c>
       <c r="B4842" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4842" s="0">
-        <v>3338</v>
+        <v>3546</v>
       </c>
       <c r="D4842" s="0">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row outlineLevel="0" r="4843">
       <c r="A4843" s="0">
-        <v>5698</v>
+        <v>6187</v>
       </c>
       <c r="B4843" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4843" s="0">
-        <v>3339</v>
+        <v>3552</v>
       </c>
       <c r="D4843" s="0">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row outlineLevel="0" r="4844">
       <c r="A4844" s="0">
-        <v>5699</v>
+        <v>6188</v>
       </c>
       <c r="B4844" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4844" s="0">
-        <v>3340</v>
+        <v>3550</v>
       </c>
       <c r="D4844" s="0">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row outlineLevel="0" r="4845">
       <c r="A4845" s="0">
-        <v>5700</v>
+        <v>6189</v>
       </c>
       <c r="B4845" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4845" s="0">
-        <v>3341</v>
+        <v>3571</v>
       </c>
       <c r="D4845" s="0">
-        <v>41</v>
+        <v>11</v>
       </c>
     </row>
     <row outlineLevel="0" r="4846">
       <c r="A4846" s="0">
-        <v>5701</v>
+        <v>6190</v>
       </c>
       <c r="B4846" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4846" s="0">
-        <v>3342</v>
+        <v>3577</v>
       </c>
       <c r="D4846" s="0">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row outlineLevel="0" r="4847">
       <c r="A4847" s="0">
-        <v>5702</v>
+        <v>6191</v>
       </c>
       <c r="B4847" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4847" s="0">
-        <v>3343</v>
+        <v>3595</v>
       </c>
       <c r="D4847" s="0">
-        <v>43</v>
+        <v>13</v>
       </c>
     </row>
     <row outlineLevel="0" r="4848">
       <c r="A4848" s="0">
-        <v>5703</v>
+        <v>6192</v>
       </c>
       <c r="B4848" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4848" s="0">
-        <v>3344</v>
+        <v>3561</v>
       </c>
       <c r="D4848" s="0">
-        <v>44</v>
+        <v>14</v>
       </c>
     </row>
     <row outlineLevel="0" r="4849">
       <c r="A4849" s="0">
-        <v>5704</v>
+        <v>6193</v>
       </c>
       <c r="B4849" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4849" s="0">
-        <v>3345</v>
+        <v>3560</v>
       </c>
       <c r="D4849" s="0">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row outlineLevel="0" r="4850">
       <c r="A4850" s="0">
-        <v>5705</v>
+        <v>6194</v>
       </c>
       <c r="B4850" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4850" s="0">
-        <v>3346</v>
+        <v>3598</v>
       </c>
       <c r="D4850" s="0">
-        <v>46</v>
+        <v>16</v>
       </c>
     </row>
     <row outlineLevel="0" r="4851">
       <c r="A4851" s="0">
-        <v>5706</v>
+        <v>6195</v>
       </c>
       <c r="B4851" s="0">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4851" s="0">
-        <v>3347</v>
+        <v>3599</v>
       </c>
       <c r="D4851" s="0">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
     <row outlineLevel="0" r="4852">
       <c r="A4852" s="0">
-        <v>5707</v>
+        <v>6196</v>
       </c>
       <c r="B4852" s="0">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C4852" s="0">
-        <v>3302</v>
+        <v>3572</v>
       </c>
       <c r="D4852" s="0">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row outlineLevel="0" r="4853">
       <c r="A4853" s="0">
-        <v>5708</v>
+        <v>6197</v>
       </c>
       <c r="B4853" s="0">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C4853" s="0">
-        <v>3304</v>
+        <v>3601</v>
       </c>
       <c r="D4853" s="0">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row outlineLevel="0" r="4854">
       <c r="A4854" s="0">
-        <v>5709</v>
+        <v>6198</v>
       </c>
       <c r="B4854" s="0">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C4854" s="0">
-        <v>3305</v>
+        <v>3602</v>
       </c>
       <c r="D4854" s="0">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row outlineLevel="0" r="4855">
       <c r="A4855" s="0">
-        <v>5710</v>
+        <v>6199</v>
       </c>
       <c r="B4855" s="0">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C4855" s="0">
-        <v>3306</v>
+        <v>3556</v>
       </c>
       <c r="D4855" s="0">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row outlineLevel="0" r="4856">
       <c r="A4856" s="0">
-        <v>5711</v>
+        <v>6200</v>
       </c>
       <c r="B4856" s="0">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C4856" s="0">
-        <v>3313</v>
+        <v>3604</v>
       </c>
       <c r="D4856" s="0">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="4857">
       <c r="A4857" s="0">
-        <v>5712</v>
+        <v>6201</v>
       </c>
       <c r="B4857" s="0">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C4857" s="0">
-        <v>3333</v>
+        <v>3579</v>
       </c>
       <c r="D4857" s="0">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row outlineLevel="0" r="4858">
       <c r="A4858" s="0">
-        <v>5713</v>
+        <v>6202</v>
       </c>
       <c r="B4858" s="0">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C4858" s="0">
-        <v>3332</v>
+        <v>3606</v>
       </c>
       <c r="D4858" s="0">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row outlineLevel="0" r="4859">
       <c r="A4859" s="0">
-        <v>5714</v>
+        <v>6203</v>
       </c>
       <c r="B4859" s="0">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C4859" s="0">
-        <v>3311</v>
+        <v>3562</v>
       </c>
       <c r="D4859" s="0">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row outlineLevel="0" r="4860">
       <c r="A4860" s="0">
-        <v>5715</v>
+        <v>6204</v>
       </c>
       <c r="B4860" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4860" s="0">
-        <v>3317</v>
+        <v>84</v>
       </c>
       <c r="D4860" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="4861">
       <c r="A4861" s="0">
-        <v>5716</v>
+        <v>6205</v>
       </c>
       <c r="B4861" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4861" s="0">
-        <v>3315</v>
+        <v>59</v>
       </c>
       <c r="D4861" s="0">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row outlineLevel="0" r="4862">
       <c r="A4862" s="0">
-        <v>5717</v>
+        <v>6206</v>
       </c>
       <c r="B4862" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4862" s="0">
-        <v>3336</v>
+        <v>3657</v>
       </c>
       <c r="D4862" s="0">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row outlineLevel="0" r="4863">
       <c r="A4863" s="0">
-        <v>5718</v>
+        <v>6207</v>
       </c>
       <c r="B4863" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4863" s="0">
-        <v>3342</v>
+        <v>3658</v>
       </c>
       <c r="D4863" s="0">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row outlineLevel="0" r="4864">
       <c r="A4864" s="0">
-        <v>5719</v>
+        <v>6208</v>
       </c>
       <c r="B4864" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4864" s="0">
-        <v>3319</v>
+        <v>54</v>
       </c>
       <c r="D4864" s="0">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="4865">
       <c r="A4865" s="0">
-        <v>5720</v>
+        <v>6209</v>
       </c>
       <c r="B4865" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4865" s="0">
-        <v>3326</v>
+        <v>57</v>
       </c>
       <c r="D4865" s="0">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row outlineLevel="0" r="4866">
       <c r="A4866" s="0">
-        <v>5721</v>
+        <v>6210</v>
       </c>
       <c r="B4866" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4866" s="0">
-        <v>3325</v>
+        <v>73</v>
       </c>
       <c r="D4866" s="0">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="4867">
       <c r="A4867" s="0">
-        <v>5722</v>
+        <v>6211</v>
       </c>
       <c r="B4867" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4867" s="0">
-        <v>3329</v>
+        <v>3662</v>
       </c>
       <c r="D4867" s="0">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row outlineLevel="0" r="4868">
       <c r="A4868" s="0">
-        <v>5723</v>
+        <v>6212</v>
       </c>
       <c r="B4868" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4868" s="0">
-        <v>3331</v>
+        <v>55</v>
       </c>
       <c r="D4868" s="0">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row outlineLevel="0" r="4869">
       <c r="A4869" s="0">
-        <v>5724</v>
+        <v>6213</v>
       </c>
       <c r="B4869" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4869" s="0">
-        <v>3337</v>
+        <v>3664</v>
       </c>
       <c r="D4869" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row outlineLevel="0" r="4870">
       <c r="A4870" s="0">
-        <v>5725</v>
+        <v>6214</v>
       </c>
       <c r="B4870" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4870" s="0">
-        <v>3340</v>
+        <v>68</v>
       </c>
       <c r="D4870" s="0">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row outlineLevel="0" r="4871">
       <c r="A4871" s="0">
-        <v>5726</v>
+        <v>6215</v>
       </c>
       <c r="B4871" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4871" s="0">
-        <v>3341</v>
+        <v>93</v>
       </c>
       <c r="D4871" s="0">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row outlineLevel="0" r="4872">
       <c r="A4872" s="0">
-        <v>5727</v>
+        <v>6216</v>
       </c>
       <c r="B4872" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4872" s="0">
-        <v>3321</v>
+        <v>89</v>
       </c>
       <c r="D4872" s="0">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row outlineLevel="0" r="4873">
       <c r="A4873" s="0">
-        <v>5728</v>
+        <v>6217</v>
       </c>
       <c r="B4873" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4873" s="0">
-        <v>3343</v>
+        <v>3668</v>
       </c>
       <c r="D4873" s="0">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row outlineLevel="0" r="4874">
       <c r="A4874" s="0">
-        <v>5729</v>
+        <v>6218</v>
       </c>
       <c r="B4874" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4874" s="0">
-        <v>3344</v>
+        <v>3669</v>
       </c>
       <c r="D4874" s="0">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row outlineLevel="0" r="4875">
       <c r="A4875" s="0">
-        <v>5730</v>
+        <v>6219</v>
       </c>
       <c r="B4875" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4875" s="0">
-        <v>3347</v>
+        <v>3670</v>
       </c>
       <c r="D4875" s="0">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row outlineLevel="0" r="4876">
       <c r="A4876" s="0">
-        <v>5731</v>
+        <v>6220</v>
       </c>
       <c r="B4876" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4876" s="0">
-        <v>3327</v>
+        <v>3671</v>
       </c>
       <c r="D4876" s="0">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row outlineLevel="0" r="4877">
       <c r="A4877" s="0">
-        <v>5904</v>
+        <v>6221</v>
       </c>
       <c r="B4877" s="0">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C4877" s="0">
-        <v>3455</v>
+        <v>79</v>
       </c>
       <c r="D4877" s="0">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row outlineLevel="0" r="4878">
       <c r="A4878" s="0">
-        <v>5905</v>
+        <v>6222</v>
       </c>
       <c r="B4878" s="0">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C4878" s="0">
-        <v>3456</v>
+        <v>63</v>
       </c>
       <c r="D4878" s="0">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row outlineLevel="0" r="4879">
       <c r="A4879" s="0">
-        <v>5906</v>
+        <v>6223</v>
       </c>
       <c r="B4879" s="0">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C4879" s="0">
-        <v>3457</v>
+        <v>88</v>
       </c>
       <c r="D4879" s="0">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row outlineLevel="0" r="4880">
       <c r="A4880" s="0">
-        <v>5907</v>
+        <v>6224</v>
       </c>
       <c r="B4880" s="0">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C4880" s="0">
-        <v>3458</v>
+        <v>60</v>
       </c>
       <c r="D4880" s="0">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row outlineLevel="0" r="4881">
       <c r="A4881" s="0">
-        <v>5908</v>
+        <v>6225</v>
       </c>
       <c r="B4881" s="0">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C4881" s="0">
-        <v>3459</v>
+        <v>3676</v>
       </c>
       <c r="D4881" s="0">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="4882">
       <c r="A4882" s="0">
-        <v>5909</v>
+        <v>6226</v>
       </c>
       <c r="B4882" s="0">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C4882" s="0">
-        <v>3460</v>
+        <v>3677</v>
       </c>
       <c r="D4882" s="0">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row outlineLevel="0" r="4883">
       <c r="A4883" s="0">
-        <v>5910</v>
+        <v>6227</v>
       </c>
       <c r="B4883" s="0">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C4883" s="0">
-        <v>3461</v>
+        <v>3678</v>
       </c>
       <c r="D4883" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row outlineLevel="0" r="4884">
       <c r="A4884" s="0">
-        <v>5911</v>
+        <v>6228</v>
       </c>
       <c r="B4884" s="0">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C4884" s="0">
-        <v>3462</v>
+        <v>52</v>
       </c>
       <c r="D4884" s="0">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row outlineLevel="0" r="4885">
       <c r="A4885" s="0">
-        <v>5912</v>
+        <v>6229</v>
       </c>
       <c r="B4885" s="0">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C4885" s="0">
-        <v>3463</v>
+        <v>77</v>
       </c>
       <c r="D4885" s="0">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row outlineLevel="0" r="4886">
       <c r="A4886" s="0">
-        <v>5913</v>
+        <v>5578</v>
       </c>
       <c r="B4886" s="0">
-        <v>172</v>
+        <v>110</v>
       </c>
       <c r="C4886" s="0">
-        <v>3464</v>
+        <v>3248</v>
       </c>
       <c r="D4886" s="0">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row outlineLevel="0" r="4887">
       <c r="A4887" s="0">
-        <v>5914</v>
+        <v>5579</v>
       </c>
       <c r="B4887" s="0">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="C4887" s="0">
-        <v>3465</v>
+        <v>3248</v>
       </c>
       <c r="D4887" s="0">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row outlineLevel="0" r="4888">
       <c r="A4888" s="0">
-        <v>5915</v>
+        <v>5580</v>
       </c>
       <c r="B4888" s="0">
-        <v>172</v>
+        <v>110</v>
       </c>
       <c r="C4888" s="0">
-        <v>3466</v>
+        <v>3249</v>
       </c>
       <c r="D4888" s="0">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row outlineLevel="0" r="4889">
       <c r="A4889" s="0">
-        <v>5916</v>
+        <v>5581</v>
       </c>
       <c r="B4889" s="0">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="C4889" s="0">
-        <v>3467</v>
+        <v>3249</v>
       </c>
       <c r="D4889" s="0">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="4890">
       <c r="A4890" s="0">
-        <v>5917</v>
+        <v>5582</v>
       </c>
       <c r="B4890" s="0">
-        <v>172</v>
+        <v>110</v>
       </c>
       <c r="C4890" s="0">
-        <v>3468</v>
+        <v>3250</v>
       </c>
       <c r="D4890" s="0">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row outlineLevel="0" r="4891">
       <c r="A4891" s="0">
-        <v>5918</v>
+        <v>5583</v>
       </c>
       <c r="B4891" s="0">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="C4891" s="0">
-        <v>3469</v>
+        <v>3250</v>
       </c>
       <c r="D4891" s="0">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row outlineLevel="0" r="4892">
       <c r="A4892" s="0">
-        <v>5919</v>
+        <v>5584</v>
       </c>
       <c r="B4892" s="0">
-        <v>172</v>
+        <v>110</v>
       </c>
       <c r="C4892" s="0">
-        <v>3470</v>
+        <v>3251</v>
       </c>
       <c r="D4892" s="0">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row outlineLevel="0" r="4893">
       <c r="A4893" s="0">
-        <v>5920</v>
+        <v>5585</v>
       </c>
       <c r="B4893" s="0">
-        <v>172</v>
+        <v>110</v>
       </c>
       <c r="C4893" s="0">
-        <v>3471</v>
+        <v>3252</v>
       </c>
       <c r="D4893" s="0">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row outlineLevel="0" r="4894">
       <c r="A4894" s="0">
-        <v>5921</v>
+        <v>5586</v>
       </c>
       <c r="B4894" s="0">
-        <v>172</v>
+        <v>110</v>
       </c>
       <c r="C4894" s="0">
-        <v>3472</v>
+        <v>3253</v>
       </c>
       <c r="D4894" s="0">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row outlineLevel="0" r="4895">
       <c r="A4895" s="0">
-        <v>5922</v>
+        <v>5587</v>
       </c>
       <c r="B4895" s="0">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="C4895" s="0">
-        <v>3473</v>
+        <v>3253</v>
       </c>
       <c r="D4895" s="0">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row outlineLevel="0" r="4896">
       <c r="A4896" s="0">
-        <v>5923</v>
+        <v>5588</v>
       </c>
       <c r="B4896" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4896" s="0">
-        <v>3474</v>
+        <v>3254</v>
       </c>
       <c r="D4896" s="0">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="4897">
       <c r="A4897" s="0">
-        <v>5924</v>
+        <v>5589</v>
       </c>
       <c r="B4897" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4897" s="0">
-        <v>3475</v>
+        <v>3255</v>
       </c>
       <c r="D4897" s="0">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row outlineLevel="0" r="4898">
       <c r="A4898" s="0">
-        <v>5925</v>
+        <v>5590</v>
       </c>
       <c r="B4898" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4898" s="0">
-        <v>3476</v>
+        <v>3256</v>
       </c>
       <c r="D4898" s="0">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row outlineLevel="0" r="4899">
       <c r="A4899" s="0">
-        <v>5926</v>
+        <v>5591</v>
       </c>
       <c r="B4899" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4899" s="0">
-        <v>3477</v>
+        <v>3257</v>
       </c>
       <c r="D4899" s="0">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row outlineLevel="0" r="4900">
       <c r="A4900" s="0">
-        <v>5927</v>
+        <v>5592</v>
       </c>
       <c r="B4900" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4900" s="0">
-        <v>3478</v>
+        <v>3258</v>
       </c>
       <c r="D4900" s="0">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="4901">
       <c r="A4901" s="0">
-        <v>5928</v>
+        <v>5593</v>
       </c>
       <c r="B4901" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4901" s="0">
-        <v>3479</v>
+        <v>3259</v>
       </c>
       <c r="D4901" s="0">
-        <v>38</v>
+        <v>6</v>
       </c>
     </row>
     <row outlineLevel="0" r="4902">
       <c r="A4902" s="0">
-        <v>5929</v>
+        <v>5594</v>
       </c>
       <c r="B4902" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4902" s="0">
-        <v>3480</v>
+        <v>3260</v>
       </c>
       <c r="D4902" s="0">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="4903">
       <c r="A4903" s="0">
-        <v>5930</v>
+        <v>5595</v>
       </c>
       <c r="B4903" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4903" s="0">
-        <v>3481</v>
+        <v>3261</v>
       </c>
       <c r="D4903" s="0">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row outlineLevel="0" r="4904">
       <c r="A4904" s="0">
-        <v>5931</v>
+        <v>5596</v>
       </c>
       <c r="B4904" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4904" s="0">
-        <v>3482</v>
+        <v>3262</v>
       </c>
       <c r="D4904" s="0">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row outlineLevel="0" r="4905">
       <c r="A4905" s="0">
-        <v>5932</v>
+        <v>5597</v>
       </c>
       <c r="B4905" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4905" s="0">
-        <v>3483</v>
+        <v>3263</v>
       </c>
       <c r="D4905" s="0">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row outlineLevel="0" r="4906">
       <c r="A4906" s="0">
-        <v>5933</v>
+        <v>5598</v>
       </c>
       <c r="B4906" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4906" s="0">
-        <v>3484</v>
+        <v>3264</v>
       </c>
       <c r="D4906" s="0">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row outlineLevel="0" r="4907">
       <c r="A4907" s="0">
-        <v>5934</v>
+        <v>5599</v>
       </c>
       <c r="B4907" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4907" s="0">
-        <v>3485</v>
+        <v>3265</v>
       </c>
       <c r="D4907" s="0">
-        <v>44</v>
+        <v>12</v>
       </c>
     </row>
     <row outlineLevel="0" r="4908">
       <c r="A4908" s="0">
-        <v>5935</v>
+        <v>5600</v>
       </c>
       <c r="B4908" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4908" s="0">
-        <v>3486</v>
+        <v>3266</v>
       </c>
       <c r="D4908" s="0">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row outlineLevel="0" r="4909">
       <c r="A4909" s="0">
-        <v>5936</v>
+        <v>5601</v>
       </c>
       <c r="B4909" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4909" s="0">
-        <v>3487</v>
+        <v>3267</v>
       </c>
       <c r="D4909" s="0">
-        <v>46</v>
+        <v>14</v>
       </c>
     </row>
     <row outlineLevel="0" r="4910">
       <c r="A4910" s="0">
-        <v>5937</v>
+        <v>5602</v>
       </c>
       <c r="B4910" s="0">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C4910" s="0">
-        <v>3488</v>
+        <v>3268</v>
       </c>
       <c r="D4910" s="0">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row outlineLevel="0" r="4911">
       <c r="A4911" s="0">
-        <v>5938</v>
+        <v>5603</v>
       </c>
       <c r="B4911" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4911" s="0">
-        <v>3443</v>
+        <v>3269</v>
       </c>
       <c r="D4911" s="0">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row outlineLevel="0" r="4912">
       <c r="A4912" s="0">
-        <v>5939</v>
+        <v>5604</v>
       </c>
       <c r="B4912" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4912" s="0">
-        <v>3445</v>
+        <v>3270</v>
       </c>
       <c r="D4912" s="0">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row outlineLevel="0" r="4913">
       <c r="A4913" s="0">
-        <v>5940</v>
+        <v>5605</v>
       </c>
       <c r="B4913" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4913" s="0">
-        <v>3446</v>
+        <v>3271</v>
       </c>
       <c r="D4913" s="0">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row outlineLevel="0" r="4914">
       <c r="A4914" s="0">
-        <v>5941</v>
+        <v>5606</v>
       </c>
       <c r="B4914" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4914" s="0">
-        <v>3447</v>
+        <v>3272</v>
       </c>
       <c r="D4914" s="0">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row outlineLevel="0" r="4915">
       <c r="A4915" s="0">
-        <v>5942</v>
+        <v>5607</v>
       </c>
       <c r="B4915" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4915" s="0">
-        <v>3454</v>
+        <v>3273</v>
       </c>
       <c r="D4915" s="0">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row outlineLevel="0" r="4916">
       <c r="A4916" s="0">
-        <v>5943</v>
+        <v>5608</v>
       </c>
       <c r="B4916" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4916" s="0">
-        <v>3474</v>
+        <v>3274</v>
       </c>
       <c r="D4916" s="0">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row outlineLevel="0" r="4917">
       <c r="A4917" s="0">
-        <v>5944</v>
+        <v>5609</v>
       </c>
       <c r="B4917" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4917" s="0">
-        <v>3473</v>
+        <v>3275</v>
       </c>
       <c r="D4917" s="0">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="4918">
       <c r="A4918" s="0">
-        <v>5945</v>
+        <v>5610</v>
       </c>
       <c r="B4918" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4918" s="0">
-        <v>3452</v>
+        <v>3276</v>
       </c>
       <c r="D4918" s="0">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row outlineLevel="0" r="4919">
       <c r="A4919" s="0">
-        <v>5946</v>
+        <v>5611</v>
       </c>
       <c r="B4919" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4919" s="0">
-        <v>3458</v>
+        <v>3277</v>
       </c>
       <c r="D4919" s="0">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row outlineLevel="0" r="4920">
       <c r="A4920" s="0">
-        <v>5947</v>
+        <v>5612</v>
       </c>
       <c r="B4920" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4920" s="0">
-        <v>3456</v>
+        <v>3278</v>
       </c>
       <c r="D4920" s="0">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row outlineLevel="0" r="4921">
       <c r="A4921" s="0">
-        <v>5948</v>
+        <v>5613</v>
       </c>
       <c r="B4921" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4921" s="0">
-        <v>3477</v>
+        <v>3279</v>
       </c>
       <c r="D4921" s="0">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row outlineLevel="0" r="4922">
       <c r="A4922" s="0">
-        <v>5949</v>
+        <v>5614</v>
       </c>
       <c r="B4922" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4922" s="0">
-        <v>3483</v>
+        <v>3280</v>
       </c>
       <c r="D4922" s="0">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row outlineLevel="0" r="4923">
       <c r="A4923" s="0">
-        <v>5950</v>
+        <v>5615</v>
       </c>
       <c r="B4923" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4923" s="0">
-        <v>3460</v>
+        <v>3281</v>
       </c>
       <c r="D4923" s="0">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row outlineLevel="0" r="4924">
       <c r="A4924" s="0">
-        <v>5951</v>
+        <v>5616</v>
       </c>
       <c r="B4924" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4924" s="0">
-        <v>3467</v>
+        <v>3282</v>
       </c>
       <c r="D4924" s="0">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row outlineLevel="0" r="4925">
       <c r="A4925" s="0">
-        <v>5952</v>
+        <v>5617</v>
       </c>
       <c r="B4925" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4925" s="0">
-        <v>3466</v>
+        <v>3283</v>
       </c>
       <c r="D4925" s="0">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row outlineLevel="0" r="4926">
       <c r="A4926" s="0">
-        <v>5953</v>
+        <v>5618</v>
       </c>
       <c r="B4926" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4926" s="0">
-        <v>3470</v>
+        <v>3284</v>
       </c>
       <c r="D4926" s="0">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row outlineLevel="0" r="4927">
       <c r="A4927" s="0">
-        <v>5954</v>
+        <v>5619</v>
       </c>
       <c r="B4927" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4927" s="0">
-        <v>3472</v>
+        <v>3285</v>
       </c>
       <c r="D4927" s="0">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row outlineLevel="0" r="4928">
       <c r="A4928" s="0">
-        <v>5955</v>
+        <v>5620</v>
       </c>
       <c r="B4928" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4928" s="0">
-        <v>3478</v>
+        <v>3286</v>
       </c>
       <c r="D4928" s="0">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row outlineLevel="0" r="4929">
       <c r="A4929" s="0">
-        <v>5956</v>
+        <v>5621</v>
       </c>
       <c r="B4929" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4929" s="0">
-        <v>3481</v>
+        <v>3287</v>
       </c>
       <c r="D4929" s="0">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row outlineLevel="0" r="4930">
       <c r="A4930" s="0">
-        <v>5957</v>
+        <v>5622</v>
       </c>
       <c r="B4930" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4930" s="0">
-        <v>3482</v>
+        <v>3288</v>
       </c>
       <c r="D4930" s="0">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row outlineLevel="0" r="4931">
       <c r="A4931" s="0">
-        <v>5958</v>
+        <v>5623</v>
       </c>
       <c r="B4931" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4931" s="0">
-        <v>3462</v>
+        <v>3289</v>
       </c>
       <c r="D4931" s="0">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row outlineLevel="0" r="4932">
       <c r="A4932" s="0">
-        <v>5959</v>
+        <v>5624</v>
       </c>
       <c r="B4932" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4932" s="0">
-        <v>3484</v>
+        <v>3290</v>
       </c>
       <c r="D4932" s="0">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row outlineLevel="0" r="4933">
       <c r="A4933" s="0">
-        <v>5960</v>
+        <v>5625</v>
       </c>
       <c r="B4933" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4933" s="0">
-        <v>3485</v>
+        <v>3291</v>
       </c>
       <c r="D4933" s="0">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row outlineLevel="0" r="4934">
       <c r="A4934" s="0">
-        <v>5961</v>
+        <v>5626</v>
       </c>
       <c r="B4934" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4934" s="0">
-        <v>3488</v>
+        <v>3292</v>
       </c>
       <c r="D4934" s="0">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row outlineLevel="0" r="4935">
       <c r="A4935" s="0">
-        <v>5962</v>
+        <v>5627</v>
       </c>
       <c r="B4935" s="0">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4935" s="0">
-        <v>3468</v>
+        <v>3293</v>
       </c>
       <c r="D4935" s="0">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row outlineLevel="0" r="4936">
       <c r="A4936" s="0">
-        <v>5963</v>
+        <v>5628</v>
       </c>
       <c r="B4936" s="0">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C4936" s="0">
-        <v>3489</v>
+        <v>3294</v>
       </c>
       <c r="D4936" s="0">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row outlineLevel="0" r="4937">
       <c r="A4937" s="0">
-        <v>5964</v>
+        <v>5629</v>
       </c>
       <c r="B4937" s="0">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C4937" s="0">
-        <v>3490</v>
+        <v>3295</v>
       </c>
       <c r="D4937" s="0">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row outlineLevel="0" r="4938">
       <c r="A4938" s="0">
-        <v>5965</v>
+        <v>5630</v>
       </c>
       <c r="B4938" s="0">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C4938" s="0">
-        <v>3491</v>
+        <v>3296</v>
       </c>
       <c r="D4938" s="0">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row outlineLevel="0" r="4939">
       <c r="A4939" s="0">
-        <v>5966</v>
+        <v>5631</v>
       </c>
       <c r="B4939" s="0">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C4939" s="0">
-        <v>3492</v>
+        <v>3297</v>
       </c>
       <c r="D4939" s="0">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row outlineLevel="0" r="4940">
       <c r="A4940" s="0">
-        <v>5967</v>
+        <v>5632</v>
       </c>
       <c r="B4940" s="0">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C4940" s="0">
-        <v>3493</v>
+        <v>3298</v>
       </c>
       <c r="D4940" s="0">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row outlineLevel="0" r="4941">
       <c r="A4941" s="0">
-        <v>5968</v>
+        <v>5633</v>
       </c>
       <c r="B4941" s="0">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C4941" s="0">
-        <v>3494</v>
+        <v>3299</v>
       </c>
       <c r="D4941" s="0">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
     <row outlineLevel="0" r="4942">
       <c r="A4942" s="0">
-        <v>5969</v>
+        <v>5634</v>
       </c>
       <c r="B4942" s="0">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C4942" s="0">
-        <v>3495</v>
+        <v>3300</v>
       </c>
       <c r="D4942" s="0">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row outlineLevel="0" r="4943">
       <c r="A4943" s="0">
-        <v>5970</v>
+        <v>5635</v>
       </c>
       <c r="B4943" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4943" s="0">
-        <v>3496</v>
+        <v>3255</v>
       </c>
       <c r="D4943" s="0">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="4944">
       <c r="A4944" s="0">
-        <v>5971</v>
+        <v>5636</v>
       </c>
       <c r="B4944" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4944" s="0">
-        <v>3497</v>
+        <v>3257</v>
       </c>
       <c r="D4944" s="0">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row outlineLevel="0" r="4945">
       <c r="A4945" s="0">
-        <v>5972</v>
+        <v>5637</v>
       </c>
       <c r="B4945" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4945" s="0">
-        <v>3498</v>
+        <v>3258</v>
       </c>
       <c r="D4945" s="0">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row outlineLevel="0" r="4946">
       <c r="A4946" s="0">
-        <v>5973</v>
+        <v>5638</v>
       </c>
       <c r="B4946" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4946" s="0">
-        <v>3499</v>
+        <v>3259</v>
       </c>
       <c r="D4946" s="0">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row outlineLevel="0" r="4947">
       <c r="A4947" s="0">
-        <v>5974</v>
+        <v>5639</v>
       </c>
       <c r="B4947" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4947" s="0">
-        <v>3500</v>
+        <v>3266</v>
       </c>
       <c r="D4947" s="0">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="4948">
       <c r="A4948" s="0">
-        <v>5975</v>
+        <v>5640</v>
       </c>
       <c r="B4948" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4948" s="0">
-        <v>3501</v>
+        <v>3286</v>
       </c>
       <c r="D4948" s="0">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row outlineLevel="0" r="4949">
       <c r="A4949" s="0">
-        <v>5976</v>
+        <v>5641</v>
       </c>
       <c r="B4949" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4949" s="0">
-        <v>3502</v>
+        <v>3285</v>
       </c>
       <c r="D4949" s="0">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="4950">
       <c r="A4950" s="0">
-        <v>5977</v>
+        <v>5642</v>
       </c>
       <c r="B4950" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4950" s="0">
-        <v>3503</v>
+        <v>3264</v>
       </c>
       <c r="D4950" s="0">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row outlineLevel="0" r="4951">
       <c r="A4951" s="0">
-        <v>5978</v>
+        <v>5643</v>
       </c>
       <c r="B4951" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4951" s="0">
-        <v>3504</v>
+        <v>3270</v>
       </c>
       <c r="D4951" s="0">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row outlineLevel="0" r="4952">
       <c r="A4952" s="0">
-        <v>5979</v>
+        <v>5644</v>
       </c>
       <c r="B4952" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4952" s="0">
-        <v>3505</v>
+        <v>3268</v>
       </c>
       <c r="D4952" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row outlineLevel="0" r="4953">
       <c r="A4953" s="0">
-        <v>5980</v>
+        <v>5645</v>
       </c>
       <c r="B4953" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4953" s="0">
-        <v>3506</v>
+        <v>3289</v>
       </c>
       <c r="D4953" s="0">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row outlineLevel="0" r="4954">
       <c r="A4954" s="0">
-        <v>5981</v>
+        <v>5646</v>
       </c>
       <c r="B4954" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4954" s="0">
-        <v>3507</v>
+        <v>3295</v>
       </c>
       <c r="D4954" s="0">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row outlineLevel="0" r="4955">
       <c r="A4955" s="0">
-        <v>5982</v>
+        <v>5647</v>
       </c>
       <c r="B4955" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4955" s="0">
-        <v>3508</v>
+        <v>3272</v>
       </c>
       <c r="D4955" s="0">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row outlineLevel="0" r="4956">
       <c r="A4956" s="0">
-        <v>5983</v>
+        <v>5648</v>
       </c>
       <c r="B4956" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4956" s="0">
-        <v>3509</v>
+        <v>3279</v>
       </c>
       <c r="D4956" s="0">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row outlineLevel="0" r="4957">
       <c r="A4957" s="0">
-        <v>5984</v>
+        <v>5649</v>
       </c>
       <c r="B4957" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4957" s="0">
-        <v>3510</v>
+        <v>3278</v>
       </c>
       <c r="D4957" s="0">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row outlineLevel="0" r="4958">
       <c r="A4958" s="0">
-        <v>5985</v>
+        <v>5650</v>
       </c>
       <c r="B4958" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4958" s="0">
-        <v>3511</v>
+        <v>3282</v>
       </c>
       <c r="D4958" s="0">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row outlineLevel="0" r="4959">
       <c r="A4959" s="0">
-        <v>5986</v>
+        <v>5651</v>
       </c>
       <c r="B4959" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4959" s="0">
-        <v>3512</v>
+        <v>3284</v>
       </c>
       <c r="D4959" s="0">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row outlineLevel="0" r="4960">
       <c r="A4960" s="0">
-        <v>5987</v>
+        <v>5652</v>
       </c>
       <c r="B4960" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4960" s="0">
-        <v>3513</v>
+        <v>3290</v>
       </c>
       <c r="D4960" s="0">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row outlineLevel="0" r="4961">
       <c r="A4961" s="0">
-        <v>5988</v>
+        <v>5653</v>
       </c>
       <c r="B4961" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4961" s="0">
-        <v>3514</v>
+        <v>3293</v>
       </c>
       <c r="D4961" s="0">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row outlineLevel="0" r="4962">
       <c r="A4962" s="0">
-        <v>5989</v>
+        <v>5654</v>
       </c>
       <c r="B4962" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4962" s="0">
-        <v>3515</v>
+        <v>3294</v>
       </c>
       <c r="D4962" s="0">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row outlineLevel="0" r="4963">
       <c r="A4963" s="0">
-        <v>5990</v>
+        <v>5655</v>
       </c>
       <c r="B4963" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4963" s="0">
-        <v>3516</v>
+        <v>3274</v>
       </c>
       <c r="D4963" s="0">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row outlineLevel="0" r="4964">
       <c r="A4964" s="0">
-        <v>5991</v>
+        <v>5656</v>
       </c>
       <c r="B4964" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4964" s="0">
-        <v>3517</v>
+        <v>3296</v>
       </c>
       <c r="D4964" s="0">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="4965">
       <c r="A4965" s="0">
-        <v>5992</v>
+        <v>5657</v>
       </c>
       <c r="B4965" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4965" s="0">
-        <v>3518</v>
+        <v>3297</v>
       </c>
       <c r="D4965" s="0">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row outlineLevel="0" r="4966">
       <c r="A4966" s="0">
-        <v>5993</v>
+        <v>5658</v>
       </c>
       <c r="B4966" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4966" s="0">
-        <v>3519</v>
+        <v>3300</v>
       </c>
       <c r="D4966" s="0">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row outlineLevel="0" r="4967">
       <c r="A4967" s="0">
-        <v>5994</v>
+        <v>5659</v>
       </c>
       <c r="B4967" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C4967" s="0">
-        <v>3520</v>
+        <v>3280</v>
       </c>
       <c r="D4967" s="0">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row outlineLevel="0" r="4968">
       <c r="A4968" s="0">
-        <v>5995</v>
+        <v>5660</v>
       </c>
       <c r="B4968" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4968" s="0">
-        <v>3521</v>
+        <v>3301</v>
       </c>
       <c r="D4968" s="0">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="4969">
       <c r="A4969" s="0">
-        <v>5996</v>
+        <v>5661</v>
       </c>
       <c r="B4969" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4969" s="0">
-        <v>3522</v>
+        <v>3302</v>
       </c>
       <c r="D4969" s="0">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row outlineLevel="0" r="4970">
       <c r="A4970" s="0">
-        <v>5997</v>
+        <v>5662</v>
       </c>
       <c r="B4970" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4970" s="0">
-        <v>3523</v>
+        <v>3303</v>
       </c>
       <c r="D4970" s="0">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row outlineLevel="0" r="4971">
       <c r="A4971" s="0">
-        <v>5998</v>
+        <v>5663</v>
       </c>
       <c r="B4971" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4971" s="0">
-        <v>3524</v>
+        <v>3304</v>
       </c>
       <c r="D4971" s="0">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row outlineLevel="0" r="4972">
       <c r="A4972" s="0">
-        <v>5999</v>
+        <v>5664</v>
       </c>
       <c r="B4972" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4972" s="0">
-        <v>3525</v>
+        <v>3305</v>
       </c>
       <c r="D4972" s="0">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="4973">
       <c r="A4973" s="0">
-        <v>6000</v>
+        <v>5665</v>
       </c>
       <c r="B4973" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4973" s="0">
-        <v>3526</v>
+        <v>3306</v>
       </c>
       <c r="D4973" s="0">
-        <v>38</v>
+        <v>6</v>
       </c>
     </row>
     <row outlineLevel="0" r="4974">
       <c r="A4974" s="0">
-        <v>6001</v>
+        <v>5666</v>
       </c>
       <c r="B4974" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4974" s="0">
-        <v>3527</v>
+        <v>3307</v>
       </c>
       <c r="D4974" s="0">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="4975">
       <c r="A4975" s="0">
-        <v>6002</v>
+        <v>5667</v>
       </c>
       <c r="B4975" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4975" s="0">
-        <v>3528</v>
+        <v>3308</v>
       </c>
       <c r="D4975" s="0">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row outlineLevel="0" r="4976">
       <c r="A4976" s="0">
-        <v>6003</v>
+        <v>5668</v>
       </c>
       <c r="B4976" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4976" s="0">
-        <v>3529</v>
+        <v>3309</v>
       </c>
       <c r="D4976" s="0">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row outlineLevel="0" r="4977">
       <c r="A4977" s="0">
-        <v>6004</v>
+        <v>5669</v>
       </c>
       <c r="B4977" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4977" s="0">
-        <v>3530</v>
+        <v>3310</v>
       </c>
       <c r="D4977" s="0">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row outlineLevel="0" r="4978">
       <c r="A4978" s="0">
-        <v>6005</v>
+        <v>5670</v>
       </c>
       <c r="B4978" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4978" s="0">
-        <v>3531</v>
+        <v>3311</v>
       </c>
       <c r="D4978" s="0">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row outlineLevel="0" r="4979">
       <c r="A4979" s="0">
-        <v>6006</v>
+        <v>5671</v>
       </c>
       <c r="B4979" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4979" s="0">
-        <v>3532</v>
+        <v>3312</v>
       </c>
       <c r="D4979" s="0">
-        <v>44</v>
+        <v>12</v>
       </c>
     </row>
     <row outlineLevel="0" r="4980">
       <c r="A4980" s="0">
-        <v>6007</v>
+        <v>5672</v>
       </c>
       <c r="B4980" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4980" s="0">
-        <v>3533</v>
+        <v>3313</v>
       </c>
       <c r="D4980" s="0">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row outlineLevel="0" r="4981">
       <c r="A4981" s="0">
-        <v>6008</v>
+        <v>5673</v>
       </c>
       <c r="B4981" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4981" s="0">
-        <v>3534</v>
+        <v>3314</v>
       </c>
       <c r="D4981" s="0">
-        <v>46</v>
+        <v>14</v>
       </c>
     </row>
     <row outlineLevel="0" r="4982">
       <c r="A4982" s="0">
-        <v>6009</v>
+        <v>5674</v>
       </c>
       <c r="B4982" s="0">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C4982" s="0">
-        <v>3535</v>
+        <v>3315</v>
       </c>
       <c r="D4982" s="0">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row outlineLevel="0" r="4983">
       <c r="A4983" s="0">
-        <v>6010</v>
+        <v>5675</v>
       </c>
       <c r="B4983" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4983" s="0">
-        <v>3490</v>
+        <v>3316</v>
       </c>
       <c r="D4983" s="0">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row outlineLevel="0" r="4984">
       <c r="A4984" s="0">
-        <v>6011</v>
+        <v>5676</v>
       </c>
       <c r="B4984" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4984" s="0">
-        <v>3492</v>
+        <v>3317</v>
       </c>
       <c r="D4984" s="0">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row outlineLevel="0" r="4985">
       <c r="A4985" s="0">
-        <v>6012</v>
+        <v>5677</v>
       </c>
       <c r="B4985" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4985" s="0">
-        <v>3493</v>
+        <v>3318</v>
       </c>
       <c r="D4985" s="0">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row outlineLevel="0" r="4986">
       <c r="A4986" s="0">
-        <v>6013</v>
+        <v>5678</v>
       </c>
       <c r="B4986" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4986" s="0">
-        <v>3494</v>
+        <v>3319</v>
       </c>
       <c r="D4986" s="0">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row outlineLevel="0" r="4987">
       <c r="A4987" s="0">
-        <v>6014</v>
+        <v>5679</v>
       </c>
       <c r="B4987" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4987" s="0">
-        <v>3501</v>
+        <v>3320</v>
       </c>
       <c r="D4987" s="0">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row outlineLevel="0" r="4988">
       <c r="A4988" s="0">
-        <v>6015</v>
+        <v>5680</v>
       </c>
       <c r="B4988" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4988" s="0">
-        <v>3521</v>
+        <v>3321</v>
       </c>
       <c r="D4988" s="0">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row outlineLevel="0" r="4989">
       <c r="A4989" s="0">
-        <v>6016</v>
+        <v>5681</v>
       </c>
       <c r="B4989" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4989" s="0">
-        <v>3520</v>
+        <v>3322</v>
       </c>
       <c r="D4989" s="0">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="4990">
       <c r="A4990" s="0">
-        <v>6017</v>
+        <v>5682</v>
       </c>
       <c r="B4990" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4990" s="0">
-        <v>3499</v>
+        <v>3323</v>
       </c>
       <c r="D4990" s="0">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row outlineLevel="0" r="4991">
       <c r="A4991" s="0">
-        <v>6018</v>
+        <v>5683</v>
       </c>
       <c r="B4991" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4991" s="0">
-        <v>3505</v>
+        <v>3324</v>
       </c>
       <c r="D4991" s="0">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row outlineLevel="0" r="4992">
       <c r="A4992" s="0">
-        <v>6019</v>
+        <v>5684</v>
       </c>
       <c r="B4992" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4992" s="0">
-        <v>3503</v>
+        <v>3325</v>
       </c>
       <c r="D4992" s="0">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row outlineLevel="0" r="4993">
       <c r="A4993" s="0">
-        <v>6020</v>
+        <v>5685</v>
       </c>
       <c r="B4993" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4993" s="0">
-        <v>3524</v>
+        <v>3326</v>
       </c>
       <c r="D4993" s="0">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row outlineLevel="0" r="4994">
       <c r="A4994" s="0">
-        <v>6021</v>
+        <v>5686</v>
       </c>
       <c r="B4994" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4994" s="0">
-        <v>3530</v>
+        <v>3327</v>
       </c>
       <c r="D4994" s="0">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row outlineLevel="0" r="4995">
       <c r="A4995" s="0">
-        <v>6022</v>
+        <v>5687</v>
       </c>
       <c r="B4995" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4995" s="0">
-        <v>3507</v>
+        <v>3328</v>
       </c>
       <c r="D4995" s="0">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row outlineLevel="0" r="4996">
       <c r="A4996" s="0">
-        <v>6023</v>
+        <v>5688</v>
       </c>
       <c r="B4996" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4996" s="0">
-        <v>3514</v>
+        <v>3329</v>
       </c>
       <c r="D4996" s="0">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row outlineLevel="0" r="4997">
       <c r="A4997" s="0">
-        <v>6024</v>
+        <v>5689</v>
       </c>
       <c r="B4997" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4997" s="0">
-        <v>3513</v>
+        <v>3330</v>
       </c>
       <c r="D4997" s="0">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row outlineLevel="0" r="4998">
       <c r="A4998" s="0">
-        <v>6025</v>
+        <v>5690</v>
       </c>
       <c r="B4998" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4998" s="0">
-        <v>3517</v>
+        <v>3331</v>
       </c>
       <c r="D4998" s="0">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row outlineLevel="0" r="4999">
       <c r="A4999" s="0">
-        <v>6026</v>
+        <v>5691</v>
       </c>
       <c r="B4999" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C4999" s="0">
-        <v>3519</v>
+        <v>3332</v>
       </c>
       <c r="D4999" s="0">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row outlineLevel="0" r="5000">
       <c r="A5000" s="0">
-        <v>6027</v>
+        <v>5692</v>
       </c>
       <c r="B5000" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C5000" s="0">
-        <v>3525</v>
+        <v>3333</v>
       </c>
       <c r="D5000" s="0">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row outlineLevel="0" r="5001">
       <c r="A5001" s="0">
-        <v>6028</v>
+        <v>5693</v>
       </c>
       <c r="B5001" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C5001" s="0">
-        <v>3528</v>
+        <v>3334</v>
       </c>
       <c r="D5001" s="0">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row outlineLevel="0" r="5002">
       <c r="A5002" s="0">
-        <v>6029</v>
+        <v>5694</v>
       </c>
       <c r="B5002" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C5002" s="0">
-        <v>3529</v>
+        <v>3335</v>
       </c>
       <c r="D5002" s="0">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row outlineLevel="0" r="5003">
       <c r="A5003" s="0">
-        <v>6030</v>
+        <v>5695</v>
       </c>
       <c r="B5003" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C5003" s="0">
-        <v>3509</v>
+        <v>3336</v>
       </c>
       <c r="D5003" s="0">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row outlineLevel="0" r="5004">
       <c r="A5004" s="0">
-        <v>6031</v>
+        <v>5696</v>
       </c>
       <c r="B5004" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C5004" s="0">
-        <v>3531</v>
+        <v>3337</v>
       </c>
       <c r="D5004" s="0">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row outlineLevel="0" r="5005">
       <c r="A5005" s="0">
-        <v>6032</v>
+        <v>5697</v>
       </c>
       <c r="B5005" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C5005" s="0">
-        <v>3532</v>
+        <v>3338</v>
       </c>
       <c r="D5005" s="0">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row outlineLevel="0" r="5006">
       <c r="A5006" s="0">
-        <v>6033</v>
+        <v>5698</v>
       </c>
       <c r="B5006" s="0">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C5006" s="0">
-        <v>3535</v>
+        <v>3339</v>
       </c>
       <c r="D5006" s="0">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row outlineLevel="0" r="5007">
       <c r="A5007" s="0">
+        <v>5699</v>
+      </c>
+      <c r="B5007" s="0">
+        <v>163</v>
+      </c>
+      <c r="C5007" s="0">
+        <v>3340</v>
+      </c>
+      <c r="D5007" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5008">
+      <c r="A5008" s="0">
+        <v>5700</v>
+      </c>
+      <c r="B5008" s="0">
+        <v>163</v>
+      </c>
+      <c r="C5008" s="0">
+        <v>3341</v>
+      </c>
+      <c r="D5008" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5009">
+      <c r="A5009" s="0">
+        <v>5701</v>
+      </c>
+      <c r="B5009" s="0">
+        <v>163</v>
+      </c>
+      <c r="C5009" s="0">
+        <v>3342</v>
+      </c>
+      <c r="D5009" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5010">
+      <c r="A5010" s="0">
+        <v>5702</v>
+      </c>
+      <c r="B5010" s="0">
+        <v>163</v>
+      </c>
+      <c r="C5010" s="0">
+        <v>3343</v>
+      </c>
+      <c r="D5010" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5011">
+      <c r="A5011" s="0">
+        <v>5703</v>
+      </c>
+      <c r="B5011" s="0">
+        <v>163</v>
+      </c>
+      <c r="C5011" s="0">
+        <v>3344</v>
+      </c>
+      <c r="D5011" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5012">
+      <c r="A5012" s="0">
+        <v>5704</v>
+      </c>
+      <c r="B5012" s="0">
+        <v>163</v>
+      </c>
+      <c r="C5012" s="0">
+        <v>3345</v>
+      </c>
+      <c r="D5012" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5013">
+      <c r="A5013" s="0">
+        <v>5705</v>
+      </c>
+      <c r="B5013" s="0">
+        <v>163</v>
+      </c>
+      <c r="C5013" s="0">
+        <v>3346</v>
+      </c>
+      <c r="D5013" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5014">
+      <c r="A5014" s="0">
+        <v>5706</v>
+      </c>
+      <c r="B5014" s="0">
+        <v>163</v>
+      </c>
+      <c r="C5014" s="0">
+        <v>3347</v>
+      </c>
+      <c r="D5014" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5015">
+      <c r="A5015" s="0">
+        <v>5707</v>
+      </c>
+      <c r="B5015" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5015" s="0">
+        <v>3302</v>
+      </c>
+      <c r="D5015" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5016">
+      <c r="A5016" s="0">
+        <v>5708</v>
+      </c>
+      <c r="B5016" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5016" s="0">
+        <v>3304</v>
+      </c>
+      <c r="D5016" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5017">
+      <c r="A5017" s="0">
+        <v>5709</v>
+      </c>
+      <c r="B5017" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5017" s="0">
+        <v>3305</v>
+      </c>
+      <c r="D5017" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5018">
+      <c r="A5018" s="0">
+        <v>5710</v>
+      </c>
+      <c r="B5018" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5018" s="0">
+        <v>3306</v>
+      </c>
+      <c r="D5018" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5019">
+      <c r="A5019" s="0">
+        <v>5711</v>
+      </c>
+      <c r="B5019" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5019" s="0">
+        <v>3313</v>
+      </c>
+      <c r="D5019" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5020">
+      <c r="A5020" s="0">
+        <v>5712</v>
+      </c>
+      <c r="B5020" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5020" s="0">
+        <v>3333</v>
+      </c>
+      <c r="D5020" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5021">
+      <c r="A5021" s="0">
+        <v>5713</v>
+      </c>
+      <c r="B5021" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5021" s="0">
+        <v>3332</v>
+      </c>
+      <c r="D5021" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5022">
+      <c r="A5022" s="0">
+        <v>5714</v>
+      </c>
+      <c r="B5022" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5022" s="0">
+        <v>3311</v>
+      </c>
+      <c r="D5022" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5023">
+      <c r="A5023" s="0">
+        <v>5715</v>
+      </c>
+      <c r="B5023" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5023" s="0">
+        <v>3317</v>
+      </c>
+      <c r="D5023" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5024">
+      <c r="A5024" s="0">
+        <v>5716</v>
+      </c>
+      <c r="B5024" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5024" s="0">
+        <v>3315</v>
+      </c>
+      <c r="D5024" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5025">
+      <c r="A5025" s="0">
+        <v>5717</v>
+      </c>
+      <c r="B5025" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5025" s="0">
+        <v>3336</v>
+      </c>
+      <c r="D5025" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5026">
+      <c r="A5026" s="0">
+        <v>5718</v>
+      </c>
+      <c r="B5026" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5026" s="0">
+        <v>3342</v>
+      </c>
+      <c r="D5026" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5027">
+      <c r="A5027" s="0">
+        <v>5719</v>
+      </c>
+      <c r="B5027" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5027" s="0">
+        <v>3319</v>
+      </c>
+      <c r="D5027" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5028">
+      <c r="A5028" s="0">
+        <v>5720</v>
+      </c>
+      <c r="B5028" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5028" s="0">
+        <v>3326</v>
+      </c>
+      <c r="D5028" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5029">
+      <c r="A5029" s="0">
+        <v>5721</v>
+      </c>
+      <c r="B5029" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5029" s="0">
+        <v>3325</v>
+      </c>
+      <c r="D5029" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5030">
+      <c r="A5030" s="0">
+        <v>5722</v>
+      </c>
+      <c r="B5030" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5030" s="0">
+        <v>3329</v>
+      </c>
+      <c r="D5030" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5031">
+      <c r="A5031" s="0">
+        <v>5723</v>
+      </c>
+      <c r="B5031" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5031" s="0">
+        <v>3331</v>
+      </c>
+      <c r="D5031" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5032">
+      <c r="A5032" s="0">
+        <v>5724</v>
+      </c>
+      <c r="B5032" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5032" s="0">
+        <v>3337</v>
+      </c>
+      <c r="D5032" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5033">
+      <c r="A5033" s="0">
+        <v>5725</v>
+      </c>
+      <c r="B5033" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5033" s="0">
+        <v>3340</v>
+      </c>
+      <c r="D5033" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5034">
+      <c r="A5034" s="0">
+        <v>5726</v>
+      </c>
+      <c r="B5034" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5034" s="0">
+        <v>3341</v>
+      </c>
+      <c r="D5034" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5035">
+      <c r="A5035" s="0">
+        <v>5727</v>
+      </c>
+      <c r="B5035" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5035" s="0">
+        <v>3321</v>
+      </c>
+      <c r="D5035" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5036">
+      <c r="A5036" s="0">
+        <v>5728</v>
+      </c>
+      <c r="B5036" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5036" s="0">
+        <v>3343</v>
+      </c>
+      <c r="D5036" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5037">
+      <c r="A5037" s="0">
+        <v>5729</v>
+      </c>
+      <c r="B5037" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5037" s="0">
+        <v>3344</v>
+      </c>
+      <c r="D5037" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5038">
+      <c r="A5038" s="0">
+        <v>5730</v>
+      </c>
+      <c r="B5038" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5038" s="0">
+        <v>3347</v>
+      </c>
+      <c r="D5038" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5039">
+      <c r="A5039" s="0">
+        <v>5731</v>
+      </c>
+      <c r="B5039" s="0">
+        <v>165</v>
+      </c>
+      <c r="C5039" s="0">
+        <v>3327</v>
+      </c>
+      <c r="D5039" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5040">
+      <c r="A5040" s="0">
+        <v>5904</v>
+      </c>
+      <c r="B5040" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5040" s="0">
+        <v>3455</v>
+      </c>
+      <c r="D5040" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5041">
+      <c r="A5041" s="0">
+        <v>5905</v>
+      </c>
+      <c r="B5041" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5041" s="0">
+        <v>3456</v>
+      </c>
+      <c r="D5041" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5042">
+      <c r="A5042" s="0">
+        <v>5906</v>
+      </c>
+      <c r="B5042" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5042" s="0">
+        <v>3457</v>
+      </c>
+      <c r="D5042" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5043">
+      <c r="A5043" s="0">
+        <v>5907</v>
+      </c>
+      <c r="B5043" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5043" s="0">
+        <v>3458</v>
+      </c>
+      <c r="D5043" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5044">
+      <c r="A5044" s="0">
+        <v>5908</v>
+      </c>
+      <c r="B5044" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5044" s="0">
+        <v>3459</v>
+      </c>
+      <c r="D5044" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5045">
+      <c r="A5045" s="0">
+        <v>5909</v>
+      </c>
+      <c r="B5045" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5045" s="0">
+        <v>3460</v>
+      </c>
+      <c r="D5045" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5046">
+      <c r="A5046" s="0">
+        <v>5910</v>
+      </c>
+      <c r="B5046" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5046" s="0">
+        <v>3461</v>
+      </c>
+      <c r="D5046" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5047">
+      <c r="A5047" s="0">
+        <v>5911</v>
+      </c>
+      <c r="B5047" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5047" s="0">
+        <v>3462</v>
+      </c>
+      <c r="D5047" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5048">
+      <c r="A5048" s="0">
+        <v>5912</v>
+      </c>
+      <c r="B5048" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5048" s="0">
+        <v>3463</v>
+      </c>
+      <c r="D5048" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5049">
+      <c r="A5049" s="0">
+        <v>5913</v>
+      </c>
+      <c r="B5049" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5049" s="0">
+        <v>3464</v>
+      </c>
+      <c r="D5049" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5050">
+      <c r="A5050" s="0">
+        <v>5914</v>
+      </c>
+      <c r="B5050" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5050" s="0">
+        <v>3465</v>
+      </c>
+      <c r="D5050" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5051">
+      <c r="A5051" s="0">
+        <v>5915</v>
+      </c>
+      <c r="B5051" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5051" s="0">
+        <v>3466</v>
+      </c>
+      <c r="D5051" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5052">
+      <c r="A5052" s="0">
+        <v>5916</v>
+      </c>
+      <c r="B5052" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5052" s="0">
+        <v>3467</v>
+      </c>
+      <c r="D5052" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5053">
+      <c r="A5053" s="0">
+        <v>5917</v>
+      </c>
+      <c r="B5053" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5053" s="0">
+        <v>3468</v>
+      </c>
+      <c r="D5053" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5054">
+      <c r="A5054" s="0">
+        <v>5918</v>
+      </c>
+      <c r="B5054" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5054" s="0">
+        <v>3469</v>
+      </c>
+      <c r="D5054" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5055">
+      <c r="A5055" s="0">
+        <v>5919</v>
+      </c>
+      <c r="B5055" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5055" s="0">
+        <v>3470</v>
+      </c>
+      <c r="D5055" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5056">
+      <c r="A5056" s="0">
+        <v>5920</v>
+      </c>
+      <c r="B5056" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5056" s="0">
+        <v>3471</v>
+      </c>
+      <c r="D5056" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5057">
+      <c r="A5057" s="0">
+        <v>5921</v>
+      </c>
+      <c r="B5057" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5057" s="0">
+        <v>3472</v>
+      </c>
+      <c r="D5057" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5058">
+      <c r="A5058" s="0">
+        <v>5922</v>
+      </c>
+      <c r="B5058" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5058" s="0">
+        <v>3473</v>
+      </c>
+      <c r="D5058" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5059">
+      <c r="A5059" s="0">
+        <v>5923</v>
+      </c>
+      <c r="B5059" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5059" s="0">
+        <v>3474</v>
+      </c>
+      <c r="D5059" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5060">
+      <c r="A5060" s="0">
+        <v>5924</v>
+      </c>
+      <c r="B5060" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5060" s="0">
+        <v>3475</v>
+      </c>
+      <c r="D5060" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5061">
+      <c r="A5061" s="0">
+        <v>5925</v>
+      </c>
+      <c r="B5061" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5061" s="0">
+        <v>3476</v>
+      </c>
+      <c r="D5061" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5062">
+      <c r="A5062" s="0">
+        <v>5926</v>
+      </c>
+      <c r="B5062" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5062" s="0">
+        <v>3477</v>
+      </c>
+      <c r="D5062" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5063">
+      <c r="A5063" s="0">
+        <v>5927</v>
+      </c>
+      <c r="B5063" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5063" s="0">
+        <v>3478</v>
+      </c>
+      <c r="D5063" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5064">
+      <c r="A5064" s="0">
+        <v>5928</v>
+      </c>
+      <c r="B5064" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5064" s="0">
+        <v>3479</v>
+      </c>
+      <c r="D5064" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5065">
+      <c r="A5065" s="0">
+        <v>5929</v>
+      </c>
+      <c r="B5065" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5065" s="0">
+        <v>3480</v>
+      </c>
+      <c r="D5065" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5066">
+      <c r="A5066" s="0">
+        <v>5930</v>
+      </c>
+      <c r="B5066" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5066" s="0">
+        <v>3481</v>
+      </c>
+      <c r="D5066" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5067">
+      <c r="A5067" s="0">
+        <v>5931</v>
+      </c>
+      <c r="B5067" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5067" s="0">
+        <v>3482</v>
+      </c>
+      <c r="D5067" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5068">
+      <c r="A5068" s="0">
+        <v>5932</v>
+      </c>
+      <c r="B5068" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5068" s="0">
+        <v>3483</v>
+      </c>
+      <c r="D5068" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5069">
+      <c r="A5069" s="0">
+        <v>5933</v>
+      </c>
+      <c r="B5069" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5069" s="0">
+        <v>3484</v>
+      </c>
+      <c r="D5069" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5070">
+      <c r="A5070" s="0">
+        <v>5934</v>
+      </c>
+      <c r="B5070" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5070" s="0">
+        <v>3485</v>
+      </c>
+      <c r="D5070" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5071">
+      <c r="A5071" s="0">
+        <v>5935</v>
+      </c>
+      <c r="B5071" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5071" s="0">
+        <v>3486</v>
+      </c>
+      <c r="D5071" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5072">
+      <c r="A5072" s="0">
+        <v>5936</v>
+      </c>
+      <c r="B5072" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5072" s="0">
+        <v>3487</v>
+      </c>
+      <c r="D5072" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5073">
+      <c r="A5073" s="0">
+        <v>5937</v>
+      </c>
+      <c r="B5073" s="0">
+        <v>172</v>
+      </c>
+      <c r="C5073" s="0">
+        <v>3488</v>
+      </c>
+      <c r="D5073" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5074">
+      <c r="A5074" s="0">
+        <v>5938</v>
+      </c>
+      <c r="B5074" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5074" s="0">
+        <v>3443</v>
+      </c>
+      <c r="D5074" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5075">
+      <c r="A5075" s="0">
+        <v>5939</v>
+      </c>
+      <c r="B5075" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5075" s="0">
+        <v>3445</v>
+      </c>
+      <c r="D5075" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5076">
+      <c r="A5076" s="0">
+        <v>5940</v>
+      </c>
+      <c r="B5076" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5076" s="0">
+        <v>3446</v>
+      </c>
+      <c r="D5076" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5077">
+      <c r="A5077" s="0">
+        <v>5941</v>
+      </c>
+      <c r="B5077" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5077" s="0">
+        <v>3447</v>
+      </c>
+      <c r="D5077" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5078">
+      <c r="A5078" s="0">
+        <v>5942</v>
+      </c>
+      <c r="B5078" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5078" s="0">
+        <v>3454</v>
+      </c>
+      <c r="D5078" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5079">
+      <c r="A5079" s="0">
+        <v>5943</v>
+      </c>
+      <c r="B5079" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5079" s="0">
+        <v>3474</v>
+      </c>
+      <c r="D5079" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5080">
+      <c r="A5080" s="0">
+        <v>5944</v>
+      </c>
+      <c r="B5080" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5080" s="0">
+        <v>3473</v>
+      </c>
+      <c r="D5080" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5081">
+      <c r="A5081" s="0">
+        <v>5945</v>
+      </c>
+      <c r="B5081" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5081" s="0">
+        <v>3452</v>
+      </c>
+      <c r="D5081" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5082">
+      <c r="A5082" s="0">
+        <v>5946</v>
+      </c>
+      <c r="B5082" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5082" s="0">
+        <v>3458</v>
+      </c>
+      <c r="D5082" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5083">
+      <c r="A5083" s="0">
+        <v>5947</v>
+      </c>
+      <c r="B5083" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5083" s="0">
+        <v>3456</v>
+      </c>
+      <c r="D5083" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5084">
+      <c r="A5084" s="0">
+        <v>5948</v>
+      </c>
+      <c r="B5084" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5084" s="0">
+        <v>3477</v>
+      </c>
+      <c r="D5084" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5085">
+      <c r="A5085" s="0">
+        <v>5949</v>
+      </c>
+      <c r="B5085" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5085" s="0">
+        <v>3483</v>
+      </c>
+      <c r="D5085" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5086">
+      <c r="A5086" s="0">
+        <v>5950</v>
+      </c>
+      <c r="B5086" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5086" s="0">
+        <v>3460</v>
+      </c>
+      <c r="D5086" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5087">
+      <c r="A5087" s="0">
+        <v>5951</v>
+      </c>
+      <c r="B5087" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5087" s="0">
+        <v>3467</v>
+      </c>
+      <c r="D5087" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5088">
+      <c r="A5088" s="0">
+        <v>5952</v>
+      </c>
+      <c r="B5088" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5088" s="0">
+        <v>3466</v>
+      </c>
+      <c r="D5088" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5089">
+      <c r="A5089" s="0">
+        <v>5953</v>
+      </c>
+      <c r="B5089" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5089" s="0">
+        <v>3470</v>
+      </c>
+      <c r="D5089" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5090">
+      <c r="A5090" s="0">
+        <v>5954</v>
+      </c>
+      <c r="B5090" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5090" s="0">
+        <v>3472</v>
+      </c>
+      <c r="D5090" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5091">
+      <c r="A5091" s="0">
+        <v>5955</v>
+      </c>
+      <c r="B5091" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5091" s="0">
+        <v>3478</v>
+      </c>
+      <c r="D5091" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5092">
+      <c r="A5092" s="0">
+        <v>5956</v>
+      </c>
+      <c r="B5092" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5092" s="0">
+        <v>3481</v>
+      </c>
+      <c r="D5092" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5093">
+      <c r="A5093" s="0">
+        <v>5957</v>
+      </c>
+      <c r="B5093" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5093" s="0">
+        <v>3482</v>
+      </c>
+      <c r="D5093" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5094">
+      <c r="A5094" s="0">
+        <v>5958</v>
+      </c>
+      <c r="B5094" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5094" s="0">
+        <v>3462</v>
+      </c>
+      <c r="D5094" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5095">
+      <c r="A5095" s="0">
+        <v>5959</v>
+      </c>
+      <c r="B5095" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5095" s="0">
+        <v>3484</v>
+      </c>
+      <c r="D5095" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5096">
+      <c r="A5096" s="0">
+        <v>5960</v>
+      </c>
+      <c r="B5096" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5096" s="0">
+        <v>3485</v>
+      </c>
+      <c r="D5096" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5097">
+      <c r="A5097" s="0">
+        <v>5961</v>
+      </c>
+      <c r="B5097" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5097" s="0">
+        <v>3488</v>
+      </c>
+      <c r="D5097" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5098">
+      <c r="A5098" s="0">
+        <v>5962</v>
+      </c>
+      <c r="B5098" s="0">
+        <v>174</v>
+      </c>
+      <c r="C5098" s="0">
+        <v>3468</v>
+      </c>
+      <c r="D5098" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5099">
+      <c r="A5099" s="0">
+        <v>5963</v>
+      </c>
+      <c r="B5099" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5099" s="0">
+        <v>3489</v>
+      </c>
+      <c r="D5099" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5100">
+      <c r="A5100" s="0">
+        <v>5964</v>
+      </c>
+      <c r="B5100" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5100" s="0">
+        <v>3490</v>
+      </c>
+      <c r="D5100" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5101">
+      <c r="A5101" s="0">
+        <v>5965</v>
+      </c>
+      <c r="B5101" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5101" s="0">
+        <v>3491</v>
+      </c>
+      <c r="D5101" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5102">
+      <c r="A5102" s="0">
+        <v>5966</v>
+      </c>
+      <c r="B5102" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5102" s="0">
+        <v>3492</v>
+      </c>
+      <c r="D5102" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5103">
+      <c r="A5103" s="0">
+        <v>5967</v>
+      </c>
+      <c r="B5103" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5103" s="0">
+        <v>3493</v>
+      </c>
+      <c r="D5103" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5104">
+      <c r="A5104" s="0">
+        <v>5968</v>
+      </c>
+      <c r="B5104" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5104" s="0">
+        <v>3494</v>
+      </c>
+      <c r="D5104" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5105">
+      <c r="A5105" s="0">
+        <v>5969</v>
+      </c>
+      <c r="B5105" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5105" s="0">
+        <v>3495</v>
+      </c>
+      <c r="D5105" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5106">
+      <c r="A5106" s="0">
+        <v>5970</v>
+      </c>
+      <c r="B5106" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5106" s="0">
+        <v>3496</v>
+      </c>
+      <c r="D5106" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5107">
+      <c r="A5107" s="0">
+        <v>5971</v>
+      </c>
+      <c r="B5107" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5107" s="0">
+        <v>3497</v>
+      </c>
+      <c r="D5107" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5108">
+      <c r="A5108" s="0">
+        <v>5972</v>
+      </c>
+      <c r="B5108" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5108" s="0">
+        <v>3498</v>
+      </c>
+      <c r="D5108" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5109">
+      <c r="A5109" s="0">
+        <v>5973</v>
+      </c>
+      <c r="B5109" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5109" s="0">
+        <v>3499</v>
+      </c>
+      <c r="D5109" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5110">
+      <c r="A5110" s="0">
+        <v>5974</v>
+      </c>
+      <c r="B5110" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5110" s="0">
+        <v>3500</v>
+      </c>
+      <c r="D5110" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5111">
+      <c r="A5111" s="0">
+        <v>5975</v>
+      </c>
+      <c r="B5111" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5111" s="0">
+        <v>3501</v>
+      </c>
+      <c r="D5111" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5112">
+      <c r="A5112" s="0">
+        <v>5976</v>
+      </c>
+      <c r="B5112" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5112" s="0">
+        <v>3502</v>
+      </c>
+      <c r="D5112" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5113">
+      <c r="A5113" s="0">
+        <v>5977</v>
+      </c>
+      <c r="B5113" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5113" s="0">
+        <v>3503</v>
+      </c>
+      <c r="D5113" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5114">
+      <c r="A5114" s="0">
+        <v>5978</v>
+      </c>
+      <c r="B5114" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5114" s="0">
+        <v>3504</v>
+      </c>
+      <c r="D5114" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5115">
+      <c r="A5115" s="0">
+        <v>5979</v>
+      </c>
+      <c r="B5115" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5115" s="0">
+        <v>3505</v>
+      </c>
+      <c r="D5115" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5116">
+      <c r="A5116" s="0">
+        <v>5980</v>
+      </c>
+      <c r="B5116" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5116" s="0">
+        <v>3506</v>
+      </c>
+      <c r="D5116" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5117">
+      <c r="A5117" s="0">
+        <v>5981</v>
+      </c>
+      <c r="B5117" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5117" s="0">
+        <v>3507</v>
+      </c>
+      <c r="D5117" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5118">
+      <c r="A5118" s="0">
+        <v>5982</v>
+      </c>
+      <c r="B5118" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5118" s="0">
+        <v>3508</v>
+      </c>
+      <c r="D5118" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5119">
+      <c r="A5119" s="0">
+        <v>5983</v>
+      </c>
+      <c r="B5119" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5119" s="0">
+        <v>3509</v>
+      </c>
+      <c r="D5119" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5120">
+      <c r="A5120" s="0">
+        <v>5984</v>
+      </c>
+      <c r="B5120" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5120" s="0">
+        <v>3510</v>
+      </c>
+      <c r="D5120" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5121">
+      <c r="A5121" s="0">
+        <v>5985</v>
+      </c>
+      <c r="B5121" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5121" s="0">
+        <v>3511</v>
+      </c>
+      <c r="D5121" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5122">
+      <c r="A5122" s="0">
+        <v>5986</v>
+      </c>
+      <c r="B5122" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5122" s="0">
+        <v>3512</v>
+      </c>
+      <c r="D5122" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5123">
+      <c r="A5123" s="0">
+        <v>5987</v>
+      </c>
+      <c r="B5123" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5123" s="0">
+        <v>3513</v>
+      </c>
+      <c r="D5123" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5124">
+      <c r="A5124" s="0">
+        <v>5988</v>
+      </c>
+      <c r="B5124" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5124" s="0">
+        <v>3514</v>
+      </c>
+      <c r="D5124" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5125">
+      <c r="A5125" s="0">
+        <v>5989</v>
+      </c>
+      <c r="B5125" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5125" s="0">
+        <v>3515</v>
+      </c>
+      <c r="D5125" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5126">
+      <c r="A5126" s="0">
+        <v>5990</v>
+      </c>
+      <c r="B5126" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5126" s="0">
+        <v>3516</v>
+      </c>
+      <c r="D5126" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5127">
+      <c r="A5127" s="0">
+        <v>5991</v>
+      </c>
+      <c r="B5127" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5127" s="0">
+        <v>3517</v>
+      </c>
+      <c r="D5127" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5128">
+      <c r="A5128" s="0">
+        <v>5992</v>
+      </c>
+      <c r="B5128" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5128" s="0">
+        <v>3518</v>
+      </c>
+      <c r="D5128" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5129">
+      <c r="A5129" s="0">
+        <v>5993</v>
+      </c>
+      <c r="B5129" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5129" s="0">
+        <v>3519</v>
+      </c>
+      <c r="D5129" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5130">
+      <c r="A5130" s="0">
+        <v>5994</v>
+      </c>
+      <c r="B5130" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5130" s="0">
+        <v>3520</v>
+      </c>
+      <c r="D5130" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5131">
+      <c r="A5131" s="0">
+        <v>5995</v>
+      </c>
+      <c r="B5131" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5131" s="0">
+        <v>3521</v>
+      </c>
+      <c r="D5131" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5132">
+      <c r="A5132" s="0">
+        <v>5996</v>
+      </c>
+      <c r="B5132" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5132" s="0">
+        <v>3522</v>
+      </c>
+      <c r="D5132" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5133">
+      <c r="A5133" s="0">
+        <v>5997</v>
+      </c>
+      <c r="B5133" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5133" s="0">
+        <v>3523</v>
+      </c>
+      <c r="D5133" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5134">
+      <c r="A5134" s="0">
+        <v>5998</v>
+      </c>
+      <c r="B5134" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5134" s="0">
+        <v>3524</v>
+      </c>
+      <c r="D5134" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5135">
+      <c r="A5135" s="0">
+        <v>5999</v>
+      </c>
+      <c r="B5135" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5135" s="0">
+        <v>3525</v>
+      </c>
+      <c r="D5135" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5136">
+      <c r="A5136" s="0">
+        <v>6000</v>
+      </c>
+      <c r="B5136" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5136" s="0">
+        <v>3526</v>
+      </c>
+      <c r="D5136" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5137">
+      <c r="A5137" s="0">
+        <v>6001</v>
+      </c>
+      <c r="B5137" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5137" s="0">
+        <v>3527</v>
+      </c>
+      <c r="D5137" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5138">
+      <c r="A5138" s="0">
+        <v>6002</v>
+      </c>
+      <c r="B5138" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5138" s="0">
+        <v>3528</v>
+      </c>
+      <c r="D5138" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5139">
+      <c r="A5139" s="0">
+        <v>6003</v>
+      </c>
+      <c r="B5139" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5139" s="0">
+        <v>3529</v>
+      </c>
+      <c r="D5139" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5140">
+      <c r="A5140" s="0">
+        <v>6004</v>
+      </c>
+      <c r="B5140" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5140" s="0">
+        <v>3530</v>
+      </c>
+      <c r="D5140" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5141">
+      <c r="A5141" s="0">
+        <v>6005</v>
+      </c>
+      <c r="B5141" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5141" s="0">
+        <v>3531</v>
+      </c>
+      <c r="D5141" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5142">
+      <c r="A5142" s="0">
+        <v>6006</v>
+      </c>
+      <c r="B5142" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5142" s="0">
+        <v>3532</v>
+      </c>
+      <c r="D5142" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5143">
+      <c r="A5143" s="0">
+        <v>6007</v>
+      </c>
+      <c r="B5143" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5143" s="0">
+        <v>3533</v>
+      </c>
+      <c r="D5143" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5144">
+      <c r="A5144" s="0">
+        <v>6008</v>
+      </c>
+      <c r="B5144" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5144" s="0">
+        <v>3534</v>
+      </c>
+      <c r="D5144" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5145">
+      <c r="A5145" s="0">
+        <v>6009</v>
+      </c>
+      <c r="B5145" s="0">
+        <v>173</v>
+      </c>
+      <c r="C5145" s="0">
+        <v>3535</v>
+      </c>
+      <c r="D5145" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5146">
+      <c r="A5146" s="0">
+        <v>6010</v>
+      </c>
+      <c r="B5146" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5146" s="0">
+        <v>3490</v>
+      </c>
+      <c r="D5146" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5147">
+      <c r="A5147" s="0">
+        <v>6011</v>
+      </c>
+      <c r="B5147" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5147" s="0">
+        <v>3492</v>
+      </c>
+      <c r="D5147" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5148">
+      <c r="A5148" s="0">
+        <v>6012</v>
+      </c>
+      <c r="B5148" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5148" s="0">
+        <v>3493</v>
+      </c>
+      <c r="D5148" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5149">
+      <c r="A5149" s="0">
+        <v>6013</v>
+      </c>
+      <c r="B5149" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5149" s="0">
+        <v>3494</v>
+      </c>
+      <c r="D5149" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5150">
+      <c r="A5150" s="0">
+        <v>6014</v>
+      </c>
+      <c r="B5150" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5150" s="0">
+        <v>3501</v>
+      </c>
+      <c r="D5150" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5151">
+      <c r="A5151" s="0">
+        <v>6015</v>
+      </c>
+      <c r="B5151" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5151" s="0">
+        <v>3521</v>
+      </c>
+      <c r="D5151" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5152">
+      <c r="A5152" s="0">
+        <v>6016</v>
+      </c>
+      <c r="B5152" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5152" s="0">
+        <v>3520</v>
+      </c>
+      <c r="D5152" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5153">
+      <c r="A5153" s="0">
+        <v>6017</v>
+      </c>
+      <c r="B5153" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5153" s="0">
+        <v>3499</v>
+      </c>
+      <c r="D5153" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5154">
+      <c r="A5154" s="0">
+        <v>6018</v>
+      </c>
+      <c r="B5154" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5154" s="0">
+        <v>3505</v>
+      </c>
+      <c r="D5154" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5155">
+      <c r="A5155" s="0">
+        <v>6019</v>
+      </c>
+      <c r="B5155" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5155" s="0">
+        <v>3503</v>
+      </c>
+      <c r="D5155" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5156">
+      <c r="A5156" s="0">
+        <v>6020</v>
+      </c>
+      <c r="B5156" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5156" s="0">
+        <v>3524</v>
+      </c>
+      <c r="D5156" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5157">
+      <c r="A5157" s="0">
+        <v>6021</v>
+      </c>
+      <c r="B5157" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5157" s="0">
+        <v>3530</v>
+      </c>
+      <c r="D5157" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5158">
+      <c r="A5158" s="0">
+        <v>6022</v>
+      </c>
+      <c r="B5158" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5158" s="0">
+        <v>3507</v>
+      </c>
+      <c r="D5158" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5159">
+      <c r="A5159" s="0">
+        <v>6023</v>
+      </c>
+      <c r="B5159" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5159" s="0">
+        <v>3514</v>
+      </c>
+      <c r="D5159" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5160">
+      <c r="A5160" s="0">
+        <v>6024</v>
+      </c>
+      <c r="B5160" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5160" s="0">
+        <v>3513</v>
+      </c>
+      <c r="D5160" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5161">
+      <c r="A5161" s="0">
+        <v>6025</v>
+      </c>
+      <c r="B5161" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5161" s="0">
+        <v>3517</v>
+      </c>
+      <c r="D5161" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5162">
+      <c r="A5162" s="0">
+        <v>6026</v>
+      </c>
+      <c r="B5162" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5162" s="0">
+        <v>3519</v>
+      </c>
+      <c r="D5162" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5163">
+      <c r="A5163" s="0">
+        <v>6027</v>
+      </c>
+      <c r="B5163" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5163" s="0">
+        <v>3525</v>
+      </c>
+      <c r="D5163" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5164">
+      <c r="A5164" s="0">
+        <v>6028</v>
+      </c>
+      <c r="B5164" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5164" s="0">
+        <v>3528</v>
+      </c>
+      <c r="D5164" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5165">
+      <c r="A5165" s="0">
+        <v>6029</v>
+      </c>
+      <c r="B5165" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5165" s="0">
+        <v>3529</v>
+      </c>
+      <c r="D5165" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5166">
+      <c r="A5166" s="0">
+        <v>6030</v>
+      </c>
+      <c r="B5166" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5166" s="0">
+        <v>3509</v>
+      </c>
+      <c r="D5166" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5167">
+      <c r="A5167" s="0">
+        <v>6031</v>
+      </c>
+      <c r="B5167" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5167" s="0">
+        <v>3531</v>
+      </c>
+      <c r="D5167" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5168">
+      <c r="A5168" s="0">
+        <v>6032</v>
+      </c>
+      <c r="B5168" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5168" s="0">
+        <v>3532</v>
+      </c>
+      <c r="D5168" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5169">
+      <c r="A5169" s="0">
+        <v>6033</v>
+      </c>
+      <c r="B5169" s="0">
+        <v>175</v>
+      </c>
+      <c r="C5169" s="0">
+        <v>3535</v>
+      </c>
+      <c r="D5169" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5170">
+      <c r="A5170" s="0">
         <v>6034</v>
       </c>
-      <c r="B5007" s="0">
+      <c r="B5170" s="0">
         <v>175</v>
       </c>
-      <c r="C5007" s="0">
+      <c r="C5170" s="0">
         <v>3515</v>
       </c>
-      <c r="D5007" s="0">
+      <c r="D5170" s="0">
         <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5171">
+      <c r="A5171" s="0">
+        <v>6035</v>
+      </c>
+      <c r="B5171" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5171" s="0">
+        <v>3536</v>
+      </c>
+      <c r="D5171" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5172">
+      <c r="A5172" s="0">
+        <v>6036</v>
+      </c>
+      <c r="B5172" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5172" s="0">
+        <v>3537</v>
+      </c>
+      <c r="D5172" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5173">
+      <c r="A5173" s="0">
+        <v>6037</v>
+      </c>
+      <c r="B5173" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5173" s="0">
+        <v>3538</v>
+      </c>
+      <c r="D5173" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5174">
+      <c r="A5174" s="0">
+        <v>6038</v>
+      </c>
+      <c r="B5174" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5174" s="0">
+        <v>3539</v>
+      </c>
+      <c r="D5174" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5175">
+      <c r="A5175" s="0">
+        <v>6039</v>
+      </c>
+      <c r="B5175" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5175" s="0">
+        <v>3540</v>
+      </c>
+      <c r="D5175" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5176">
+      <c r="A5176" s="0">
+        <v>6040</v>
+      </c>
+      <c r="B5176" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5176" s="0">
+        <v>3541</v>
+      </c>
+      <c r="D5176" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5177">
+      <c r="A5177" s="0">
+        <v>6041</v>
+      </c>
+      <c r="B5177" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5177" s="0">
+        <v>3542</v>
+      </c>
+      <c r="D5177" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5178">
+      <c r="A5178" s="0">
+        <v>6042</v>
+      </c>
+      <c r="B5178" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5178" s="0">
+        <v>3543</v>
+      </c>
+      <c r="D5178" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5179">
+      <c r="A5179" s="0">
+        <v>6043</v>
+      </c>
+      <c r="B5179" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5179" s="0">
+        <v>3544</v>
+      </c>
+      <c r="D5179" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5180">
+      <c r="A5180" s="0">
+        <v>6044</v>
+      </c>
+      <c r="B5180" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5180" s="0">
+        <v>3545</v>
+      </c>
+      <c r="D5180" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5181">
+      <c r="A5181" s="0">
+        <v>6045</v>
+      </c>
+      <c r="B5181" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5181" s="0">
+        <v>3546</v>
+      </c>
+      <c r="D5181" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5182">
+      <c r="A5182" s="0">
+        <v>6046</v>
+      </c>
+      <c r="B5182" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5182" s="0">
+        <v>3547</v>
+      </c>
+      <c r="D5182" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5183">
+      <c r="A5183" s="0">
+        <v>6047</v>
+      </c>
+      <c r="B5183" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5183" s="0">
+        <v>3548</v>
+      </c>
+      <c r="D5183" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5184">
+      <c r="A5184" s="0">
+        <v>6048</v>
+      </c>
+      <c r="B5184" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5184" s="0">
+        <v>3549</v>
+      </c>
+      <c r="D5184" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5185">
+      <c r="A5185" s="0">
+        <v>6049</v>
+      </c>
+      <c r="B5185" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5185" s="0">
+        <v>3550</v>
+      </c>
+      <c r="D5185" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5186">
+      <c r="A5186" s="0">
+        <v>6050</v>
+      </c>
+      <c r="B5186" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5186" s="0">
+        <v>3551</v>
+      </c>
+      <c r="D5186" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5187">
+      <c r="A5187" s="0">
+        <v>6051</v>
+      </c>
+      <c r="B5187" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5187" s="0">
+        <v>3552</v>
+      </c>
+      <c r="D5187" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5188">
+      <c r="A5188" s="0">
+        <v>6052</v>
+      </c>
+      <c r="B5188" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5188" s="0">
+        <v>3553</v>
+      </c>
+      <c r="D5188" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5189">
+      <c r="A5189" s="0">
+        <v>6053</v>
+      </c>
+      <c r="B5189" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5189" s="0">
+        <v>3554</v>
+      </c>
+      <c r="D5189" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5190">
+      <c r="A5190" s="0">
+        <v>6054</v>
+      </c>
+      <c r="B5190" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5190" s="0">
+        <v>3555</v>
+      </c>
+      <c r="D5190" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5191">
+      <c r="A5191" s="0">
+        <v>6055</v>
+      </c>
+      <c r="B5191" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5191" s="0">
+        <v>3556</v>
+      </c>
+      <c r="D5191" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5192">
+      <c r="A5192" s="0">
+        <v>6056</v>
+      </c>
+      <c r="B5192" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5192" s="0">
+        <v>3557</v>
+      </c>
+      <c r="D5192" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5193">
+      <c r="A5193" s="0">
+        <v>6057</v>
+      </c>
+      <c r="B5193" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5193" s="0">
+        <v>3558</v>
+      </c>
+      <c r="D5193" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5194">
+      <c r="A5194" s="0">
+        <v>6058</v>
+      </c>
+      <c r="B5194" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5194" s="0">
+        <v>3559</v>
+      </c>
+      <c r="D5194" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5195">
+      <c r="A5195" s="0">
+        <v>6059</v>
+      </c>
+      <c r="B5195" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5195" s="0">
+        <v>3560</v>
+      </c>
+      <c r="D5195" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5196">
+      <c r="A5196" s="0">
+        <v>6060</v>
+      </c>
+      <c r="B5196" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5196" s="0">
+        <v>3561</v>
+      </c>
+      <c r="D5196" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5197">
+      <c r="A5197" s="0">
+        <v>6061</v>
+      </c>
+      <c r="B5197" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5197" s="0">
+        <v>3562</v>
+      </c>
+      <c r="D5197" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5198">
+      <c r="A5198" s="0">
+        <v>6062</v>
+      </c>
+      <c r="B5198" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5198" s="0">
+        <v>3563</v>
+      </c>
+      <c r="D5198" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5199">
+      <c r="A5199" s="0">
+        <v>6063</v>
+      </c>
+      <c r="B5199" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5199" s="0">
+        <v>3564</v>
+      </c>
+      <c r="D5199" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5200">
+      <c r="A5200" s="0">
+        <v>6064</v>
+      </c>
+      <c r="B5200" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5200" s="0">
+        <v>3565</v>
+      </c>
+      <c r="D5200" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5201">
+      <c r="A5201" s="0">
+        <v>6065</v>
+      </c>
+      <c r="B5201" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5201" s="0">
+        <v>3566</v>
+      </c>
+      <c r="D5201" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5202">
+      <c r="A5202" s="0">
+        <v>6066</v>
+      </c>
+      <c r="B5202" s="0">
+        <v>158</v>
+      </c>
+      <c r="C5202" s="0">
+        <v>3567</v>
+      </c>
+      <c r="D5202" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5203">
+      <c r="A5203" s="0">
+        <v>6230</v>
+      </c>
+      <c r="B5203" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5203" s="0">
+        <v>3681</v>
+      </c>
+      <c r="D5203" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5204">
+      <c r="A5204" s="0">
+        <v>6231</v>
+      </c>
+      <c r="B5204" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5204" s="0">
+        <v>3682</v>
+      </c>
+      <c r="D5204" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5205">
+      <c r="A5205" s="0">
+        <v>6232</v>
+      </c>
+      <c r="B5205" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5205" s="0">
+        <v>62</v>
+      </c>
+      <c r="D5205" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5206">
+      <c r="A5206" s="0">
+        <v>6233</v>
+      </c>
+      <c r="B5206" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5206" s="0">
+        <v>83</v>
+      </c>
+      <c r="D5206" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5207">
+      <c r="A5207" s="0">
+        <v>6234</v>
+      </c>
+      <c r="B5207" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5207" s="0">
+        <v>67</v>
+      </c>
+      <c r="D5207" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5208">
+      <c r="A5208" s="0">
+        <v>6235</v>
+      </c>
+      <c r="B5208" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5208" s="0">
+        <v>3686</v>
+      </c>
+      <c r="D5208" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5209">
+      <c r="A5209" s="0">
+        <v>6236</v>
+      </c>
+      <c r="B5209" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5209" s="0">
+        <v>48</v>
+      </c>
+      <c r="D5209" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5210">
+      <c r="A5210" s="0">
+        <v>6237</v>
+      </c>
+      <c r="B5210" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5210" s="0">
+        <v>75</v>
+      </c>
+      <c r="D5210" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5211">
+      <c r="A5211" s="0">
+        <v>6238</v>
+      </c>
+      <c r="B5211" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5211" s="0">
+        <v>85</v>
+      </c>
+      <c r="D5211" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5212">
+      <c r="A5212" s="0">
+        <v>6239</v>
+      </c>
+      <c r="B5212" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5212" s="0">
+        <v>74</v>
+      </c>
+      <c r="D5212" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5213">
+      <c r="A5213" s="0">
+        <v>6240</v>
+      </c>
+      <c r="B5213" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5213" s="0">
+        <v>78</v>
+      </c>
+      <c r="D5213" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5214">
+      <c r="A5214" s="0">
+        <v>6241</v>
+      </c>
+      <c r="B5214" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5214" s="0">
+        <v>3692</v>
+      </c>
+      <c r="D5214" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5215">
+      <c r="A5215" s="0">
+        <v>6242</v>
+      </c>
+      <c r="B5215" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5215" s="0">
+        <v>69</v>
+      </c>
+      <c r="D5215" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5216">
+      <c r="A5216" s="0">
+        <v>6243</v>
+      </c>
+      <c r="B5216" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5216" s="0">
+        <v>3694</v>
+      </c>
+      <c r="D5216" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5217">
+      <c r="A5217" s="0">
+        <v>6244</v>
+      </c>
+      <c r="B5217" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5217" s="0">
+        <v>3695</v>
+      </c>
+      <c r="D5217" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5218">
+      <c r="A5218" s="0">
+        <v>6245</v>
+      </c>
+      <c r="B5218" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5218" s="0">
+        <v>66</v>
+      </c>
+      <c r="D5218" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5219">
+      <c r="A5219" s="0">
+        <v>6246</v>
+      </c>
+      <c r="B5219" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5219" s="0">
+        <v>3697</v>
+      </c>
+      <c r="D5219" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5220">
+      <c r="A5220" s="0">
+        <v>6247</v>
+      </c>
+      <c r="B5220" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5220" s="0">
+        <v>65</v>
+      </c>
+      <c r="D5220" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5221">
+      <c r="A5221" s="0">
+        <v>6248</v>
+      </c>
+      <c r="B5221" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5221" s="0">
+        <v>87</v>
+      </c>
+      <c r="D5221" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5222">
+      <c r="A5222" s="0">
+        <v>6249</v>
+      </c>
+      <c r="B5222" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5222" s="0">
+        <v>3700</v>
+      </c>
+      <c r="D5222" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5223">
+      <c r="A5223" s="0">
+        <v>6250</v>
+      </c>
+      <c r="B5223" s="0">
+        <v>156</v>
+      </c>
+      <c r="C5223" s="0">
+        <v>58</v>
+      </c>
+      <c r="D5223" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5224">
+      <c r="A5224" s="0">
+        <v>6251</v>
+      </c>
+      <c r="B5224" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5224" s="0">
+        <v>59</v>
+      </c>
+      <c r="D5224" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5225">
+      <c r="A5225" s="0">
+        <v>6252</v>
+      </c>
+      <c r="B5225" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5225" s="0">
+        <v>3658</v>
+      </c>
+      <c r="D5225" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5226">
+      <c r="A5226" s="0">
+        <v>6253</v>
+      </c>
+      <c r="B5226" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5226" s="0">
+        <v>54</v>
+      </c>
+      <c r="D5226" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5227">
+      <c r="A5227" s="0">
+        <v>6254</v>
+      </c>
+      <c r="B5227" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5227" s="0">
+        <v>57</v>
+      </c>
+      <c r="D5227" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5228">
+      <c r="A5228" s="0">
+        <v>6255</v>
+      </c>
+      <c r="B5228" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5228" s="0">
+        <v>89</v>
+      </c>
+      <c r="D5228" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5229">
+      <c r="A5229" s="0">
+        <v>6256</v>
+      </c>
+      <c r="B5229" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5229" s="0">
+        <v>48</v>
+      </c>
+      <c r="D5229" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5230">
+      <c r="A5230" s="0">
+        <v>6257</v>
+      </c>
+      <c r="B5230" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5230" s="0">
+        <v>3686</v>
+      </c>
+      <c r="D5230" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5231">
+      <c r="A5231" s="0">
+        <v>6258</v>
+      </c>
+      <c r="B5231" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5231" s="0">
+        <v>68</v>
+      </c>
+      <c r="D5231" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5232">
+      <c r="A5232" s="0">
+        <v>6259</v>
+      </c>
+      <c r="B5232" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5232" s="0">
+        <v>3671</v>
+      </c>
+      <c r="D5232" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5233">
+      <c r="A5233" s="0">
+        <v>6260</v>
+      </c>
+      <c r="B5233" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5233" s="0">
+        <v>3669</v>
+      </c>
+      <c r="D5233" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5234">
+      <c r="A5234" s="0">
+        <v>6261</v>
+      </c>
+      <c r="B5234" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5234" s="0">
+        <v>74</v>
+      </c>
+      <c r="D5234" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5235">
+      <c r="A5235" s="0">
+        <v>6262</v>
+      </c>
+      <c r="B5235" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5235" s="0">
+        <v>66</v>
+      </c>
+      <c r="D5235" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5236">
+      <c r="A5236" s="0">
+        <v>6263</v>
+      </c>
+      <c r="B5236" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5236" s="0">
+        <v>63</v>
+      </c>
+      <c r="D5236" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5237">
+      <c r="A5237" s="0">
+        <v>6264</v>
+      </c>
+      <c r="B5237" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5237" s="0">
+        <v>77</v>
+      </c>
+      <c r="D5237" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5238">
+      <c r="A5238" s="0">
+        <v>6265</v>
+      </c>
+      <c r="B5238" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5238" s="0">
+        <v>52</v>
+      </c>
+      <c r="D5238" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5239">
+      <c r="A5239" s="0">
+        <v>6266</v>
+      </c>
+      <c r="B5239" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5239" s="0">
+        <v>62</v>
+      </c>
+      <c r="D5239" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5240">
+      <c r="A5240" s="0">
+        <v>6267</v>
+      </c>
+      <c r="B5240" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5240" s="0">
+        <v>67</v>
+      </c>
+      <c r="D5240" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5241">
+      <c r="A5241" s="0">
+        <v>6268</v>
+      </c>
+      <c r="B5241" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5241" s="0">
+        <v>78</v>
+      </c>
+      <c r="D5241" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5242">
+      <c r="A5242" s="0">
+        <v>6269</v>
+      </c>
+      <c r="B5242" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5242" s="0">
+        <v>3694</v>
+      </c>
+      <c r="D5242" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5243">
+      <c r="A5243" s="0">
+        <v>6270</v>
+      </c>
+      <c r="B5243" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5243" s="0">
+        <v>3695</v>
+      </c>
+      <c r="D5243" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5244">
+      <c r="A5244" s="0">
+        <v>6271</v>
+      </c>
+      <c r="B5244" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5244" s="0">
+        <v>60</v>
+      </c>
+      <c r="D5244" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5245">
+      <c r="A5245" s="0">
+        <v>6272</v>
+      </c>
+      <c r="B5245" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5245" s="0">
+        <v>3697</v>
+      </c>
+      <c r="D5245" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5246">
+      <c r="A5246" s="0">
+        <v>6273</v>
+      </c>
+      <c r="B5246" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5246" s="0">
+        <v>65</v>
+      </c>
+      <c r="D5246" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5247">
+      <c r="A5247" s="0">
+        <v>6274</v>
+      </c>
+      <c r="B5247" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5247" s="0">
+        <v>58</v>
+      </c>
+      <c r="D5247" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5248">
+      <c r="A5248" s="0">
+        <v>6275</v>
+      </c>
+      <c r="B5248" s="0">
+        <v>157</v>
+      </c>
+      <c r="C5248" s="0">
+        <v>3681</v>
+      </c>
+      <c r="D5248" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5249">
+      <c r="A5249" s="0">
+        <v>6276</v>
+      </c>
+      <c r="B5249" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5249" s="0">
+        <v>3655</v>
+      </c>
+      <c r="D5249" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5250">
+      <c r="A5250" s="0">
+        <v>6277</v>
+      </c>
+      <c r="B5250" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5250" s="0">
+        <v>3656</v>
+      </c>
+      <c r="D5250" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5251">
+      <c r="A5251" s="0">
+        <v>6278</v>
+      </c>
+      <c r="B5251" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5251" s="0">
+        <v>3659</v>
+      </c>
+      <c r="D5251" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5252">
+      <c r="A5252" s="0">
+        <v>6279</v>
+      </c>
+      <c r="B5252" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5252" s="0">
+        <v>3660</v>
+      </c>
+      <c r="D5252" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5253">
+      <c r="A5253" s="0">
+        <v>6280</v>
+      </c>
+      <c r="B5253" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5253" s="0">
+        <v>3661</v>
+      </c>
+      <c r="D5253" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5254">
+      <c r="A5254" s="0">
+        <v>6281</v>
+      </c>
+      <c r="B5254" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5254" s="0">
+        <v>3663</v>
+      </c>
+      <c r="D5254" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5255">
+      <c r="A5255" s="0">
+        <v>6282</v>
+      </c>
+      <c r="B5255" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5255" s="0">
+        <v>3665</v>
+      </c>
+      <c r="D5255" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5256">
+      <c r="A5256" s="0">
+        <v>6283</v>
+      </c>
+      <c r="B5256" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5256" s="0">
+        <v>3666</v>
+      </c>
+      <c r="D5256" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5257">
+      <c r="A5257" s="0">
+        <v>6284</v>
+      </c>
+      <c r="B5257" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5257" s="0">
+        <v>3667</v>
+      </c>
+      <c r="D5257" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5258">
+      <c r="A5258" s="0">
+        <v>6285</v>
+      </c>
+      <c r="B5258" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5258" s="0">
+        <v>3672</v>
+      </c>
+      <c r="D5258" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5259">
+      <c r="A5259" s="0">
+        <v>6286</v>
+      </c>
+      <c r="B5259" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5259" s="0">
+        <v>3673</v>
+      </c>
+      <c r="D5259" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5260">
+      <c r="A5260" s="0">
+        <v>6287</v>
+      </c>
+      <c r="B5260" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5260" s="0">
+        <v>3674</v>
+      </c>
+      <c r="D5260" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5261">
+      <c r="A5261" s="0">
+        <v>6288</v>
+      </c>
+      <c r="B5261" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5261" s="0">
+        <v>3675</v>
+      </c>
+      <c r="D5261" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5262">
+      <c r="A5262" s="0">
+        <v>6289</v>
+      </c>
+      <c r="B5262" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5262" s="0">
+        <v>3679</v>
+      </c>
+      <c r="D5262" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5263">
+      <c r="A5263" s="0">
+        <v>6290</v>
+      </c>
+      <c r="B5263" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5263" s="0">
+        <v>3680</v>
+      </c>
+      <c r="D5263" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5264">
+      <c r="A5264" s="0">
+        <v>6291</v>
+      </c>
+      <c r="B5264" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5264" s="0">
+        <v>3683</v>
+      </c>
+      <c r="D5264" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5265">
+      <c r="A5265" s="0">
+        <v>6292</v>
+      </c>
+      <c r="B5265" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5265" s="0">
+        <v>3684</v>
+      </c>
+      <c r="D5265" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5266">
+      <c r="A5266" s="0">
+        <v>6293</v>
+      </c>
+      <c r="B5266" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5266" s="0">
+        <v>3685</v>
+      </c>
+      <c r="D5266" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5267">
+      <c r="A5267" s="0">
+        <v>6294</v>
+      </c>
+      <c r="B5267" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5267" s="0">
+        <v>3687</v>
+      </c>
+      <c r="D5267" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5268">
+      <c r="A5268" s="0">
+        <v>6295</v>
+      </c>
+      <c r="B5268" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5268" s="0">
+        <v>3688</v>
+      </c>
+      <c r="D5268" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5269">
+      <c r="A5269" s="0">
+        <v>6296</v>
+      </c>
+      <c r="B5269" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5269" s="0">
+        <v>3689</v>
+      </c>
+      <c r="D5269" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5270">
+      <c r="A5270" s="0">
+        <v>6297</v>
+      </c>
+      <c r="B5270" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5270" s="0">
+        <v>3690</v>
+      </c>
+      <c r="D5270" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5271">
+      <c r="A5271" s="0">
+        <v>6298</v>
+      </c>
+      <c r="B5271" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5271" s="0">
+        <v>3691</v>
+      </c>
+      <c r="D5271" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5272">
+      <c r="A5272" s="0">
+        <v>6299</v>
+      </c>
+      <c r="B5272" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5272" s="0">
+        <v>3693</v>
+      </c>
+      <c r="D5272" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5273">
+      <c r="A5273" s="0">
+        <v>6300</v>
+      </c>
+      <c r="B5273" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5273" s="0">
+        <v>3696</v>
+      </c>
+      <c r="D5273" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5274">
+      <c r="A5274" s="0">
+        <v>6301</v>
+      </c>
+      <c r="B5274" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5274" s="0">
+        <v>3698</v>
+      </c>
+      <c r="D5274" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5275">
+      <c r="A5275" s="0">
+        <v>6302</v>
+      </c>
+      <c r="B5275" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5275" s="0">
+        <v>3699</v>
+      </c>
+      <c r="D5275" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5276">
+      <c r="A5276" s="0">
+        <v>6303</v>
+      </c>
+      <c r="B5276" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5276" s="0">
+        <v>3701</v>
+      </c>
+      <c r="D5276" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5277">
+      <c r="A5277" s="0">
+        <v>6304</v>
+      </c>
+      <c r="B5277" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5277" s="0">
+        <v>3702</v>
+      </c>
+      <c r="D5277" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5278">
+      <c r="A5278" s="0">
+        <v>6305</v>
+      </c>
+      <c r="B5278" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5278" s="0">
+        <v>3703</v>
+      </c>
+      <c r="D5278" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5279">
+      <c r="A5279" s="0">
+        <v>6306</v>
+      </c>
+      <c r="B5279" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5279" s="0">
+        <v>3704</v>
+      </c>
+      <c r="D5279" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5280">
+      <c r="A5280" s="0">
+        <v>6307</v>
+      </c>
+      <c r="B5280" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5280" s="0">
+        <v>3705</v>
+      </c>
+      <c r="D5280" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5281">
+      <c r="A5281" s="0">
+        <v>6308</v>
+      </c>
+      <c r="B5281" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5281" s="0">
+        <v>3706</v>
+      </c>
+      <c r="D5281" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5282">
+      <c r="A5282" s="0">
+        <v>6309</v>
+      </c>
+      <c r="B5282" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5282" s="0">
+        <v>3707</v>
+      </c>
+      <c r="D5282" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5283">
+      <c r="A5283" s="0">
+        <v>6310</v>
+      </c>
+      <c r="B5283" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5283" s="0">
+        <v>3708</v>
+      </c>
+      <c r="D5283" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5284">
+      <c r="A5284" s="0">
+        <v>6311</v>
+      </c>
+      <c r="B5284" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5284" s="0">
+        <v>3709</v>
+      </c>
+      <c r="D5284" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5285">
+      <c r="A5285" s="0">
+        <v>6312</v>
+      </c>
+      <c r="B5285" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5285" s="0">
+        <v>3710</v>
+      </c>
+      <c r="D5285" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5286">
+      <c r="A5286" s="0">
+        <v>6313</v>
+      </c>
+      <c r="B5286" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5286" s="0">
+        <v>3711</v>
+      </c>
+      <c r="D5286" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5287">
+      <c r="A5287" s="0">
+        <v>6314</v>
+      </c>
+      <c r="B5287" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5287" s="0">
+        <v>3712</v>
+      </c>
+      <c r="D5287" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5288">
+      <c r="A5288" s="0">
+        <v>6315</v>
+      </c>
+      <c r="B5288" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5288" s="0">
+        <v>3713</v>
+      </c>
+      <c r="D5288" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5289">
+      <c r="A5289" s="0">
+        <v>6316</v>
+      </c>
+      <c r="B5289" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5289" s="0">
+        <v>3714</v>
+      </c>
+      <c r="D5289" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5290">
+      <c r="A5290" s="0">
+        <v>6317</v>
+      </c>
+      <c r="B5290" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5290" s="0">
+        <v>3715</v>
+      </c>
+      <c r="D5290" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5291">
+      <c r="A5291" s="0">
+        <v>6318</v>
+      </c>
+      <c r="B5291" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5291" s="0">
+        <v>3716</v>
+      </c>
+      <c r="D5291" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5292">
+      <c r="A5292" s="0">
+        <v>6319</v>
+      </c>
+      <c r="B5292" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5292" s="0">
+        <v>3717</v>
+      </c>
+      <c r="D5292" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5293">
+      <c r="A5293" s="0">
+        <v>6320</v>
+      </c>
+      <c r="B5293" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5293" s="0">
+        <v>3718</v>
+      </c>
+      <c r="D5293" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5294">
+      <c r="A5294" s="0">
+        <v>6321</v>
+      </c>
+      <c r="B5294" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5294" s="0">
+        <v>3719</v>
+      </c>
+      <c r="D5294" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5295">
+      <c r="A5295" s="0">
+        <v>6322</v>
+      </c>
+      <c r="B5295" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5295" s="0">
+        <v>3720</v>
+      </c>
+      <c r="D5295" s="0">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
